--- a/research/traditional_assets/database/data/spain/spain_diversified.xlsx
+++ b/research/traditional_assets/database/data/spain/spain_diversified.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="bme_alb" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -588,46 +590,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.0013</v>
+        <v>0.291</v>
       </c>
       <c r="E2">
-        <v>-0.295</v>
+        <v>-0.118</v>
       </c>
       <c r="G2">
-        <v>-0.8299046663321625</v>
+        <v>0.576419965576592</v>
       </c>
       <c r="H2">
-        <v>-0.8299046663321625</v>
+        <v>0.576419965576592</v>
       </c>
       <c r="I2">
-        <v>-0.2584044154540893</v>
+        <v>0.6113597246127367</v>
       </c>
       <c r="J2">
-        <v>-0.2367081956659629</v>
+        <v>0.5992130114104115</v>
       </c>
       <c r="K2">
-        <v>51.9</v>
+        <v>391.5</v>
       </c>
       <c r="L2">
-        <v>0.2604114400401405</v>
+        <v>0.6738382099827883</v>
       </c>
       <c r="M2">
-        <v>69</v>
+        <v>60.9</v>
       </c>
       <c r="N2">
-        <v>0.02031802120141343</v>
+        <v>0.0226748082508005</v>
       </c>
       <c r="O2">
-        <v>1.329479768786127</v>
+        <v>0.1555555555555556</v>
       </c>
       <c r="P2">
-        <v>69</v>
+        <v>60.9</v>
       </c>
       <c r="Q2">
-        <v>0.02031802120141343</v>
+        <v>0.0226748082508005</v>
       </c>
       <c r="R2">
-        <v>1.329479768786127</v>
+        <v>0.1555555555555556</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,73 +638,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>107.8</v>
+        <v>356.3</v>
       </c>
       <c r="V2">
-        <v>0.03174322732626619</v>
+        <v>0.1326606597661777</v>
       </c>
       <c r="W2">
-        <v>0.01143574828133263</v>
+        <v>0.08372003507046169</v>
       </c>
       <c r="X2">
-        <v>0.06318209191518474</v>
+        <v>0.1144241435552536</v>
       </c>
       <c r="Y2">
-        <v>-0.05174634363385212</v>
+        <v>-0.03070410848479194</v>
       </c>
       <c r="Z2">
-        <v>0.04677086266779312</v>
+        <v>0.1238515486772825</v>
       </c>
       <c r="AA2">
-        <v>-0.01107104651183385</v>
+        <v>0.07421345945075762</v>
       </c>
       <c r="AB2">
-        <v>0.06090668665062256</v>
+        <v>0.1019670140578315</v>
       </c>
       <c r="AC2">
-        <v>-0.07197773316245641</v>
+        <v>-0.02775355460707388</v>
       </c>
       <c r="AD2">
-        <v>232.7</v>
+        <v>645.6</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>232.7</v>
+        <v>645.6</v>
       </c>
       <c r="AG2">
-        <v>124.9</v>
+        <v>289.3</v>
       </c>
       <c r="AH2">
-        <v>0.0641276490203103</v>
+        <v>0.1937923995917632</v>
       </c>
       <c r="AI2">
-        <v>0.0456229781393981</v>
+        <v>0.1271041285216467</v>
       </c>
       <c r="AJ2">
-        <v>0.03547388451816297</v>
+        <v>0.09724042889314644</v>
       </c>
       <c r="AK2">
-        <v>0.02501652412522282</v>
+        <v>0.06125344060978192</v>
       </c>
       <c r="AL2">
-        <v>9.369999999999999</v>
+        <v>12.2</v>
       </c>
       <c r="AM2">
-        <v>-13.53</v>
+        <v>5.819999999999999</v>
       </c>
       <c r="AN2">
-        <v>-12.51075268817204</v>
+        <v>1.684759916492693</v>
       </c>
       <c r="AO2">
-        <v>-5.496264674493063</v>
+        <v>29.11475409836066</v>
       </c>
       <c r="AP2">
-        <v>-6.715053763440859</v>
+        <v>0.7549582463465554</v>
       </c>
       <c r="AQ2">
-        <v>3.806356245380636</v>
+        <v>61.03092783505155</v>
       </c>
     </row>
     <row r="3">
@@ -722,46 +724,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.0013</v>
+        <v>0.291</v>
       </c>
       <c r="E3">
-        <v>-0.295</v>
+        <v>-0.118</v>
       </c>
       <c r="G3">
-        <v>-0.8299046663321625</v>
+        <v>0.576419965576592</v>
       </c>
       <c r="H3">
-        <v>-0.8299046663321625</v>
+        <v>0.576419965576592</v>
       </c>
       <c r="I3">
-        <v>-0.2584044154540893</v>
+        <v>0.6113597246127367</v>
       </c>
       <c r="J3">
-        <v>-0.2367081956659629</v>
+        <v>0.5992130114104115</v>
       </c>
       <c r="K3">
-        <v>51.9</v>
+        <v>391.5</v>
       </c>
       <c r="L3">
-        <v>0.2604114400401405</v>
+        <v>0.6738382099827883</v>
       </c>
       <c r="M3">
-        <v>69</v>
+        <v>60.9</v>
       </c>
       <c r="N3">
-        <v>0.02031802120141343</v>
+        <v>0.0226748082508005</v>
       </c>
       <c r="O3">
-        <v>1.329479768786127</v>
+        <v>0.1555555555555556</v>
       </c>
       <c r="P3">
-        <v>69</v>
+        <v>60.9</v>
       </c>
       <c r="Q3">
-        <v>0.02031802120141343</v>
+        <v>0.0226748082508005</v>
       </c>
       <c r="R3">
-        <v>1.329479768786127</v>
+        <v>0.1555555555555556</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -770,73 +772,8785 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>107.8</v>
+        <v>356.3</v>
       </c>
       <c r="V3">
-        <v>0.03174322732626619</v>
+        <v>0.1326606597661777</v>
       </c>
       <c r="W3">
-        <v>0.01143574828133263</v>
+        <v>0.08372003507046169</v>
       </c>
       <c r="X3">
-        <v>0.06318209191518474</v>
+        <v>0.1144241435552536</v>
       </c>
       <c r="Y3">
-        <v>-0.05174634363385212</v>
+        <v>-0.03070410848479194</v>
       </c>
       <c r="Z3">
-        <v>0.04677086266779312</v>
+        <v>0.1238515486772825</v>
       </c>
       <c r="AA3">
-        <v>-0.01107104651183385</v>
+        <v>0.07421345945075762</v>
       </c>
       <c r="AB3">
-        <v>0.06090668665062256</v>
+        <v>0.1019670140578315</v>
       </c>
       <c r="AC3">
-        <v>-0.07197773316245641</v>
+        <v>-0.02775355460707388</v>
       </c>
       <c r="AD3">
-        <v>232.7</v>
+        <v>645.6</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>232.7</v>
+        <v>645.6</v>
       </c>
       <c r="AG3">
-        <v>124.9</v>
+        <v>289.3</v>
       </c>
       <c r="AH3">
-        <v>0.0641276490203103</v>
+        <v>0.1937923995917632</v>
       </c>
       <c r="AI3">
-        <v>0.0456229781393981</v>
+        <v>0.1271041285216467</v>
       </c>
       <c r="AJ3">
-        <v>0.03547388451816297</v>
+        <v>0.09724042889314644</v>
       </c>
       <c r="AK3">
-        <v>0.02501652412522282</v>
+        <v>0.06125344060978192</v>
       </c>
       <c r="AL3">
-        <v>9.369999999999999</v>
+        <v>12.2</v>
       </c>
       <c r="AM3">
-        <v>-13.53</v>
+        <v>5.819999999999999</v>
       </c>
       <c r="AN3">
-        <v>-12.51075268817204</v>
+        <v>1.684759916492693</v>
       </c>
       <c r="AO3">
-        <v>-5.496264674493063</v>
+        <v>29.11475409836066</v>
       </c>
       <c r="AP3">
-        <v>-6.715053763440859</v>
+        <v>0.7549582463465554</v>
       </c>
       <c r="AQ3">
-        <v>3.806356245380636</v>
+        <v>61.03092783505155</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AQ2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_capital</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>actual_equity_value</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>actual_enterprise_value</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_capital</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_rating</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>actual_beta</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Corporación Financiera Alba, S.A. (BME:ALB)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>BME:ALB</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Diversified</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>0.193792399591763</v>
+      </c>
+      <c r="F2">
+        <v>0.43</v>
+      </c>
+      <c r="G2">
+        <v>2685.8</v>
+      </c>
+      <c r="H2">
+        <v>2072.08713006412</v>
+      </c>
+      <c r="I2">
+        <v>2975.1</v>
+      </c>
+      <c r="J2">
+        <v>3148.28913006412</v>
+      </c>
+      <c r="K2">
+        <v>645.6</v>
+      </c>
+      <c r="L2">
+        <v>1432.502</v>
+      </c>
+      <c r="M2">
+        <v>0.101967014057831</v>
+      </c>
+      <c r="N2">
+        <v>0.09703862850123821</v>
+      </c>
+      <c r="O2">
+        <v>0.0501433486238532</v>
+      </c>
+      <c r="P2">
+        <v>0.04125</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="S2">
+        <v>0.114424143555254</v>
+      </c>
+      <c r="T2">
+        <v>0.139124786844277</v>
+      </c>
+      <c r="U2">
+        <v>0.871937875576893</v>
+      </c>
+      <c r="V2">
+        <v>1.15673351652294</v>
+      </c>
+      <c r="W2">
+        <v>4.508323072625251</v>
+      </c>
+      <c r="X2">
+        <v>0</v>
+      </c>
+      <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>0.0388</v>
+      </c>
+      <c r="AA2">
+        <v>2685.8</v>
+      </c>
+      <c r="AB2">
+        <v>0.08673111430699013</v>
+      </c>
+      <c r="AC2">
+        <v>0.06685779816513762</v>
+      </c>
+      <c r="AD2">
+        <v>0.25</v>
+      </c>
+      <c r="AE2">
+        <v>0</v>
+      </c>
+      <c r="AF2">
+        <v>1</v>
+      </c>
+      <c r="AG2">
+        <v>383.2</v>
+      </c>
+      <c r="AH2">
+        <v>28</v>
+      </c>
+      <c r="AI2">
+        <v>31.12</v>
+      </c>
+      <c r="AJ2">
+        <v>645.6</v>
+      </c>
+      <c r="AK2">
+        <v>645.6</v>
+      </c>
+      <c r="AL2">
+        <v>12.2</v>
+      </c>
+      <c r="AM2">
+        <v>645.6</v>
+      </c>
+      <c r="AN2">
+        <v>356.3</v>
+      </c>
+      <c r="AO2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ2">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.102872973110631</v>
+      </c>
+      <c r="C2">
+        <v>3301.61608234308</v>
+      </c>
+      <c r="D2">
+        <v>2945.31608234308</v>
+      </c>
+      <c r="E2">
+        <v>-645.6</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>356.3</v>
+      </c>
+      <c r="H2">
+        <v>2685.8</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>383.2</v>
+      </c>
+      <c r="K2">
+        <v>28</v>
+      </c>
+      <c r="L2">
+        <v>355.2</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>355.2</v>
+      </c>
+      <c r="O2">
+        <v>88.8</v>
+      </c>
+      <c r="P2">
+        <v>266.4</v>
+      </c>
+      <c r="Q2">
+        <v>294.4</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.102872973110631</v>
+      </c>
+      <c r="T2">
+        <v>0.7387541786196905</v>
+      </c>
+      <c r="U2">
+        <v>0.0457</v>
+      </c>
+      <c r="V2">
+        <v>0.25</v>
+      </c>
+      <c r="W2">
+        <v>0.034275</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.1026675406778544</v>
+      </c>
+      <c r="C3">
+        <v>3275.00339076427</v>
+      </c>
+      <c r="D3">
+        <v>2952.01739076427</v>
+      </c>
+      <c r="E3">
+        <v>-612.2860000000001</v>
+      </c>
+      <c r="F3">
+        <v>33.314</v>
+      </c>
+      <c r="G3">
+        <v>356.3</v>
+      </c>
+      <c r="H3">
+        <v>2685.8</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>383.2</v>
+      </c>
+      <c r="K3">
+        <v>28</v>
+      </c>
+      <c r="L3">
+        <v>355.2</v>
+      </c>
+      <c r="M3">
+        <v>1.5224498</v>
+      </c>
+      <c r="N3">
+        <v>353.6775502</v>
+      </c>
+      <c r="O3">
+        <v>88.41938755</v>
+      </c>
+      <c r="P3">
+        <v>265.25816265</v>
+      </c>
+      <c r="Q3">
+        <v>293.25816265</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.1033583744220752</v>
+      </c>
+      <c r="T3">
+        <v>0.7443508011849912</v>
+      </c>
+      <c r="U3">
+        <v>0.0457</v>
+      </c>
+      <c r="V3">
+        <v>0.25</v>
+      </c>
+      <c r="W3">
+        <v>0.034275</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>233.3081852682433</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.1024621082450778</v>
+      </c>
+      <c r="C4">
+        <v>3248.421262929271</v>
+      </c>
+      <c r="D4">
+        <v>2958.749262929271</v>
+      </c>
+      <c r="E4">
+        <v>-578.972</v>
+      </c>
+      <c r="F4">
+        <v>66.628</v>
+      </c>
+      <c r="G4">
+        <v>356.3</v>
+      </c>
+      <c r="H4">
+        <v>2685.8</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>383.2</v>
+      </c>
+      <c r="K4">
+        <v>28</v>
+      </c>
+      <c r="L4">
+        <v>355.2</v>
+      </c>
+      <c r="M4">
+        <v>3.0448996</v>
+      </c>
+      <c r="N4">
+        <v>352.1551004</v>
+      </c>
+      <c r="O4">
+        <v>88.0387751</v>
+      </c>
+      <c r="P4">
+        <v>264.1163253</v>
+      </c>
+      <c r="Q4">
+        <v>292.1163253</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.1038536818827325</v>
+      </c>
+      <c r="T4">
+        <v>0.7500616405373389</v>
+      </c>
+      <c r="U4">
+        <v>0.0457</v>
+      </c>
+      <c r="V4">
+        <v>0.25</v>
+      </c>
+      <c r="W4">
+        <v>0.034275</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>116.6540926341216</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.1022566758123012</v>
+      </c>
+      <c r="C5">
+        <v>3221.869908411536</v>
+      </c>
+      <c r="D5">
+        <v>2965.511908411536</v>
+      </c>
+      <c r="E5">
+        <v>-545.658</v>
+      </c>
+      <c r="F5">
+        <v>99.94199999999999</v>
+      </c>
+      <c r="G5">
+        <v>356.3</v>
+      </c>
+      <c r="H5">
+        <v>2685.8</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>383.2</v>
+      </c>
+      <c r="K5">
+        <v>28</v>
+      </c>
+      <c r="L5">
+        <v>355.2</v>
+      </c>
+      <c r="M5">
+        <v>4.5673494</v>
+      </c>
+      <c r="N5">
+        <v>350.6326506</v>
+      </c>
+      <c r="O5">
+        <v>87.65816264999999</v>
+      </c>
+      <c r="P5">
+        <v>262.97448795</v>
+      </c>
+      <c r="Q5">
+        <v>290.97448795</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.1043592018683518</v>
+      </c>
+      <c r="T5">
+        <v>0.7558902291546833</v>
+      </c>
+      <c r="U5">
+        <v>0.0457</v>
+      </c>
+      <c r="V5">
+        <v>0.25</v>
+      </c>
+      <c r="W5">
+        <v>0.034275</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>77.76939508941443</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.1020512433795247</v>
+      </c>
+      <c r="C6">
+        <v>3195.349538704943</v>
+      </c>
+      <c r="D6">
+        <v>2972.305538704943</v>
+      </c>
+      <c r="E6">
+        <v>-512.3440000000001</v>
+      </c>
+      <c r="F6">
+        <v>133.256</v>
+      </c>
+      <c r="G6">
+        <v>356.3</v>
+      </c>
+      <c r="H6">
+        <v>2685.8</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>383.2</v>
+      </c>
+      <c r="K6">
+        <v>28</v>
+      </c>
+      <c r="L6">
+        <v>355.2</v>
+      </c>
+      <c r="M6">
+        <v>6.089799200000001</v>
+      </c>
+      <c r="N6">
+        <v>349.1102008</v>
+      </c>
+      <c r="O6">
+        <v>87.27755019999999</v>
+      </c>
+      <c r="P6">
+        <v>261.8326506</v>
+      </c>
+      <c r="Q6">
+        <v>289.8326506</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.1048752535203382</v>
+      </c>
+      <c r="T6">
+        <v>0.7618402467015558</v>
+      </c>
+      <c r="U6">
+        <v>0.0457</v>
+      </c>
+      <c r="V6">
+        <v>0.25</v>
+      </c>
+      <c r="W6">
+        <v>0.034275</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>58.32704631706082</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.1018458109467481</v>
+      </c>
+      <c r="C7">
+        <v>3168.86036724585</v>
+      </c>
+      <c r="D7">
+        <v>2979.13036724585</v>
+      </c>
+      <c r="E7">
+        <v>-479.03</v>
+      </c>
+      <c r="F7">
+        <v>166.57</v>
+      </c>
+      <c r="G7">
+        <v>356.3</v>
+      </c>
+      <c r="H7">
+        <v>2685.8</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>383.2</v>
+      </c>
+      <c r="K7">
+        <v>28</v>
+      </c>
+      <c r="L7">
+        <v>355.2</v>
+      </c>
+      <c r="M7">
+        <v>7.612249000000002</v>
+      </c>
+      <c r="N7">
+        <v>347.587751</v>
+      </c>
+      <c r="O7">
+        <v>86.89693774999999</v>
+      </c>
+      <c r="P7">
+        <v>260.69081325</v>
+      </c>
+      <c r="Q7">
+        <v>288.69081325</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.1054021694176296</v>
+      </c>
+      <c r="T7">
+        <v>0.7679155277757309</v>
+      </c>
+      <c r="U7">
+        <v>0.0457</v>
+      </c>
+      <c r="V7">
+        <v>0.25</v>
+      </c>
+      <c r="W7">
+        <v>0.034275</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>46.66163705364865</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.1016403785139715</v>
+      </c>
+      <c r="C8">
+        <v>3142.402609435449</v>
+      </c>
+      <c r="D8">
+        <v>2985.986609435448</v>
+      </c>
+      <c r="E8">
+        <v>-445.716</v>
+      </c>
+      <c r="F8">
+        <v>199.884</v>
+      </c>
+      <c r="G8">
+        <v>356.3</v>
+      </c>
+      <c r="H8">
+        <v>2685.8</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>383.2</v>
+      </c>
+      <c r="K8">
+        <v>28</v>
+      </c>
+      <c r="L8">
+        <v>355.2</v>
+      </c>
+      <c r="M8">
+        <v>9.134698800000001</v>
+      </c>
+      <c r="N8">
+        <v>346.0653012</v>
+      </c>
+      <c r="O8">
+        <v>86.51632529999999</v>
+      </c>
+      <c r="P8">
+        <v>259.5489759</v>
+      </c>
+      <c r="Q8">
+        <v>287.5489759</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.1059402962914591</v>
+      </c>
+      <c r="T8">
+        <v>0.7741200701493566</v>
+      </c>
+      <c r="U8">
+        <v>0.0457</v>
+      </c>
+      <c r="V8">
+        <v>0.25</v>
+      </c>
+      <c r="W8">
+        <v>0.034275</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>38.88469754470722</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.1014349460811949</v>
+      </c>
+      <c r="C9">
+        <v>3115.976482662416</v>
+      </c>
+      <c r="D9">
+        <v>2992.874482662416</v>
+      </c>
+      <c r="E9">
+        <v>-412.402</v>
+      </c>
+      <c r="F9">
+        <v>233.198</v>
+      </c>
+      <c r="G9">
+        <v>356.3</v>
+      </c>
+      <c r="H9">
+        <v>2685.8</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>383.2</v>
+      </c>
+      <c r="K9">
+        <v>28</v>
+      </c>
+      <c r="L9">
+        <v>355.2</v>
+      </c>
+      <c r="M9">
+        <v>10.6571486</v>
+      </c>
+      <c r="N9">
+        <v>344.5428514</v>
+      </c>
+      <c r="O9">
+        <v>86.13571284999999</v>
+      </c>
+      <c r="P9">
+        <v>258.40713855</v>
+      </c>
+      <c r="Q9">
+        <v>286.40713855</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.1064899957862311</v>
+      </c>
+      <c r="T9">
+        <v>0.7804580435417697</v>
+      </c>
+      <c r="U9">
+        <v>0.0457</v>
+      </c>
+      <c r="V9">
+        <v>0.25</v>
+      </c>
+      <c r="W9">
+        <v>0.034275</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>33.32974075260618</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.1012295136484184</v>
+      </c>
+      <c r="C10">
+        <v>3089.582206325903</v>
+      </c>
+      <c r="D10">
+        <v>2999.794206325903</v>
+      </c>
+      <c r="E10">
+        <v>-379.088</v>
+      </c>
+      <c r="F10">
+        <v>266.512</v>
+      </c>
+      <c r="G10">
+        <v>356.3</v>
+      </c>
+      <c r="H10">
+        <v>2685.8</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>383.2</v>
+      </c>
+      <c r="K10">
+        <v>28</v>
+      </c>
+      <c r="L10">
+        <v>355.2</v>
+      </c>
+      <c r="M10">
+        <v>12.1795984</v>
+      </c>
+      <c r="N10">
+        <v>343.0204016</v>
+      </c>
+      <c r="O10">
+        <v>85.7551004</v>
+      </c>
+      <c r="P10">
+        <v>257.2653012</v>
+      </c>
+      <c r="Q10">
+        <v>285.2653012</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.10705164527002</v>
+      </c>
+      <c r="T10">
+        <v>0.7869337989644529</v>
+      </c>
+      <c r="U10">
+        <v>0.0457</v>
+      </c>
+      <c r="V10">
+        <v>0.25</v>
+      </c>
+      <c r="W10">
+        <v>0.034275</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>29.16352315853041</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.1010240812156418</v>
+      </c>
+      <c r="C11">
+        <v>3063.220001858821</v>
+      </c>
+      <c r="D11">
+        <v>3006.746001858821</v>
+      </c>
+      <c r="E11">
+        <v>-345.774</v>
+      </c>
+      <c r="F11">
+        <v>299.826</v>
+      </c>
+      <c r="G11">
+        <v>356.3</v>
+      </c>
+      <c r="H11">
+        <v>2685.8</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>383.2</v>
+      </c>
+      <c r="K11">
+        <v>28</v>
+      </c>
+      <c r="L11">
+        <v>355.2</v>
+      </c>
+      <c r="M11">
+        <v>13.7020482</v>
+      </c>
+      <c r="N11">
+        <v>341.4979518</v>
+      </c>
+      <c r="O11">
+        <v>85.37448795</v>
+      </c>
+      <c r="P11">
+        <v>256.12346385</v>
+      </c>
+      <c r="Q11">
+        <v>284.12346385</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.1076256386985075</v>
+      </c>
+      <c r="T11">
+        <v>0.7935518786821401</v>
+      </c>
+      <c r="U11">
+        <v>0.0457</v>
+      </c>
+      <c r="V11">
+        <v>0.25</v>
+      </c>
+      <c r="W11">
+        <v>0.034275</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>25.92313169647148</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.1008186487828652</v>
+      </c>
+      <c r="C12">
+        <v>3036.890092751468</v>
+      </c>
+      <c r="D12">
+        <v>3013.730092751468</v>
+      </c>
+      <c r="E12">
+        <v>-312.46</v>
+      </c>
+      <c r="F12">
+        <v>333.14</v>
+      </c>
+      <c r="G12">
+        <v>356.3</v>
+      </c>
+      <c r="H12">
+        <v>2685.8</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>383.2</v>
+      </c>
+      <c r="K12">
+        <v>28</v>
+      </c>
+      <c r="L12">
+        <v>355.2</v>
+      </c>
+      <c r="M12">
+        <v>15.224498</v>
+      </c>
+      <c r="N12">
+        <v>339.975502</v>
+      </c>
+      <c r="O12">
+        <v>84.9938755</v>
+      </c>
+      <c r="P12">
+        <v>254.9816265</v>
+      </c>
+      <c r="Q12">
+        <v>282.9816265</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.1082123875365169</v>
+      </c>
+      <c r="T12">
+        <v>0.800317026837998</v>
+      </c>
+      <c r="U12">
+        <v>0.0457</v>
+      </c>
+      <c r="V12">
+        <v>0.25</v>
+      </c>
+      <c r="W12">
+        <v>0.034275</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>23.33081852682433</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.1006132163500886</v>
+      </c>
+      <c r="C13">
+        <v>3010.592704575469</v>
+      </c>
+      <c r="D13">
+        <v>3020.746704575469</v>
+      </c>
+      <c r="E13">
+        <v>-279.146</v>
+      </c>
+      <c r="F13">
+        <v>366.454</v>
+      </c>
+      <c r="G13">
+        <v>356.3</v>
+      </c>
+      <c r="H13">
+        <v>2685.8</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>383.2</v>
+      </c>
+      <c r="K13">
+        <v>28</v>
+      </c>
+      <c r="L13">
+        <v>355.2</v>
+      </c>
+      <c r="M13">
+        <v>16.7469478</v>
+      </c>
+      <c r="N13">
+        <v>338.4530522</v>
+      </c>
+      <c r="O13">
+        <v>84.61326305</v>
+      </c>
+      <c r="P13">
+        <v>253.83978915</v>
+      </c>
+      <c r="Q13">
+        <v>281.83978915</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.1088123217416726</v>
+      </c>
+      <c r="T13">
+        <v>0.8072342007951113</v>
+      </c>
+      <c r="U13">
+        <v>0.0457</v>
+      </c>
+      <c r="V13">
+        <v>0.25</v>
+      </c>
+      <c r="W13">
+        <v>0.034275</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>21.20983502438576</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.100407783917312</v>
+      </c>
+      <c r="C14">
+        <v>2984.328065008078</v>
+      </c>
+      <c r="D14">
+        <v>3027.796065008078</v>
+      </c>
+      <c r="E14">
+        <v>-245.8320000000001</v>
+      </c>
+      <c r="F14">
+        <v>399.768</v>
+      </c>
+      <c r="G14">
+        <v>356.3</v>
+      </c>
+      <c r="H14">
+        <v>2685.8</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>383.2</v>
+      </c>
+      <c r="K14">
+        <v>28</v>
+      </c>
+      <c r="L14">
+        <v>355.2</v>
+      </c>
+      <c r="M14">
+        <v>18.2693976</v>
+      </c>
+      <c r="N14">
+        <v>336.9306024</v>
+      </c>
+      <c r="O14">
+        <v>84.2326506</v>
+      </c>
+      <c r="P14">
+        <v>252.6979518</v>
+      </c>
+      <c r="Q14">
+        <v>280.6979518</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.1094258908151273</v>
+      </c>
+      <c r="T14">
+        <v>0.8143085832512498</v>
+      </c>
+      <c r="U14">
+        <v>0.0457</v>
+      </c>
+      <c r="V14">
+        <v>0.25</v>
+      </c>
+      <c r="W14">
+        <v>0.034275</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>19.44234877235361</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.1002023514845355</v>
+      </c>
+      <c r="C15">
+        <v>2958.096403856788</v>
+      </c>
+      <c r="D15">
+        <v>3034.878403856787</v>
+      </c>
+      <c r="E15">
+        <v>-212.518</v>
+      </c>
+      <c r="F15">
+        <v>433.0820000000001</v>
+      </c>
+      <c r="G15">
+        <v>356.3</v>
+      </c>
+      <c r="H15">
+        <v>2685.8</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>383.2</v>
+      </c>
+      <c r="K15">
+        <v>28</v>
+      </c>
+      <c r="L15">
+        <v>355.2</v>
+      </c>
+      <c r="M15">
+        <v>19.79184740000001</v>
+      </c>
+      <c r="N15">
+        <v>335.4081526</v>
+      </c>
+      <c r="O15">
+        <v>83.85203815</v>
+      </c>
+      <c r="P15">
+        <v>251.55611445</v>
+      </c>
+      <c r="Q15">
+        <v>279.55611445</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.1100535649247534</v>
+      </c>
+      <c r="T15">
+        <v>0.8215455951891385</v>
+      </c>
+      <c r="U15">
+        <v>0.0457</v>
+      </c>
+      <c r="V15">
+        <v>0.25</v>
+      </c>
+      <c r="W15">
+        <v>0.034275</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>17.94678348217256</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.09999691905175889</v>
+      </c>
+      <c r="C16">
+        <v>2931.897953084311</v>
+      </c>
+      <c r="D16">
+        <v>3041.993953084311</v>
+      </c>
+      <c r="E16">
+        <v>-179.204</v>
+      </c>
+      <c r="F16">
+        <v>466.3960000000001</v>
+      </c>
+      <c r="G16">
+        <v>356.3</v>
+      </c>
+      <c r="H16">
+        <v>2685.8</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>383.2</v>
+      </c>
+      <c r="K16">
+        <v>28</v>
+      </c>
+      <c r="L16">
+        <v>355.2</v>
+      </c>
+      <c r="M16">
+        <v>21.31429720000001</v>
+      </c>
+      <c r="N16">
+        <v>333.8857028</v>
+      </c>
+      <c r="O16">
+        <v>83.4714257</v>
+      </c>
+      <c r="P16">
+        <v>250.4142771</v>
+      </c>
+      <c r="Q16">
+        <v>278.4142771</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.1106958361066964</v>
+      </c>
+      <c r="T16">
+        <v>0.8289509097302341</v>
+      </c>
+      <c r="U16">
+        <v>0.0457</v>
+      </c>
+      <c r="V16">
+        <v>0.25</v>
+      </c>
+      <c r="W16">
+        <v>0.034275</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>16.66487037630309</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.09979148661898232</v>
+      </c>
+      <c r="C17">
+        <v>2905.732946833907</v>
+      </c>
+      <c r="D17">
+        <v>3049.142946833907</v>
+      </c>
+      <c r="E17">
+        <v>-145.89</v>
+      </c>
+      <c r="F17">
+        <v>499.71</v>
+      </c>
+      <c r="G17">
+        <v>356.3</v>
+      </c>
+      <c r="H17">
+        <v>2685.8</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>383.2</v>
+      </c>
+      <c r="K17">
+        <v>28</v>
+      </c>
+      <c r="L17">
+        <v>355.2</v>
+      </c>
+      <c r="M17">
+        <v>22.836747</v>
+      </c>
+      <c r="N17">
+        <v>332.363253</v>
+      </c>
+      <c r="O17">
+        <v>83.09081325</v>
+      </c>
+      <c r="P17">
+        <v>249.27243975</v>
+      </c>
+      <c r="Q17">
+        <v>277.27243975</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.1113532195517439</v>
+      </c>
+      <c r="T17">
+        <v>0.8365304669664142</v>
+      </c>
+      <c r="U17">
+        <v>0.0457</v>
+      </c>
+      <c r="V17">
+        <v>0.25</v>
+      </c>
+      <c r="W17">
+        <v>0.034275</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>15.55387901788289</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.09958605418620572</v>
+      </c>
+      <c r="C18">
+        <v>2879.601621455057</v>
+      </c>
+      <c r="D18">
+        <v>3056.325621455057</v>
+      </c>
+      <c r="E18">
+        <v>-112.576</v>
+      </c>
+      <c r="F18">
+        <v>533.024</v>
+      </c>
+      <c r="G18">
+        <v>356.3</v>
+      </c>
+      <c r="H18">
+        <v>2685.8</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>383.2</v>
+      </c>
+      <c r="K18">
+        <v>28</v>
+      </c>
+      <c r="L18">
+        <v>355.2</v>
+      </c>
+      <c r="M18">
+        <v>24.3591968</v>
+      </c>
+      <c r="N18">
+        <v>330.8408032</v>
+      </c>
+      <c r="O18">
+        <v>82.7102008</v>
+      </c>
+      <c r="P18">
+        <v>248.1306024</v>
+      </c>
+      <c r="Q18">
+        <v>276.1306024</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.1120262549835783</v>
+      </c>
+      <c r="T18">
+        <v>0.8442904898510748</v>
+      </c>
+      <c r="U18">
+        <v>0.0457</v>
+      </c>
+      <c r="V18">
+        <v>0.25</v>
+      </c>
+      <c r="W18">
+        <v>0.034275</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>14.5817615792652</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.09938062175342918</v>
+      </c>
+      <c r="C19">
+        <v>2853.504215529516</v>
+      </c>
+      <c r="D19">
+        <v>3063.542215529516</v>
+      </c>
+      <c r="E19">
+        <v>-79.26199999999994</v>
+      </c>
+      <c r="F19">
+        <v>566.3380000000001</v>
+      </c>
+      <c r="G19">
+        <v>356.3</v>
+      </c>
+      <c r="H19">
+        <v>2685.8</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>383.2</v>
+      </c>
+      <c r="K19">
+        <v>28</v>
+      </c>
+      <c r="L19">
+        <v>355.2</v>
+      </c>
+      <c r="M19">
+        <v>25.88164660000001</v>
+      </c>
+      <c r="N19">
+        <v>329.3183534</v>
+      </c>
+      <c r="O19">
+        <v>82.32958834999999</v>
+      </c>
+      <c r="P19">
+        <v>246.98876505</v>
+      </c>
+      <c r="Q19">
+        <v>274.98876505</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.1127155081366617</v>
+      </c>
+      <c r="T19">
+        <v>0.8522375012389805</v>
+      </c>
+      <c r="U19">
+        <v>0.0457</v>
+      </c>
+      <c r="V19">
+        <v>0.25</v>
+      </c>
+      <c r="W19">
+        <v>0.034275</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>13.72401089813196</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.09917518932065258</v>
+      </c>
+      <c r="C20">
+        <v>2827.440969897734</v>
+      </c>
+      <c r="D20">
+        <v>3070.792969897734</v>
+      </c>
+      <c r="E20">
+        <v>-45.94799999999998</v>
+      </c>
+      <c r="F20">
+        <v>599.652</v>
+      </c>
+      <c r="G20">
+        <v>356.3</v>
+      </c>
+      <c r="H20">
+        <v>2685.8</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>383.2</v>
+      </c>
+      <c r="K20">
+        <v>28</v>
+      </c>
+      <c r="L20">
+        <v>355.2</v>
+      </c>
+      <c r="M20">
+        <v>27.4040964</v>
+      </c>
+      <c r="N20">
+        <v>327.7959036</v>
+      </c>
+      <c r="O20">
+        <v>81.94897589999999</v>
+      </c>
+      <c r="P20">
+        <v>245.8469277</v>
+      </c>
+      <c r="Q20">
+        <v>273.8469277</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.1134215723422592</v>
+      </c>
+      <c r="T20">
+        <v>0.8603783421729322</v>
+      </c>
+      <c r="U20">
+        <v>0.0457</v>
+      </c>
+      <c r="V20">
+        <v>0.25</v>
+      </c>
+      <c r="W20">
+        <v>0.034275</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>12.96156584823574</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.09919775688787602</v>
+      </c>
+      <c r="C21">
+        <v>2793.328768112862</v>
+      </c>
+      <c r="D21">
+        <v>3069.994768112862</v>
+      </c>
+      <c r="E21">
+        <v>-12.63400000000001</v>
+      </c>
+      <c r="F21">
+        <v>632.966</v>
+      </c>
+      <c r="G21">
+        <v>356.3</v>
+      </c>
+      <c r="H21">
+        <v>2685.8</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>383.2</v>
+      </c>
+      <c r="K21">
+        <v>28</v>
+      </c>
+      <c r="L21">
+        <v>355.2</v>
+      </c>
+      <c r="M21">
+        <v>29.9392918</v>
+      </c>
+      <c r="N21">
+        <v>325.2607082</v>
+      </c>
+      <c r="O21">
+        <v>81.31517705</v>
+      </c>
+      <c r="P21">
+        <v>243.94553115</v>
+      </c>
+      <c r="Q21">
+        <v>271.94553115</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.1141450702319457</v>
+      </c>
+      <c r="T21">
+        <v>0.8687201915250065</v>
+      </c>
+      <c r="U21">
+        <v>0.0473</v>
+      </c>
+      <c r="V21">
+        <v>0.25</v>
+      </c>
+      <c r="W21">
+        <v>0.035475</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>11.86400808585593</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.09900432445509944</v>
+      </c>
+      <c r="C22">
+        <v>2766.869855730635</v>
+      </c>
+      <c r="D22">
+        <v>3076.849855730635</v>
+      </c>
+      <c r="E22">
+        <v>20.68000000000006</v>
+      </c>
+      <c r="F22">
+        <v>666.2800000000001</v>
+      </c>
+      <c r="G22">
+        <v>356.3</v>
+      </c>
+      <c r="H22">
+        <v>2685.8</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>383.2</v>
+      </c>
+      <c r="K22">
+        <v>28</v>
+      </c>
+      <c r="L22">
+        <v>355.2</v>
+      </c>
+      <c r="M22">
+        <v>31.51504400000001</v>
+      </c>
+      <c r="N22">
+        <v>323.684956</v>
+      </c>
+      <c r="O22">
+        <v>80.921239</v>
+      </c>
+      <c r="P22">
+        <v>242.763717</v>
+      </c>
+      <c r="Q22">
+        <v>270.763717</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.1148866555688743</v>
+      </c>
+      <c r="T22">
+        <v>0.8772705871108825</v>
+      </c>
+      <c r="U22">
+        <v>0.0473</v>
+      </c>
+      <c r="V22">
+        <v>0.25</v>
+      </c>
+      <c r="W22">
+        <v>0.035475</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>11.27080768156313</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.09881089202232286</v>
+      </c>
+      <c r="C23">
+        <v>2740.44162574043</v>
+      </c>
+      <c r="D23">
+        <v>3083.73562574043</v>
+      </c>
+      <c r="E23">
+        <v>53.99399999999991</v>
+      </c>
+      <c r="F23">
+        <v>699.5939999999999</v>
+      </c>
+      <c r="G23">
+        <v>356.3</v>
+      </c>
+      <c r="H23">
+        <v>2685.8</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>383.2</v>
+      </c>
+      <c r="K23">
+        <v>28</v>
+      </c>
+      <c r="L23">
+        <v>355.2</v>
+      </c>
+      <c r="M23">
+        <v>33.0907962</v>
+      </c>
+      <c r="N23">
+        <v>322.1092038</v>
+      </c>
+      <c r="O23">
+        <v>80.52730095</v>
+      </c>
+      <c r="P23">
+        <v>241.58190285</v>
+      </c>
+      <c r="Q23">
+        <v>269.58190285</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.1156470152181302</v>
+      </c>
+      <c r="T23">
+        <v>0.8860374484077933</v>
+      </c>
+      <c r="U23">
+        <v>0.0473</v>
+      </c>
+      <c r="V23">
+        <v>0.25</v>
+      </c>
+      <c r="W23">
+        <v>0.035475</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>10.73410255386965</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.09924445958954627</v>
+      </c>
+      <c r="C24">
+        <v>2691.736237825321</v>
+      </c>
+      <c r="D24">
+        <v>3068.34423782532</v>
+      </c>
+      <c r="E24">
+        <v>87.30799999999999</v>
+      </c>
+      <c r="F24">
+        <v>732.908</v>
+      </c>
+      <c r="G24">
+        <v>356.3</v>
+      </c>
+      <c r="H24">
+        <v>2685.8</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>383.2</v>
+      </c>
+      <c r="K24">
+        <v>28</v>
+      </c>
+      <c r="L24">
+        <v>355.2</v>
+      </c>
+      <c r="M24">
+        <v>37.4515988</v>
+      </c>
+      <c r="N24">
+        <v>317.7484012</v>
+      </c>
+      <c r="O24">
+        <v>79.4371003</v>
+      </c>
+      <c r="P24">
+        <v>238.3113009</v>
+      </c>
+      <c r="Q24">
+        <v>266.3113009</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.1164268712686491</v>
+      </c>
+      <c r="T24">
+        <v>0.8950291010200095</v>
+      </c>
+      <c r="U24">
+        <v>0.0511</v>
+      </c>
+      <c r="V24">
+        <v>0.25</v>
+      </c>
+      <c r="W24">
+        <v>0.038325</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>9.484241297597153</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.0990795271567697</v>
+      </c>
+      <c r="C25">
+        <v>2664.259099097229</v>
+      </c>
+      <c r="D25">
+        <v>3074.181099097229</v>
+      </c>
+      <c r="E25">
+        <v>120.6220000000001</v>
+      </c>
+      <c r="F25">
+        <v>766.2220000000001</v>
+      </c>
+      <c r="G25">
+        <v>356.3</v>
+      </c>
+      <c r="H25">
+        <v>2685.8</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>383.2</v>
+      </c>
+      <c r="K25">
+        <v>28</v>
+      </c>
+      <c r="L25">
+        <v>355.2</v>
+      </c>
+      <c r="M25">
+        <v>39.15394420000001</v>
+      </c>
+      <c r="N25">
+        <v>316.0460558</v>
+      </c>
+      <c r="O25">
+        <v>79.01151394999999</v>
+      </c>
+      <c r="P25">
+        <v>237.03454185</v>
+      </c>
+      <c r="Q25">
+        <v>265.03454185</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.1172269833204801</v>
+      </c>
+      <c r="T25">
+        <v>0.9042543030507251</v>
+      </c>
+      <c r="U25">
+        <v>0.0511</v>
+      </c>
+      <c r="V25">
+        <v>0.25</v>
+      </c>
+      <c r="W25">
+        <v>0.038325</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>9.071882980310319</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.09891459472399312</v>
+      </c>
+      <c r="C26">
+        <v>2636.80420942543</v>
+      </c>
+      <c r="D26">
+        <v>3080.04020942543</v>
+      </c>
+      <c r="E26">
+        <v>153.9359999999999</v>
+      </c>
+      <c r="F26">
+        <v>799.5359999999999</v>
+      </c>
+      <c r="G26">
+        <v>356.3</v>
+      </c>
+      <c r="H26">
+        <v>2685.8</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>383.2</v>
+      </c>
+      <c r="K26">
+        <v>28</v>
+      </c>
+      <c r="L26">
+        <v>355.2</v>
+      </c>
+      <c r="M26">
+        <v>40.8562896</v>
+      </c>
+      <c r="N26">
+        <v>314.3437104</v>
+      </c>
+      <c r="O26">
+        <v>78.58592759999999</v>
+      </c>
+      <c r="P26">
+        <v>235.7577828</v>
+      </c>
+      <c r="Q26">
+        <v>263.7577828</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.1180481509526225</v>
+      </c>
+      <c r="T26">
+        <v>0.9137222735559331</v>
+      </c>
+      <c r="U26">
+        <v>0.0511</v>
+      </c>
+      <c r="V26">
+        <v>0.25</v>
+      </c>
+      <c r="W26">
+        <v>0.038325</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>8.693887856130724</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.09874966229121655</v>
+      </c>
+      <c r="C27">
+        <v>2609.371696266893</v>
+      </c>
+      <c r="D27">
+        <v>3085.921696266893</v>
+      </c>
+      <c r="E27">
+        <v>187.25</v>
+      </c>
+      <c r="F27">
+        <v>832.85</v>
+      </c>
+      <c r="G27">
+        <v>356.3</v>
+      </c>
+      <c r="H27">
+        <v>2685.8</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>383.2</v>
+      </c>
+      <c r="K27">
+        <v>28</v>
+      </c>
+      <c r="L27">
+        <v>355.2</v>
+      </c>
+      <c r="M27">
+        <v>42.558635</v>
+      </c>
+      <c r="N27">
+        <v>312.641365</v>
+      </c>
+      <c r="O27">
+        <v>78.16034125</v>
+      </c>
+      <c r="P27">
+        <v>234.48102375</v>
+      </c>
+      <c r="Q27">
+        <v>262.48102375</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.1188912163882887</v>
+      </c>
+      <c r="T27">
+        <v>0.9234427232746132</v>
+      </c>
+      <c r="U27">
+        <v>0.0511</v>
+      </c>
+      <c r="V27">
+        <v>0.25</v>
+      </c>
+      <c r="W27">
+        <v>0.038325</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>8.346132341885495</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.09858472985843997</v>
+      </c>
+      <c r="C28">
+        <v>2581.961688053994</v>
+      </c>
+      <c r="D28">
+        <v>3091.825688053994</v>
+      </c>
+      <c r="E28">
+        <v>220.5640000000001</v>
+      </c>
+      <c r="F28">
+        <v>866.1640000000001</v>
+      </c>
+      <c r="G28">
+        <v>356.3</v>
+      </c>
+      <c r="H28">
+        <v>2685.8</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>383.2</v>
+      </c>
+      <c r="K28">
+        <v>28</v>
+      </c>
+      <c r="L28">
+        <v>355.2</v>
+      </c>
+      <c r="M28">
+        <v>44.26098040000001</v>
+      </c>
+      <c r="N28">
+        <v>310.9390196</v>
+      </c>
+      <c r="O28">
+        <v>77.7347549</v>
+      </c>
+      <c r="P28">
+        <v>233.2042647</v>
+      </c>
+      <c r="Q28">
+        <v>261.2042647</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.1197570673762702</v>
+      </c>
+      <c r="T28">
+        <v>0.9334258878505549</v>
+      </c>
+      <c r="U28">
+        <v>0.0511</v>
+      </c>
+      <c r="V28">
+        <v>0.25</v>
+      </c>
+      <c r="W28">
+        <v>0.038325</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>8.025127251812975</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.0988045474256634</v>
+      </c>
+      <c r="C29">
+        <v>2540.784001516095</v>
+      </c>
+      <c r="D29">
+        <v>3083.962001516095</v>
+      </c>
+      <c r="E29">
+        <v>253.878</v>
+      </c>
+      <c r="F29">
+        <v>899.4780000000001</v>
+      </c>
+      <c r="G29">
+        <v>356.3</v>
+      </c>
+      <c r="H29">
+        <v>2685.8</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>383.2</v>
+      </c>
+      <c r="K29">
+        <v>28</v>
+      </c>
+      <c r="L29">
+        <v>355.2</v>
+      </c>
+      <c r="M29">
+        <v>47.67233400000001</v>
+      </c>
+      <c r="N29">
+        <v>307.527666</v>
+      </c>
+      <c r="O29">
+        <v>76.88191649999999</v>
+      </c>
+      <c r="P29">
+        <v>230.6457495</v>
+      </c>
+      <c r="Q29">
+        <v>258.6457495</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.1206466403091279</v>
+      </c>
+      <c r="T29">
+        <v>0.9436825637847417</v>
+      </c>
+      <c r="U29">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V29">
+        <v>0.25</v>
+      </c>
+      <c r="W29">
+        <v>0.03975000000000001</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>7.450862380683939</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.09865386499288681</v>
+      </c>
+      <c r="C30">
+        <v>2512.856149377852</v>
+      </c>
+      <c r="D30">
+        <v>3089.348149377852</v>
+      </c>
+      <c r="E30">
+        <v>287.1920000000001</v>
+      </c>
+      <c r="F30">
+        <v>932.7920000000001</v>
+      </c>
+      <c r="G30">
+        <v>356.3</v>
+      </c>
+      <c r="H30">
+        <v>2685.8</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>383.2</v>
+      </c>
+      <c r="K30">
+        <v>28</v>
+      </c>
+      <c r="L30">
+        <v>355.2</v>
+      </c>
+      <c r="M30">
+        <v>49.43797600000001</v>
+      </c>
+      <c r="N30">
+        <v>305.762024</v>
+      </c>
+      <c r="O30">
+        <v>76.440506</v>
+      </c>
+      <c r="P30">
+        <v>229.321518</v>
+      </c>
+      <c r="Q30">
+        <v>257.321518</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.1215609236012317</v>
+      </c>
+      <c r="T30">
+        <v>0.9542241473837669</v>
+      </c>
+      <c r="U30">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V30">
+        <v>0.25</v>
+      </c>
+      <c r="W30">
+        <v>0.03975000000000001</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>7.184760152802371</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.09850318256011022</v>
+      </c>
+      <c r="C31">
+        <v>2484.947143998739</v>
+      </c>
+      <c r="D31">
+        <v>3094.753143998739</v>
+      </c>
+      <c r="E31">
+        <v>320.506</v>
+      </c>
+      <c r="F31">
+        <v>966.106</v>
+      </c>
+      <c r="G31">
+        <v>356.3</v>
+      </c>
+      <c r="H31">
+        <v>2685.8</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>383.2</v>
+      </c>
+      <c r="K31">
+        <v>28</v>
+      </c>
+      <c r="L31">
+        <v>355.2</v>
+      </c>
+      <c r="M31">
+        <v>51.20361800000001</v>
+      </c>
+      <c r="N31">
+        <v>303.996382</v>
+      </c>
+      <c r="O31">
+        <v>75.9990955</v>
+      </c>
+      <c r="P31">
+        <v>227.9972865</v>
+      </c>
+      <c r="Q31">
+        <v>255.9972865</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.1225009613522679</v>
+      </c>
+      <c r="T31">
+        <v>0.9650626769996661</v>
+      </c>
+      <c r="U31">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V31">
+        <v>0.25</v>
+      </c>
+      <c r="W31">
+        <v>0.03975000000000001</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>6.937009802705737</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.09835250012733365</v>
+      </c>
+      <c r="C32">
+        <v>2457.057084472635</v>
+      </c>
+      <c r="D32">
+        <v>3100.177084472635</v>
+      </c>
+      <c r="E32">
+        <v>353.8199999999999</v>
+      </c>
+      <c r="F32">
+        <v>999.42</v>
+      </c>
+      <c r="G32">
+        <v>356.3</v>
+      </c>
+      <c r="H32">
+        <v>2685.8</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>383.2</v>
+      </c>
+      <c r="K32">
+        <v>28</v>
+      </c>
+      <c r="L32">
+        <v>355.2</v>
+      </c>
+      <c r="M32">
+        <v>52.96926000000001</v>
+      </c>
+      <c r="N32">
+        <v>302.23074</v>
+      </c>
+      <c r="O32">
+        <v>75.55768499999999</v>
+      </c>
+      <c r="P32">
+        <v>226.673055</v>
+      </c>
+      <c r="Q32">
+        <v>254.673055</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.1234678573247624</v>
+      </c>
+      <c r="T32">
+        <v>0.9762108788903053</v>
+      </c>
+      <c r="U32">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V32">
+        <v>0.25</v>
+      </c>
+      <c r="W32">
+        <v>0.03975000000000001</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>6.705776142615546</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.09820181769455708</v>
+      </c>
+      <c r="C33">
+        <v>2429.186070589342</v>
+      </c>
+      <c r="D33">
+        <v>3105.620070589342</v>
+      </c>
+      <c r="E33">
+        <v>387.1339999999999</v>
+      </c>
+      <c r="F33">
+        <v>1032.734</v>
+      </c>
+      <c r="G33">
+        <v>356.3</v>
+      </c>
+      <c r="H33">
+        <v>2685.8</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>383.2</v>
+      </c>
+      <c r="K33">
+        <v>28</v>
+      </c>
+      <c r="L33">
+        <v>355.2</v>
+      </c>
+      <c r="M33">
+        <v>54.734902</v>
+      </c>
+      <c r="N33">
+        <v>300.465098</v>
+      </c>
+      <c r="O33">
+        <v>75.1162745</v>
+      </c>
+      <c r="P33">
+        <v>225.3488235</v>
+      </c>
+      <c r="Q33">
+        <v>253.3488235</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.124462779267474</v>
+      </c>
+      <c r="T33">
+        <v>0.9876822170676297</v>
+      </c>
+      <c r="U33">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V33">
+        <v>0.25</v>
+      </c>
+      <c r="W33">
+        <v>0.03975000000000001</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>6.489460783176336</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.0980511352617805</v>
+      </c>
+      <c r="C34">
+        <v>2401.334202840691</v>
+      </c>
+      <c r="D34">
+        <v>3111.082202840691</v>
+      </c>
+      <c r="E34">
+        <v>420.448</v>
+      </c>
+      <c r="F34">
+        <v>1066.048</v>
+      </c>
+      <c r="G34">
+        <v>356.3</v>
+      </c>
+      <c r="H34">
+        <v>2685.8</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>383.2</v>
+      </c>
+      <c r="K34">
+        <v>28</v>
+      </c>
+      <c r="L34">
+        <v>355.2</v>
+      </c>
+      <c r="M34">
+        <v>56.500544</v>
+      </c>
+      <c r="N34">
+        <v>298.699456</v>
+      </c>
+      <c r="O34">
+        <v>74.674864</v>
+      </c>
+      <c r="P34">
+        <v>224.024592</v>
+      </c>
+      <c r="Q34">
+        <v>252.024592</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.1254869636202655</v>
+      </c>
+      <c r="T34">
+        <v>0.9994909475442872</v>
+      </c>
+      <c r="U34">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V34">
+        <v>0.25</v>
+      </c>
+      <c r="W34">
+        <v>0.03975000000000001</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>6.286665133702075</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.09839545282900393</v>
+      </c>
+      <c r="C35">
+        <v>2355.567029604706</v>
+      </c>
+      <c r="D35">
+        <v>3098.629029604706</v>
+      </c>
+      <c r="E35">
+        <v>453.7620000000001</v>
+      </c>
+      <c r="F35">
+        <v>1099.362</v>
+      </c>
+      <c r="G35">
+        <v>356.3</v>
+      </c>
+      <c r="H35">
+        <v>2685.8</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>383.2</v>
+      </c>
+      <c r="K35">
+        <v>28</v>
+      </c>
+      <c r="L35">
+        <v>355.2</v>
+      </c>
+      <c r="M35">
+        <v>60.46491</v>
+      </c>
+      <c r="N35">
+        <v>294.73509</v>
+      </c>
+      <c r="O35">
+        <v>73.6837725</v>
+      </c>
+      <c r="P35">
+        <v>221.0513175</v>
+      </c>
+      <c r="Q35">
+        <v>249.0513175</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.1265417206403044</v>
+      </c>
+      <c r="T35">
+        <v>1.011652177438158</v>
+      </c>
+      <c r="U35">
+        <v>0.055</v>
+      </c>
+      <c r="V35">
+        <v>0.25</v>
+      </c>
+      <c r="W35">
+        <v>0.04125</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>5.874481579481388</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.09825977039622734</v>
+      </c>
+      <c r="C36">
+        <v>2327.148429250918</v>
+      </c>
+      <c r="D36">
+        <v>3103.524429250917</v>
+      </c>
+      <c r="E36">
+        <v>487.0760000000001</v>
+      </c>
+      <c r="F36">
+        <v>1132.676</v>
+      </c>
+      <c r="G36">
+        <v>356.3</v>
+      </c>
+      <c r="H36">
+        <v>2685.8</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>383.2</v>
+      </c>
+      <c r="K36">
+        <v>28</v>
+      </c>
+      <c r="L36">
+        <v>355.2</v>
+      </c>
+      <c r="M36">
+        <v>62.29718000000001</v>
+      </c>
+      <c r="N36">
+        <v>292.90282</v>
+      </c>
+      <c r="O36">
+        <v>73.22570499999999</v>
+      </c>
+      <c r="P36">
+        <v>219.677115</v>
+      </c>
+      <c r="Q36">
+        <v>247.677115</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.1276284399942839</v>
+      </c>
+      <c r="T36">
+        <v>1.024181929450026</v>
+      </c>
+      <c r="U36">
+        <v>0.055</v>
+      </c>
+      <c r="V36">
+        <v>0.25</v>
+      </c>
+      <c r="W36">
+        <v>0.04125</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>5.70170270949664</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.09812408796345076</v>
+      </c>
+      <c r="C37">
+        <v>2298.74532146408</v>
+      </c>
+      <c r="D37">
+        <v>3108.43532146408</v>
+      </c>
+      <c r="E37">
+        <v>520.3900000000002</v>
+      </c>
+      <c r="F37">
+        <v>1165.99</v>
+      </c>
+      <c r="G37">
+        <v>356.3</v>
+      </c>
+      <c r="H37">
+        <v>2685.8</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>383.2</v>
+      </c>
+      <c r="K37">
+        <v>28</v>
+      </c>
+      <c r="L37">
+        <v>355.2</v>
+      </c>
+      <c r="M37">
+        <v>64.12945000000002</v>
+      </c>
+      <c r="N37">
+        <v>291.07055</v>
+      </c>
+      <c r="O37">
+        <v>72.76763749999999</v>
+      </c>
+      <c r="P37">
+        <v>218.3029125</v>
+      </c>
+      <c r="Q37">
+        <v>246.3029125</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.1287485968668473</v>
+      </c>
+      <c r="T37">
+        <v>1.037097212293027</v>
+      </c>
+      <c r="U37">
+        <v>0.055</v>
+      </c>
+      <c r="V37">
+        <v>0.25</v>
+      </c>
+      <c r="W37">
+        <v>0.04125</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>5.538796917796736</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.09798840553067419</v>
+      </c>
+      <c r="C38">
+        <v>2270.357779905197</v>
+      </c>
+      <c r="D38">
+        <v>3113.361779905197</v>
+      </c>
+      <c r="E38">
+        <v>553.7040000000001</v>
+      </c>
+      <c r="F38">
+        <v>1199.304</v>
+      </c>
+      <c r="G38">
+        <v>356.3</v>
+      </c>
+      <c r="H38">
+        <v>2685.8</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>383.2</v>
+      </c>
+      <c r="K38">
+        <v>28</v>
+      </c>
+      <c r="L38">
+        <v>355.2</v>
+      </c>
+      <c r="M38">
+        <v>65.96172</v>
+      </c>
+      <c r="N38">
+        <v>289.23828</v>
+      </c>
+      <c r="O38">
+        <v>72.30956999999999</v>
+      </c>
+      <c r="P38">
+        <v>216.92871</v>
+      </c>
+      <c r="Q38">
+        <v>244.92871</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.1299037586416784</v>
+      </c>
+      <c r="T38">
+        <v>1.050416097724872</v>
+      </c>
+      <c r="U38">
+        <v>0.055</v>
+      </c>
+      <c r="V38">
+        <v>0.25</v>
+      </c>
+      <c r="W38">
+        <v>0.04125</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>5.384941447857939</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.09785272309789761</v>
+      </c>
+      <c r="C39">
+        <v>2241.985878702983</v>
+      </c>
+      <c r="D39">
+        <v>3118.303878702982</v>
+      </c>
+      <c r="E39">
+        <v>587.0179999999999</v>
+      </c>
+      <c r="F39">
+        <v>1232.618</v>
+      </c>
+      <c r="G39">
+        <v>356.3</v>
+      </c>
+      <c r="H39">
+        <v>2685.8</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>383.2</v>
+      </c>
+      <c r="K39">
+        <v>28</v>
+      </c>
+      <c r="L39">
+        <v>355.2</v>
+      </c>
+      <c r="M39">
+        <v>67.79398999999999</v>
+      </c>
+      <c r="N39">
+        <v>287.40601</v>
+      </c>
+      <c r="O39">
+        <v>71.8515025</v>
+      </c>
+      <c r="P39">
+        <v>215.5545075</v>
+      </c>
+      <c r="Q39">
+        <v>243.5545075</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.1310955922188851</v>
+      </c>
+      <c r="T39">
+        <v>1.064157804916459</v>
+      </c>
+      <c r="U39">
+        <v>0.055</v>
+      </c>
+      <c r="V39">
+        <v>0.25</v>
+      </c>
+      <c r="W39">
+        <v>0.04125</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>5.239402489807725</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.09771704066512105</v>
+      </c>
+      <c r="C40">
+        <v>2213.629692457584</v>
+      </c>
+      <c r="D40">
+        <v>3123.261692457583</v>
+      </c>
+      <c r="E40">
+        <v>620.332</v>
+      </c>
+      <c r="F40">
+        <v>1265.932</v>
+      </c>
+      <c r="G40">
+        <v>356.3</v>
+      </c>
+      <c r="H40">
+        <v>2685.8</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>383.2</v>
+      </c>
+      <c r="K40">
+        <v>28</v>
+      </c>
+      <c r="L40">
+        <v>355.2</v>
+      </c>
+      <c r="M40">
+        <v>69.62626</v>
+      </c>
+      <c r="N40">
+        <v>285.57374</v>
+      </c>
+      <c r="O40">
+        <v>71.393435</v>
+      </c>
+      <c r="P40">
+        <v>214.180305</v>
+      </c>
+      <c r="Q40">
+        <v>242.180305</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.1323258720405178</v>
+      </c>
+      <c r="T40">
+        <v>1.078342792985193</v>
+      </c>
+      <c r="U40">
+        <v>0.055</v>
+      </c>
+      <c r="V40">
+        <v>0.25</v>
+      </c>
+      <c r="W40">
+        <v>0.04125</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>5.101523476918048</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.09758135823234446</v>
+      </c>
+      <c r="C41">
+        <v>2185.289296244333</v>
+      </c>
+      <c r="D41">
+        <v>3128.235296244333</v>
+      </c>
+      <c r="E41">
+        <v>653.6460000000001</v>
+      </c>
+      <c r="F41">
+        <v>1299.246</v>
+      </c>
+      <c r="G41">
+        <v>356.3</v>
+      </c>
+      <c r="H41">
+        <v>2685.8</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>383.2</v>
+      </c>
+      <c r="K41">
+        <v>28</v>
+      </c>
+      <c r="L41">
+        <v>355.2</v>
+      </c>
+      <c r="M41">
+        <v>71.45853000000001</v>
+      </c>
+      <c r="N41">
+        <v>283.74147</v>
+      </c>
+      <c r="O41">
+        <v>70.9353675</v>
+      </c>
+      <c r="P41">
+        <v>212.8061025</v>
+      </c>
+      <c r="Q41">
+        <v>240.8061025</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.1335964889054827</v>
+      </c>
+      <c r="T41">
+        <v>1.092992862629952</v>
+      </c>
+      <c r="U41">
+        <v>0.055</v>
+      </c>
+      <c r="V41">
+        <v>0.25</v>
+      </c>
+      <c r="W41">
+        <v>0.04125</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>4.970715182638097</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.09744567579956788</v>
+      </c>
+      <c r="C42">
+        <v>2156.964765617535</v>
+      </c>
+      <c r="D42">
+        <v>3133.224765617535</v>
+      </c>
+      <c r="E42">
+        <v>686.9600000000002</v>
+      </c>
+      <c r="F42">
+        <v>1332.56</v>
+      </c>
+      <c r="G42">
+        <v>356.3</v>
+      </c>
+      <c r="H42">
+        <v>2685.8</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>383.2</v>
+      </c>
+      <c r="K42">
+        <v>28</v>
+      </c>
+      <c r="L42">
+        <v>355.2</v>
+      </c>
+      <c r="M42">
+        <v>73.2908</v>
+      </c>
+      <c r="N42">
+        <v>281.9092</v>
+      </c>
+      <c r="O42">
+        <v>70.4773</v>
+      </c>
+      <c r="P42">
+        <v>211.4319</v>
+      </c>
+      <c r="Q42">
+        <v>239.4319</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.1349094596659465</v>
+      </c>
+      <c r="T42">
+        <v>1.108131267929536</v>
+      </c>
+      <c r="U42">
+        <v>0.055</v>
+      </c>
+      <c r="V42">
+        <v>0.25</v>
+      </c>
+      <c r="W42">
+        <v>0.04125</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>4.846447303072145</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.09730999336679129</v>
+      </c>
+      <c r="C43">
+        <v>2128.656176614295</v>
+      </c>
+      <c r="D43">
+        <v>3138.230176614295</v>
+      </c>
+      <c r="E43">
+        <v>720.2740000000002</v>
+      </c>
+      <c r="F43">
+        <v>1365.874</v>
+      </c>
+      <c r="G43">
+        <v>356.3</v>
+      </c>
+      <c r="H43">
+        <v>2685.8</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>383.2</v>
+      </c>
+      <c r="K43">
+        <v>28</v>
+      </c>
+      <c r="L43">
+        <v>355.2</v>
+      </c>
+      <c r="M43">
+        <v>75.12307000000001</v>
+      </c>
+      <c r="N43">
+        <v>280.0769299999999</v>
+      </c>
+      <c r="O43">
+        <v>70.01923249999999</v>
+      </c>
+      <c r="P43">
+        <v>210.0576975</v>
+      </c>
+      <c r="Q43">
+        <v>238.0576975</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.1362669379098158</v>
+      </c>
+      <c r="T43">
+        <v>1.123782839510461</v>
+      </c>
+      <c r="U43">
+        <v>0.055</v>
+      </c>
+      <c r="V43">
+        <v>0.25</v>
+      </c>
+      <c r="W43">
+        <v>0.04125</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>4.728241271289897</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.09717431093401474</v>
+      </c>
+      <c r="C44">
+        <v>2100.363605758381</v>
+      </c>
+      <c r="D44">
+        <v>3143.25160575838</v>
+      </c>
+      <c r="E44">
+        <v>753.5879999999999</v>
+      </c>
+      <c r="F44">
+        <v>1399.188</v>
+      </c>
+      <c r="G44">
+        <v>356.3</v>
+      </c>
+      <c r="H44">
+        <v>2685.8</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>383.2</v>
+      </c>
+      <c r="K44">
+        <v>28</v>
+      </c>
+      <c r="L44">
+        <v>355.2</v>
+      </c>
+      <c r="M44">
+        <v>76.95533999999999</v>
+      </c>
+      <c r="N44">
+        <v>278.24466</v>
+      </c>
+      <c r="O44">
+        <v>69.561165</v>
+      </c>
+      <c r="P44">
+        <v>208.683495</v>
+      </c>
+      <c r="Q44">
+        <v>236.683495</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.1376712257483013</v>
+      </c>
+      <c r="T44">
+        <v>1.139974120456247</v>
+      </c>
+      <c r="U44">
+        <v>0.055</v>
+      </c>
+      <c r="V44">
+        <v>0.25</v>
+      </c>
+      <c r="W44">
+        <v>0.04125</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>4.615664098163949</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.09703862850123816</v>
+      </c>
+      <c r="C45">
+        <v>2072.087130064125</v>
+      </c>
+      <c r="D45">
+        <v>3148.289130064124</v>
+      </c>
+      <c r="E45">
+        <v>786.9019999999999</v>
+      </c>
+      <c r="F45">
+        <v>1432.502</v>
+      </c>
+      <c r="G45">
+        <v>356.3</v>
+      </c>
+      <c r="H45">
+        <v>2685.8</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>383.2</v>
+      </c>
+      <c r="K45">
+        <v>28</v>
+      </c>
+      <c r="L45">
+        <v>355.2</v>
+      </c>
+      <c r="M45">
+        <v>78.78761</v>
+      </c>
+      <c r="N45">
+        <v>276.41239</v>
+      </c>
+      <c r="O45">
+        <v>69.10309749999999</v>
+      </c>
+      <c r="P45">
+        <v>207.3092925</v>
+      </c>
+      <c r="Q45">
+        <v>235.3092925</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.1391247868442775</v>
+      </c>
+      <c r="T45">
+        <v>1.156733516522936</v>
+      </c>
+      <c r="U45">
+        <v>0.055</v>
+      </c>
+      <c r="V45">
+        <v>0.25</v>
+      </c>
+      <c r="W45">
+        <v>0.04125</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>4.508323072625251</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.09815694606846158</v>
+      </c>
+      <c r="C46">
+        <v>1997.728629092492</v>
+      </c>
+      <c r="D46">
+        <v>3107.244629092492</v>
+      </c>
+      <c r="E46">
+        <v>820.216</v>
+      </c>
+      <c r="F46">
+        <v>1465.816</v>
+      </c>
+      <c r="G46">
+        <v>356.3</v>
+      </c>
+      <c r="H46">
+        <v>2685.8</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>383.2</v>
+      </c>
+      <c r="K46">
+        <v>28</v>
+      </c>
+      <c r="L46">
+        <v>355.2</v>
+      </c>
+      <c r="M46">
+        <v>86.18998080000001</v>
+      </c>
+      <c r="N46">
+        <v>269.0100192</v>
+      </c>
+      <c r="O46">
+        <v>67.2525048</v>
+      </c>
+      <c r="P46">
+        <v>201.7575144</v>
+      </c>
+      <c r="Q46">
+        <v>229.7575144</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.1406302608365385</v>
+      </c>
+      <c r="T46">
+        <v>1.174091462449151</v>
+      </c>
+      <c r="U46">
+        <v>0.05880000000000001</v>
+      </c>
+      <c r="V46">
+        <v>0.25</v>
+      </c>
+      <c r="W46">
+        <v>0.0441</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>4.121128659074953</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.09804976363568499</v>
+      </c>
+      <c r="C47">
+        <v>1968.302011567631</v>
+      </c>
+      <c r="D47">
+        <v>3111.132011567631</v>
+      </c>
+      <c r="E47">
+        <v>853.5300000000001</v>
+      </c>
+      <c r="F47">
+        <v>1499.13</v>
+      </c>
+      <c r="G47">
+        <v>356.3</v>
+      </c>
+      <c r="H47">
+        <v>2685.8</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>383.2</v>
+      </c>
+      <c r="K47">
+        <v>28</v>
+      </c>
+      <c r="L47">
+        <v>355.2</v>
+      </c>
+      <c r="M47">
+        <v>88.14884400000001</v>
+      </c>
+      <c r="N47">
+        <v>267.051156</v>
+      </c>
+      <c r="O47">
+        <v>66.762789</v>
+      </c>
+      <c r="P47">
+        <v>200.288367</v>
+      </c>
+      <c r="Q47">
+        <v>228.288367</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.1421904793376091</v>
+      </c>
+      <c r="T47">
+        <v>1.192080606409046</v>
+      </c>
+      <c r="U47">
+        <v>0.05880000000000001</v>
+      </c>
+      <c r="V47">
+        <v>0.25</v>
+      </c>
+      <c r="W47">
+        <v>0.0441</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>4.029548022206621</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.09939158120290843</v>
+      </c>
+      <c r="C48">
+        <v>1887.012362822453</v>
+      </c>
+      <c r="D48">
+        <v>3063.156362822454</v>
+      </c>
+      <c r="E48">
+        <v>886.8440000000002</v>
+      </c>
+      <c r="F48">
+        <v>1532.444</v>
+      </c>
+      <c r="G48">
+        <v>356.3</v>
+      </c>
+      <c r="H48">
+        <v>2685.8</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>383.2</v>
+      </c>
+      <c r="K48">
+        <v>28</v>
+      </c>
+      <c r="L48">
+        <v>355.2</v>
+      </c>
+      <c r="M48">
+        <v>96.54397200000001</v>
+      </c>
+      <c r="N48">
+        <v>258.656028</v>
+      </c>
+      <c r="O48">
+        <v>64.664007</v>
+      </c>
+      <c r="P48">
+        <v>193.992021</v>
+      </c>
+      <c r="Q48">
+        <v>221.992021</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.1438084837090897</v>
+      </c>
+      <c r="T48">
+        <v>1.210736014960048</v>
+      </c>
+      <c r="U48">
+        <v>0.063</v>
+      </c>
+      <c r="V48">
+        <v>0.25</v>
+      </c>
+      <c r="W48">
+        <v>0.04725</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>3.679152542014741</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.09931589877013186</v>
+      </c>
+      <c r="C49">
+        <v>1856.364921187701</v>
+      </c>
+      <c r="D49">
+        <v>3065.822921187701</v>
+      </c>
+      <c r="E49">
+        <v>920.158</v>
+      </c>
+      <c r="F49">
+        <v>1565.758</v>
+      </c>
+      <c r="G49">
+        <v>356.3</v>
+      </c>
+      <c r="H49">
+        <v>2685.8</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>383.2</v>
+      </c>
+      <c r="K49">
+        <v>28</v>
+      </c>
+      <c r="L49">
+        <v>355.2</v>
+      </c>
+      <c r="M49">
+        <v>98.642754</v>
+      </c>
+      <c r="N49">
+        <v>256.557246</v>
+      </c>
+      <c r="O49">
+        <v>64.13931149999999</v>
+      </c>
+      <c r="P49">
+        <v>192.4179345</v>
+      </c>
+      <c r="Q49">
+        <v>220.4179345</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.1454875448493054</v>
+      </c>
+      <c r="T49">
+        <v>1.23009540119222</v>
+      </c>
+      <c r="U49">
+        <v>0.063</v>
+      </c>
+      <c r="V49">
+        <v>0.25</v>
+      </c>
+      <c r="W49">
+        <v>0.04725</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>3.600872700695279</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.09924021633735527</v>
+      </c>
+      <c r="C50">
+        <v>1825.722126216699</v>
+      </c>
+      <c r="D50">
+        <v>3068.494126216699</v>
+      </c>
+      <c r="E50">
+        <v>953.4719999999999</v>
+      </c>
+      <c r="F50">
+        <v>1599.072</v>
+      </c>
+      <c r="G50">
+        <v>356.3</v>
+      </c>
+      <c r="H50">
+        <v>2685.8</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>383.2</v>
+      </c>
+      <c r="K50">
+        <v>28</v>
+      </c>
+      <c r="L50">
+        <v>355.2</v>
+      </c>
+      <c r="M50">
+        <v>100.741536</v>
+      </c>
+      <c r="N50">
+        <v>254.458464</v>
+      </c>
+      <c r="O50">
+        <v>63.614616</v>
+      </c>
+      <c r="P50">
+        <v>190.843848</v>
+      </c>
+      <c r="Q50">
+        <v>218.843848</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.1472311852641447</v>
+      </c>
+      <c r="T50">
+        <v>1.250199379202553</v>
+      </c>
+      <c r="U50">
+        <v>0.063</v>
+      </c>
+      <c r="V50">
+        <v>0.25</v>
+      </c>
+      <c r="W50">
+        <v>0.04725</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>3.525854519430794</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.1017737839045787</v>
+      </c>
+      <c r="C51">
+        <v>1705.444659620304</v>
+      </c>
+      <c r="D51">
+        <v>2981.530659620304</v>
+      </c>
+      <c r="E51">
+        <v>986.7859999999999</v>
+      </c>
+      <c r="F51">
+        <v>1632.386</v>
+      </c>
+      <c r="G51">
+        <v>356.3</v>
+      </c>
+      <c r="H51">
+        <v>2685.8</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>383.2</v>
+      </c>
+      <c r="K51">
+        <v>28</v>
+      </c>
+      <c r="L51">
+        <v>355.2</v>
+      </c>
+      <c r="M51">
+        <v>114.4302586</v>
+      </c>
+      <c r="N51">
+        <v>240.7697414</v>
+      </c>
+      <c r="O51">
+        <v>60.19243535</v>
+      </c>
+      <c r="P51">
+        <v>180.57730605</v>
+      </c>
+      <c r="Q51">
+        <v>208.57730605</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.149043203734468</v>
+      </c>
+      <c r="T51">
+        <v>1.271091748507408</v>
+      </c>
+      <c r="U51">
+        <v>0.0701</v>
+      </c>
+      <c r="V51">
+        <v>0.25</v>
+      </c>
+      <c r="W51">
+        <v>0.052575</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>3.104074082726927</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.1017513514718021</v>
+      </c>
+      <c r="C52">
+        <v>1672.8790077936</v>
+      </c>
+      <c r="D52">
+        <v>2982.2790077936</v>
+      </c>
+      <c r="E52">
+        <v>1020.1</v>
+      </c>
+      <c r="F52">
+        <v>1665.7</v>
+      </c>
+      <c r="G52">
+        <v>356.3</v>
+      </c>
+      <c r="H52">
+        <v>2685.8</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>383.2</v>
+      </c>
+      <c r="K52">
+        <v>28</v>
+      </c>
+      <c r="L52">
+        <v>355.2</v>
+      </c>
+      <c r="M52">
+        <v>116.76557</v>
+      </c>
+      <c r="N52">
+        <v>238.43443</v>
+      </c>
+      <c r="O52">
+        <v>59.6086075</v>
+      </c>
+      <c r="P52">
+        <v>178.8258225</v>
+      </c>
+      <c r="Q52">
+        <v>206.8258225</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.1509277029436042</v>
+      </c>
+      <c r="T52">
+        <v>1.292819812584458</v>
+      </c>
+      <c r="U52">
+        <v>0.0701</v>
+      </c>
+      <c r="V52">
+        <v>0.25</v>
+      </c>
+      <c r="W52">
+        <v>0.052575</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>3.041992601072388</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.1098761690390255</v>
+      </c>
+      <c r="C53">
+        <v>1391.044720016232</v>
+      </c>
+      <c r="D53">
+        <v>2733.758720016232</v>
+      </c>
+      <c r="E53">
+        <v>1053.414</v>
+      </c>
+      <c r="F53">
+        <v>1699.014</v>
+      </c>
+      <c r="G53">
+        <v>356.3</v>
+      </c>
+      <c r="H53">
+        <v>2685.8</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>383.2</v>
+      </c>
+      <c r="K53">
+        <v>28</v>
+      </c>
+      <c r="L53">
+        <v>355.2</v>
+      </c>
+      <c r="M53">
+        <v>155.2898796</v>
+      </c>
+      <c r="N53">
+        <v>199.9101204</v>
+      </c>
+      <c r="O53">
+        <v>49.97753009999999</v>
+      </c>
+      <c r="P53">
+        <v>149.9325903</v>
+      </c>
+      <c r="Q53">
+        <v>177.9325903</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.1528891204878072</v>
+      </c>
+      <c r="T53">
+        <v>1.315434736419755</v>
+      </c>
+      <c r="U53">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V53">
+        <v>0.25</v>
+      </c>
+      <c r="W53">
+        <v>0.06855</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>2.287335149688659</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.1100134866062489</v>
+      </c>
+      <c r="C54">
+        <v>1353.885908891879</v>
+      </c>
+      <c r="D54">
+        <v>2729.913908891879</v>
+      </c>
+      <c r="E54">
+        <v>1086.728</v>
+      </c>
+      <c r="F54">
+        <v>1732.328</v>
+      </c>
+      <c r="G54">
+        <v>356.3</v>
+      </c>
+      <c r="H54">
+        <v>2685.8</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>383.2</v>
+      </c>
+      <c r="K54">
+        <v>28</v>
+      </c>
+      <c r="L54">
+        <v>355.2</v>
+      </c>
+      <c r="M54">
+        <v>158.3347792</v>
+      </c>
+      <c r="N54">
+        <v>196.8652207999999</v>
+      </c>
+      <c r="O54">
+        <v>49.21630519999999</v>
+      </c>
+      <c r="P54">
+        <v>147.6489156</v>
+      </c>
+      <c r="Q54">
+        <v>175.6489156</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.1549322637630186</v>
+      </c>
+      <c r="T54">
+        <v>1.338991948748189</v>
+      </c>
+      <c r="U54">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V54">
+        <v>0.25</v>
+      </c>
+      <c r="W54">
+        <v>0.06855</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>2.24334793527157</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.1101508041734724</v>
+      </c>
+      <c r="C55">
+        <v>1316.737897412115</v>
+      </c>
+      <c r="D55">
+        <v>2726.079897412115</v>
+      </c>
+      <c r="E55">
+        <v>1120.042</v>
+      </c>
+      <c r="F55">
+        <v>1765.642</v>
+      </c>
+      <c r="G55">
+        <v>356.3</v>
+      </c>
+      <c r="H55">
+        <v>2685.8</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>383.2</v>
+      </c>
+      <c r="K55">
+        <v>28</v>
+      </c>
+      <c r="L55">
+        <v>355.2</v>
+      </c>
+      <c r="M55">
+        <v>161.3796788</v>
+      </c>
+      <c r="N55">
+        <v>193.8203212</v>
+      </c>
+      <c r="O55">
+        <v>48.45508029999999</v>
+      </c>
+      <c r="P55">
+        <v>145.3652409</v>
+      </c>
+      <c r="Q55">
+        <v>173.3652409</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.1570623493052604</v>
+      </c>
+      <c r="T55">
+        <v>1.363551595643791</v>
+      </c>
+      <c r="U55">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V55">
+        <v>0.25</v>
+      </c>
+      <c r="W55">
+        <v>0.06855</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>2.201020615738144</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.1102881217406958</v>
+      </c>
+      <c r="C56">
+        <v>1279.600640138266</v>
+      </c>
+      <c r="D56">
+        <v>2722.256640138266</v>
+      </c>
+      <c r="E56">
+        <v>1153.356</v>
+      </c>
+      <c r="F56">
+        <v>1798.956</v>
+      </c>
+      <c r="G56">
+        <v>356.3</v>
+      </c>
+      <c r="H56">
+        <v>2685.8</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>383.2</v>
+      </c>
+      <c r="K56">
+        <v>28</v>
+      </c>
+      <c r="L56">
+        <v>355.2</v>
+      </c>
+      <c r="M56">
+        <v>164.4245784</v>
+      </c>
+      <c r="N56">
+        <v>190.7754216</v>
+      </c>
+      <c r="O56">
+        <v>47.69385539999999</v>
+      </c>
+      <c r="P56">
+        <v>143.0815662</v>
+      </c>
+      <c r="Q56">
+        <v>171.0815662</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.1592850472623822</v>
+      </c>
+      <c r="T56">
+        <v>1.389179053273983</v>
+      </c>
+      <c r="U56">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V56">
+        <v>0.25</v>
+      </c>
+      <c r="W56">
+        <v>0.06855</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>2.160260974705956</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.1104254393079192</v>
+      </c>
+      <c r="C57">
+        <v>1242.474091886206</v>
+      </c>
+      <c r="D57">
+        <v>2718.444091886206</v>
+      </c>
+      <c r="E57">
+        <v>1186.67</v>
+      </c>
+      <c r="F57">
+        <v>1832.27</v>
+      </c>
+      <c r="G57">
+        <v>356.3</v>
+      </c>
+      <c r="H57">
+        <v>2685.8</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>383.2</v>
+      </c>
+      <c r="K57">
+        <v>28</v>
+      </c>
+      <c r="L57">
+        <v>355.2</v>
+      </c>
+      <c r="M57">
+        <v>167.469478</v>
+      </c>
+      <c r="N57">
+        <v>187.730522</v>
+      </c>
+      <c r="O57">
+        <v>46.93263049999999</v>
+      </c>
+      <c r="P57">
+        <v>140.7978915</v>
+      </c>
+      <c r="Q57">
+        <v>168.7978915</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.1616065317953761</v>
+      </c>
+      <c r="T57">
+        <v>1.415945509021074</v>
+      </c>
+      <c r="U57">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V57">
+        <v>0.25</v>
+      </c>
+      <c r="W57">
+        <v>0.06855</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>2.120983502438575</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.1105627568751426</v>
+      </c>
+      <c r="C58">
+        <v>1205.358207724578</v>
+      </c>
+      <c r="D58">
+        <v>2714.642207724578</v>
+      </c>
+      <c r="E58">
+        <v>1219.984</v>
+      </c>
+      <c r="F58">
+        <v>1865.584</v>
+      </c>
+      <c r="G58">
+        <v>356.3</v>
+      </c>
+      <c r="H58">
+        <v>2685.8</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>383.2</v>
+      </c>
+      <c r="K58">
+        <v>28</v>
+      </c>
+      <c r="L58">
+        <v>355.2</v>
+      </c>
+      <c r="M58">
+        <v>170.5143776</v>
+      </c>
+      <c r="N58">
+        <v>184.6856223999999</v>
+      </c>
+      <c r="O58">
+        <v>46.17140559999999</v>
+      </c>
+      <c r="P58">
+        <v>138.5142168</v>
+      </c>
+      <c r="Q58">
+        <v>166.5142168</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.1640335383525969</v>
+      </c>
+      <c r="T58">
+        <v>1.443928621847577</v>
+      </c>
+      <c r="U58">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V58">
+        <v>0.25</v>
+      </c>
+      <c r="W58">
+        <v>0.06855</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>2.083108797037887</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.1107000744423661</v>
+      </c>
+      <c r="C59">
+        <v>1168.252942973029</v>
+      </c>
+      <c r="D59">
+        <v>2710.850942973029</v>
+      </c>
+      <c r="E59">
+        <v>1253.298</v>
+      </c>
+      <c r="F59">
+        <v>1898.898</v>
+      </c>
+      <c r="G59">
+        <v>356.3</v>
+      </c>
+      <c r="H59">
+        <v>2685.8</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>383.2</v>
+      </c>
+      <c r="K59">
+        <v>28</v>
+      </c>
+      <c r="L59">
+        <v>355.2</v>
+      </c>
+      <c r="M59">
+        <v>173.5592772000001</v>
+      </c>
+      <c r="N59">
+        <v>181.6407227999999</v>
+      </c>
+      <c r="O59">
+        <v>45.41018069999998</v>
+      </c>
+      <c r="P59">
+        <v>136.2305421</v>
+      </c>
+      <c r="Q59">
+        <v>164.2305421</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.166573428935735</v>
+      </c>
+      <c r="T59">
+        <v>1.473213274805546</v>
+      </c>
+      <c r="U59">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V59">
+        <v>0.25</v>
+      </c>
+      <c r="W59">
+        <v>0.06855</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>2.046563028668801</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.1108373920095895</v>
+      </c>
+      <c r="C60">
+        <v>1131.158253200462</v>
+      </c>
+      <c r="D60">
+        <v>2707.070253200462</v>
+      </c>
+      <c r="E60">
+        <v>1286.612</v>
+      </c>
+      <c r="F60">
+        <v>1932.212</v>
+      </c>
+      <c r="G60">
+        <v>356.3</v>
+      </c>
+      <c r="H60">
+        <v>2685.8</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>383.2</v>
+      </c>
+      <c r="K60">
+        <v>28</v>
+      </c>
+      <c r="L60">
+        <v>355.2</v>
+      </c>
+      <c r="M60">
+        <v>176.6041768</v>
+      </c>
+      <c r="N60">
+        <v>178.5958232</v>
+      </c>
+      <c r="O60">
+        <v>44.6489558</v>
+      </c>
+      <c r="P60">
+        <v>133.9468674</v>
+      </c>
+      <c r="Q60">
+        <v>161.9468674</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.1692342666894988</v>
+      </c>
+      <c r="T60">
+        <v>1.503892435047227</v>
+      </c>
+      <c r="U60">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V60">
+        <v>0.25</v>
+      </c>
+      <c r="W60">
+        <v>0.06855</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>2.011277459208994</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.1203114595768129</v>
+      </c>
+      <c r="C61">
+        <v>860.2277113864834</v>
+      </c>
+      <c r="D61">
+        <v>2469.453711386483</v>
+      </c>
+      <c r="E61">
+        <v>1319.926</v>
+      </c>
+      <c r="F61">
+        <v>1965.526</v>
+      </c>
+      <c r="G61">
+        <v>356.3</v>
+      </c>
+      <c r="H61">
+        <v>2685.8</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>383.2</v>
+      </c>
+      <c r="K61">
+        <v>28</v>
+      </c>
+      <c r="L61">
+        <v>355.2</v>
+      </c>
+      <c r="M61">
+        <v>221.121675</v>
+      </c>
+      <c r="N61">
+        <v>134.078325</v>
+      </c>
+      <c r="O61">
+        <v>33.51958125</v>
+      </c>
+      <c r="P61">
+        <v>100.55874375</v>
+      </c>
+      <c r="Q61">
+        <v>128.55874375</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.1720249014068607</v>
+      </c>
+      <c r="T61">
+        <v>1.536068139690942</v>
+      </c>
+      <c r="U61">
+        <v>0.1125</v>
+      </c>
+      <c r="V61">
+        <v>0.25</v>
+      </c>
+      <c r="W61">
+        <v>0.08437500000000001</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>1.606355414954233</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.1206070271440363</v>
+      </c>
+      <c r="C62">
+        <v>820.1698181624599</v>
+      </c>
+      <c r="D62">
+        <v>2462.70981816246</v>
+      </c>
+      <c r="E62">
+        <v>1353.24</v>
+      </c>
+      <c r="F62">
+        <v>1998.84</v>
+      </c>
+      <c r="G62">
+        <v>356.3</v>
+      </c>
+      <c r="H62">
+        <v>2685.8</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>383.2</v>
+      </c>
+      <c r="K62">
+        <v>28</v>
+      </c>
+      <c r="L62">
+        <v>355.2</v>
+      </c>
+      <c r="M62">
+        <v>224.8695</v>
+      </c>
+      <c r="N62">
+        <v>130.3305</v>
+      </c>
+      <c r="O62">
+        <v>32.582625</v>
+      </c>
+      <c r="P62">
+        <v>97.74787499999999</v>
+      </c>
+      <c r="Q62">
+        <v>125.747875</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.1749550678600908</v>
+      </c>
+      <c r="T62">
+        <v>1.569852629566842</v>
+      </c>
+      <c r="U62">
+        <v>0.1125</v>
+      </c>
+      <c r="V62">
+        <v>0.25</v>
+      </c>
+      <c r="W62">
+        <v>0.08437500000000001</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>1.579582824704996</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.1209025947112597</v>
+      </c>
+      <c r="C63">
+        <v>780.1486587562326</v>
+      </c>
+      <c r="D63">
+        <v>2456.002658756232</v>
+      </c>
+      <c r="E63">
+        <v>1386.554</v>
+      </c>
+      <c r="F63">
+        <v>2032.154</v>
+      </c>
+      <c r="G63">
+        <v>356.3</v>
+      </c>
+      <c r="H63">
+        <v>2685.8</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>383.2</v>
+      </c>
+      <c r="K63">
+        <v>28</v>
+      </c>
+      <c r="L63">
+        <v>355.2</v>
+      </c>
+      <c r="M63">
+        <v>228.617325</v>
+      </c>
+      <c r="N63">
+        <v>126.582675</v>
+      </c>
+      <c r="O63">
+        <v>31.64566875</v>
+      </c>
+      <c r="P63">
+        <v>94.93700625</v>
+      </c>
+      <c r="Q63">
+        <v>122.93700625</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.1780354992596404</v>
+      </c>
+      <c r="T63">
+        <v>1.605369657385097</v>
+      </c>
+      <c r="U63">
+        <v>0.1125</v>
+      </c>
+      <c r="V63">
+        <v>0.25</v>
+      </c>
+      <c r="W63">
+        <v>0.08437500000000001</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>1.553688024299996</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.1211981622784832</v>
+      </c>
+      <c r="C64">
+        <v>740.1639338507066</v>
+      </c>
+      <c r="D64">
+        <v>2449.331933850706</v>
+      </c>
+      <c r="E64">
+        <v>1419.868</v>
+      </c>
+      <c r="F64">
+        <v>2065.468</v>
+      </c>
+      <c r="G64">
+        <v>356.3</v>
+      </c>
+      <c r="H64">
+        <v>2685.8</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>383.2</v>
+      </c>
+      <c r="K64">
+        <v>28</v>
+      </c>
+      <c r="L64">
+        <v>355.2</v>
+      </c>
+      <c r="M64">
+        <v>232.36515</v>
+      </c>
+      <c r="N64">
+        <v>122.83485</v>
+      </c>
+      <c r="O64">
+        <v>30.7087125</v>
+      </c>
+      <c r="P64">
+        <v>92.1261375</v>
+      </c>
+      <c r="Q64">
+        <v>120.1261375</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.1812780586275873</v>
+      </c>
+      <c r="T64">
+        <v>1.642756002456943</v>
+      </c>
+      <c r="U64">
+        <v>0.1125</v>
+      </c>
+      <c r="V64">
+        <v>0.25</v>
+      </c>
+      <c r="W64">
+        <v>0.08437500000000001</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>1.528628540037092</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.1214937298457066</v>
+      </c>
+      <c r="C65">
+        <v>700.2153473718672</v>
+      </c>
+      <c r="D65">
+        <v>2442.697347371867</v>
+      </c>
+      <c r="E65">
+        <v>1453.182</v>
+      </c>
+      <c r="F65">
+        <v>2098.782</v>
+      </c>
+      <c r="G65">
+        <v>356.3</v>
+      </c>
+      <c r="H65">
+        <v>2685.8</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>383.2</v>
+      </c>
+      <c r="K65">
+        <v>28</v>
+      </c>
+      <c r="L65">
+        <v>355.2</v>
+      </c>
+      <c r="M65">
+        <v>236.112975</v>
+      </c>
+      <c r="N65">
+        <v>119.087025</v>
+      </c>
+      <c r="O65">
+        <v>29.77175624999999</v>
+      </c>
+      <c r="P65">
+        <v>89.31526874999997</v>
+      </c>
+      <c r="Q65">
+        <v>117.31526875</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.1846958914748827</v>
+      </c>
+      <c r="T65">
+        <v>1.682163231046187</v>
+      </c>
+      <c r="U65">
+        <v>0.1125</v>
+      </c>
+      <c r="V65">
+        <v>0.25</v>
+      </c>
+      <c r="W65">
+        <v>0.08437500000000001</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>1.504364594957138</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.1685223584039322</v>
+      </c>
+      <c r="C66">
+        <v>-68.80320060674376</v>
+      </c>
+      <c r="D66">
+        <v>1706.992799393256</v>
+      </c>
+      <c r="E66">
+        <v>1486.496</v>
+      </c>
+      <c r="F66">
+        <v>2132.096</v>
+      </c>
+      <c r="G66">
+        <v>356.3</v>
+      </c>
+      <c r="H66">
+        <v>2685.8</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>383.2</v>
+      </c>
+      <c r="K66">
+        <v>28</v>
+      </c>
+      <c r="L66">
+        <v>355.2</v>
+      </c>
+      <c r="M66">
+        <v>419.1700736</v>
+      </c>
+      <c r="N66">
+        <v>-63.97007359999998</v>
+      </c>
+      <c r="O66">
+        <v>-15.99251839999999</v>
+      </c>
+      <c r="P66">
+        <v>-47.97755519999998</v>
+      </c>
+      <c r="Q66">
+        <v>-19.97755519999998</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.1926494960300805</v>
+      </c>
+      <c r="T66">
+        <v>1.773867397639107</v>
+      </c>
+      <c r="U66">
+        <v>0.1966</v>
+      </c>
+      <c r="V66">
+        <v>0.2118471846936737</v>
+      </c>
+      <c r="W66">
+        <v>0.1549508434892237</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>0.8473887387746949</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.1701003584039322</v>
+      </c>
+      <c r="C67">
+        <v>-119.1954444991873</v>
+      </c>
+      <c r="D67">
+        <v>1689.914555500813</v>
+      </c>
+      <c r="E67">
+        <v>1519.81</v>
+      </c>
+      <c r="F67">
+        <v>2165.41</v>
+      </c>
+      <c r="G67">
+        <v>356.3</v>
+      </c>
+      <c r="H67">
+        <v>2685.8</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>383.2</v>
+      </c>
+      <c r="K67">
+        <v>28</v>
+      </c>
+      <c r="L67">
+        <v>355.2</v>
+      </c>
+      <c r="M67">
+        <v>425.7196060000001</v>
+      </c>
+      <c r="N67">
+        <v>-70.51960600000007</v>
+      </c>
+      <c r="O67">
+        <v>-17.62990150000002</v>
+      </c>
+      <c r="P67">
+        <v>-52.88970450000005</v>
+      </c>
+      <c r="Q67">
+        <v>-24.88970450000005</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.1970451959166542</v>
+      </c>
+      <c r="T67">
+        <v>1.824549323285939</v>
+      </c>
+      <c r="U67">
+        <v>0.1966</v>
+      </c>
+      <c r="V67">
+        <v>0.2085879972368479</v>
+      </c>
+      <c r="W67">
+        <v>0.1555915997432357</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>0.8343519889473917</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.1716783584039322</v>
+      </c>
+      <c r="C68">
+        <v>-169.2493422247644</v>
+      </c>
+      <c r="D68">
+        <v>1673.174657775236</v>
+      </c>
+      <c r="E68">
+        <v>1553.124</v>
+      </c>
+      <c r="F68">
+        <v>2198.724</v>
+      </c>
+      <c r="G68">
+        <v>356.3</v>
+      </c>
+      <c r="H68">
+        <v>2685.8</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>383.2</v>
+      </c>
+      <c r="K68">
+        <v>28</v>
+      </c>
+      <c r="L68">
+        <v>355.2</v>
+      </c>
+      <c r="M68">
+        <v>432.2691384</v>
+      </c>
+      <c r="N68">
+        <v>-77.06913840000004</v>
+      </c>
+      <c r="O68">
+        <v>-19.26728460000001</v>
+      </c>
+      <c r="P68">
+        <v>-57.80185380000003</v>
+      </c>
+      <c r="Q68">
+        <v>-29.80185380000003</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.2016994663847911</v>
+      </c>
+      <c r="T68">
+        <v>1.878212538676701</v>
+      </c>
+      <c r="U68">
+        <v>0.1966</v>
+      </c>
+      <c r="V68">
+        <v>0.2054275730362896</v>
+      </c>
+      <c r="W68">
+        <v>0.1562129391410655</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>0.8217102921451586</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.1732563584039322</v>
+      </c>
+      <c r="C69">
+        <v>-218.9748498941915</v>
+      </c>
+      <c r="D69">
+        <v>1656.763150105809</v>
+      </c>
+      <c r="E69">
+        <v>1586.438</v>
+      </c>
+      <c r="F69">
+        <v>2232.038</v>
+      </c>
+      <c r="G69">
+        <v>356.3</v>
+      </c>
+      <c r="H69">
+        <v>2685.8</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>383.2</v>
+      </c>
+      <c r="K69">
+        <v>28</v>
+      </c>
+      <c r="L69">
+        <v>355.2</v>
+      </c>
+      <c r="M69">
+        <v>438.8186708</v>
+      </c>
+      <c r="N69">
+        <v>-83.61867080000002</v>
+      </c>
+      <c r="O69">
+        <v>-20.9046677</v>
+      </c>
+      <c r="P69">
+        <v>-62.71400310000001</v>
+      </c>
+      <c r="Q69">
+        <v>-34.71400310000001</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.2066358138509969</v>
+      </c>
+      <c r="T69">
+        <v>1.935128070151753</v>
+      </c>
+      <c r="U69">
+        <v>0.1966</v>
+      </c>
+      <c r="V69">
+        <v>0.2023614898566435</v>
+      </c>
+      <c r="W69">
+        <v>0.1568157310941839</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>0.8094459594265742</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.1872292314539069</v>
+      </c>
+      <c r="C70">
+        <v>-384.6850275620272</v>
+      </c>
+      <c r="D70">
+        <v>1524.366972437973</v>
+      </c>
+      <c r="E70">
+        <v>1619.752</v>
+      </c>
+      <c r="F70">
+        <v>2265.352</v>
+      </c>
+      <c r="G70">
+        <v>356.3</v>
+      </c>
+      <c r="H70">
+        <v>2685.8</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>383.2</v>
+      </c>
+      <c r="K70">
+        <v>28</v>
+      </c>
+      <c r="L70">
+        <v>355.2</v>
+      </c>
+      <c r="M70">
+        <v>484.3322576</v>
+      </c>
+      <c r="N70">
+        <v>-129.1322576000001</v>
+      </c>
+      <c r="O70">
+        <v>-32.28306440000001</v>
+      </c>
+      <c r="P70">
+        <v>-96.84919320000004</v>
+      </c>
+      <c r="Q70">
+        <v>-68.84919320000004</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.2140646613150116</v>
+      </c>
+      <c r="T70">
+        <v>2.020781846462291</v>
+      </c>
+      <c r="U70">
+        <v>0.2138</v>
+      </c>
+      <c r="V70">
+        <v>0.1833452110747867</v>
+      </c>
+      <c r="W70">
+        <v>0.1746007938722106</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>0.733380844299147</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.1889792314539069</v>
+      </c>
+      <c r="C71">
+        <v>-433.104415179836</v>
+      </c>
+      <c r="D71">
+        <v>1509.261584820164</v>
+      </c>
+      <c r="E71">
+        <v>1653.066</v>
+      </c>
+      <c r="F71">
+        <v>2298.666</v>
+      </c>
+      <c r="G71">
+        <v>356.3</v>
+      </c>
+      <c r="H71">
+        <v>2685.8</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>383.2</v>
+      </c>
+      <c r="K71">
+        <v>28</v>
+      </c>
+      <c r="L71">
+        <v>355.2</v>
+      </c>
+      <c r="M71">
+        <v>491.4547908</v>
+      </c>
+      <c r="N71">
+        <v>-136.2547908</v>
+      </c>
+      <c r="O71">
+        <v>-34.06369770000001</v>
+      </c>
+      <c r="P71">
+        <v>-102.1910931</v>
+      </c>
+      <c r="Q71">
+        <v>-74.19109310000002</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.2197183600671087</v>
+      </c>
+      <c r="T71">
+        <v>2.085968357638494</v>
+      </c>
+      <c r="U71">
+        <v>0.2138</v>
+      </c>
+      <c r="V71">
+        <v>0.1806880341026884</v>
+      </c>
+      <c r="W71">
+        <v>0.1751688983088452</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>0.7227521364107536</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.1907292314539069</v>
+      </c>
+      <c r="C72">
+        <v>-481.2273730064983</v>
+      </c>
+      <c r="D72">
+        <v>1494.452626993502</v>
+      </c>
+      <c r="E72">
+        <v>1686.380000000001</v>
+      </c>
+      <c r="F72">
+        <v>2331.98</v>
+      </c>
+      <c r="G72">
+        <v>356.3</v>
+      </c>
+      <c r="H72">
+        <v>2685.8</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>383.2</v>
+      </c>
+      <c r="K72">
+        <v>28</v>
+      </c>
+      <c r="L72">
+        <v>355.2</v>
+      </c>
+      <c r="M72">
+        <v>498.5773240000001</v>
+      </c>
+      <c r="N72">
+        <v>-143.3773240000001</v>
+      </c>
+      <c r="O72">
+        <v>-35.84433100000003</v>
+      </c>
+      <c r="P72">
+        <v>-107.5329930000001</v>
+      </c>
+      <c r="Q72">
+        <v>-79.53299300000008</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.2257489720693457</v>
+      </c>
+      <c r="T72">
+        <v>2.155500636226444</v>
+      </c>
+      <c r="U72">
+        <v>0.2138</v>
+      </c>
+      <c r="V72">
+        <v>0.17810677647265</v>
+      </c>
+      <c r="W72">
+        <v>0.1757207711901474</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>0.7124271058905999</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.1924792314539069</v>
+      </c>
+      <c r="C73">
+        <v>-529.0625420126614</v>
+      </c>
+      <c r="D73">
+        <v>1479.931457987338</v>
+      </c>
+      <c r="E73">
+        <v>1719.694</v>
+      </c>
+      <c r="F73">
+        <v>2365.294</v>
+      </c>
+      <c r="G73">
+        <v>356.3</v>
+      </c>
+      <c r="H73">
+        <v>2685.8</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>383.2</v>
+      </c>
+      <c r="K73">
+        <v>28</v>
+      </c>
+      <c r="L73">
+        <v>355.2</v>
+      </c>
+      <c r="M73">
+        <v>505.6998571999999</v>
+      </c>
+      <c r="N73">
+        <v>-150.4998572</v>
+      </c>
+      <c r="O73">
+        <v>-37.62496429999999</v>
+      </c>
+      <c r="P73">
+        <v>-112.8748929</v>
+      </c>
+      <c r="Q73">
+        <v>-84.87489289999996</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.2321954883475989</v>
+      </c>
+      <c r="T73">
+        <v>2.229828244372183</v>
+      </c>
+      <c r="U73">
+        <v>0.2138</v>
+      </c>
+      <c r="V73">
+        <v>0.1755982303251479</v>
+      </c>
+      <c r="W73">
+        <v>0.1762570983564834</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>0.7023929213005917</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.1942292314539069</v>
+      </c>
+      <c r="C74">
+        <v>-576.6182305535388</v>
+      </c>
+      <c r="D74">
+        <v>1465.689769446461</v>
+      </c>
+      <c r="E74">
+        <v>1753.008</v>
+      </c>
+      <c r="F74">
+        <v>2398.608</v>
+      </c>
+      <c r="G74">
+        <v>356.3</v>
+      </c>
+      <c r="H74">
+        <v>2685.8</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>383.2</v>
+      </c>
+      <c r="K74">
+        <v>28</v>
+      </c>
+      <c r="L74">
+        <v>355.2</v>
+      </c>
+      <c r="M74">
+        <v>512.8223904</v>
+      </c>
+      <c r="N74">
+        <v>-157.6223904</v>
+      </c>
+      <c r="O74">
+        <v>-39.40559760000001</v>
+      </c>
+      <c r="P74">
+        <v>-118.2167928</v>
+      </c>
+      <c r="Q74">
+        <v>-90.21679280000002</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.2391024700742989</v>
+      </c>
+      <c r="T74">
+        <v>2.309464967385475</v>
+      </c>
+      <c r="U74">
+        <v>0.2138</v>
+      </c>
+      <c r="V74">
+        <v>0.1731593660150764</v>
+      </c>
+      <c r="W74">
+        <v>0.1767785275459766</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>0.6926374640603055</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.1959792314539069</v>
+      </c>
+      <c r="C75">
+        <v>-623.9024302204973</v>
+      </c>
+      <c r="D75">
+        <v>1451.719569779503</v>
+      </c>
+      <c r="E75">
+        <v>1786.322</v>
+      </c>
+      <c r="F75">
+        <v>2431.922</v>
+      </c>
+      <c r="G75">
+        <v>356.3</v>
+      </c>
+      <c r="H75">
+        <v>2685.8</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>383.2</v>
+      </c>
+      <c r="K75">
+        <v>28</v>
+      </c>
+      <c r="L75">
+        <v>355.2</v>
+      </c>
+      <c r="M75">
+        <v>519.9449235999999</v>
+      </c>
+      <c r="N75">
+        <v>-164.7449235999999</v>
+      </c>
+      <c r="O75">
+        <v>-41.18623089999998</v>
+      </c>
+      <c r="P75">
+        <v>-123.5586927</v>
+      </c>
+      <c r="Q75">
+        <v>-95.55869269999995</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.2465210800770507</v>
+      </c>
+      <c r="T75">
+        <v>2.395000706918271</v>
+      </c>
+      <c r="U75">
+        <v>0.2138</v>
+      </c>
+      <c r="V75">
+        <v>0.1707873199052808</v>
+      </c>
+      <c r="W75">
+        <v>0.1772856710042509</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>0.6831492796211234</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.1977292314539069</v>
+      </c>
+      <c r="C76">
+        <v>-670.9228307946798</v>
+      </c>
+      <c r="D76">
+        <v>1438.01316920532</v>
+      </c>
+      <c r="E76">
+        <v>1819.636</v>
+      </c>
+      <c r="F76">
+        <v>2465.236</v>
+      </c>
+      <c r="G76">
+        <v>356.3</v>
+      </c>
+      <c r="H76">
+        <v>2685.8</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>383.2</v>
+      </c>
+      <c r="K76">
+        <v>28</v>
+      </c>
+      <c r="L76">
+        <v>355.2</v>
+      </c>
+      <c r="M76">
+        <v>527.0674567999999</v>
+      </c>
+      <c r="N76">
+        <v>-171.8674568</v>
+      </c>
+      <c r="O76">
+        <v>-42.96686419999999</v>
+      </c>
+      <c r="P76">
+        <v>-128.9005926</v>
+      </c>
+      <c r="Q76">
+        <v>-100.9005926</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.2545103523877065</v>
+      </c>
+      <c r="T76">
+        <v>2.487116118722819</v>
+      </c>
+      <c r="U76">
+        <v>0.2138</v>
+      </c>
+      <c r="V76">
+        <v>0.1684793831498041</v>
+      </c>
+      <c r="W76">
+        <v>0.1777791078825719</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>0.6739175325992163</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.1994792314539069</v>
+      </c>
+      <c r="C77">
+        <v>-717.6868343614387</v>
+      </c>
+      <c r="D77">
+        <v>1424.563165638561</v>
+      </c>
+      <c r="E77">
+        <v>1852.95</v>
+      </c>
+      <c r="F77">
+        <v>2498.55</v>
+      </c>
+      <c r="G77">
+        <v>356.3</v>
+      </c>
+      <c r="H77">
+        <v>2685.8</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>383.2</v>
+      </c>
+      <c r="K77">
+        <v>28</v>
+      </c>
+      <c r="L77">
+        <v>355.2</v>
+      </c>
+      <c r="M77">
+        <v>534.18999</v>
+      </c>
+      <c r="N77">
+        <v>-178.98999</v>
+      </c>
+      <c r="O77">
+        <v>-44.74749749999999</v>
+      </c>
+      <c r="P77">
+        <v>-134.2424925</v>
+      </c>
+      <c r="Q77">
+        <v>-106.2424925</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.2631387664832148</v>
+      </c>
+      <c r="T77">
+        <v>2.586600763471732</v>
+      </c>
+      <c r="U77">
+        <v>0.2138</v>
+      </c>
+      <c r="V77">
+        <v>0.1662329913744733</v>
+      </c>
+      <c r="W77">
+        <v>0.1782593864441376</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>0.6649319654978934</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.2012292314539069</v>
+      </c>
+      <c r="C78">
+        <v>-764.2015686400202</v>
+      </c>
+      <c r="D78">
+        <v>1411.36243135998</v>
+      </c>
+      <c r="E78">
+        <v>1886.264</v>
+      </c>
+      <c r="F78">
+        <v>2531.864</v>
+      </c>
+      <c r="G78">
+        <v>356.3</v>
+      </c>
+      <c r="H78">
+        <v>2685.8</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>383.2</v>
+      </c>
+      <c r="K78">
+        <v>28</v>
+      </c>
+      <c r="L78">
+        <v>355.2</v>
+      </c>
+      <c r="M78">
+        <v>541.3125232</v>
+      </c>
+      <c r="N78">
+        <v>-186.1125232</v>
+      </c>
+      <c r="O78">
+        <v>-46.5281308</v>
+      </c>
+      <c r="P78">
+        <v>-139.5843924</v>
+      </c>
+      <c r="Q78">
+        <v>-111.5843924</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.272486215086682</v>
+      </c>
+      <c r="T78">
+        <v>2.694375795283054</v>
+      </c>
+      <c r="U78">
+        <v>0.2138</v>
+      </c>
+      <c r="V78">
+        <v>0.1640457151721776</v>
+      </c>
+      <c r="W78">
+        <v>0.1787270260961884</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>0.6561828606887106</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.2029792314539069</v>
+      </c>
+      <c r="C79">
+        <v>-810.4738995789392</v>
+      </c>
+      <c r="D79">
+        <v>1398.404100421061</v>
+      </c>
+      <c r="E79">
+        <v>1919.578</v>
+      </c>
+      <c r="F79">
+        <v>2565.178</v>
+      </c>
+      <c r="G79">
+        <v>356.3</v>
+      </c>
+      <c r="H79">
+        <v>2685.8</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>383.2</v>
+      </c>
+      <c r="K79">
+        <v>28</v>
+      </c>
+      <c r="L79">
+        <v>355.2</v>
+      </c>
+      <c r="M79">
+        <v>548.4350564</v>
+      </c>
+      <c r="N79">
+        <v>-193.2350564</v>
+      </c>
+      <c r="O79">
+        <v>-48.3087641</v>
+      </c>
+      <c r="P79">
+        <v>-144.9262923</v>
+      </c>
+      <c r="Q79">
+        <v>-116.9262923</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.2826464853078422</v>
+      </c>
+      <c r="T79">
+        <v>2.811522568991014</v>
+      </c>
+      <c r="U79">
+        <v>0.2138</v>
+      </c>
+      <c r="V79">
+        <v>0.1619152513387727</v>
+      </c>
+      <c r="W79">
+        <v>0.1791825192637704</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>0.6476610053550909</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.2047292314539069</v>
+      </c>
+      <c r="C80">
+        <v>-856.5104432637961</v>
+      </c>
+      <c r="D80">
+        <v>1385.681556736204</v>
+      </c>
+      <c r="E80">
+        <v>1952.892</v>
+      </c>
+      <c r="F80">
+        <v>2598.492</v>
+      </c>
+      <c r="G80">
+        <v>356.3</v>
+      </c>
+      <c r="H80">
+        <v>2685.8</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>383.2</v>
+      </c>
+      <c r="K80">
+        <v>28</v>
+      </c>
+      <c r="L80">
+        <v>355.2</v>
+      </c>
+      <c r="M80">
+        <v>555.5575896</v>
+      </c>
+      <c r="N80">
+        <v>-200.3575896</v>
+      </c>
+      <c r="O80">
+        <v>-50.08939740000001</v>
+      </c>
+      <c r="P80">
+        <v>-150.2681922</v>
+      </c>
+      <c r="Q80">
+        <v>-122.2681922</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.2937304164581986</v>
+      </c>
+      <c r="T80">
+        <v>2.939319049399697</v>
+      </c>
+      <c r="U80">
+        <v>0.2138</v>
+      </c>
+      <c r="V80">
+        <v>0.1598394147831474</v>
+      </c>
+      <c r="W80">
+        <v>0.1796263331193631</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>0.6393576591325898</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.2064792314539069</v>
+      </c>
+      <c r="C81">
+        <v>-902.3175771809481</v>
+      </c>
+      <c r="D81">
+        <v>1373.188422819052</v>
+      </c>
+      <c r="E81">
+        <v>1986.206</v>
+      </c>
+      <c r="F81">
+        <v>2631.806</v>
+      </c>
+      <c r="G81">
+        <v>356.3</v>
+      </c>
+      <c r="H81">
+        <v>2685.8</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>383.2</v>
+      </c>
+      <c r="K81">
+        <v>28</v>
+      </c>
+      <c r="L81">
+        <v>355.2</v>
+      </c>
+      <c r="M81">
+        <v>562.6801227999999</v>
+      </c>
+      <c r="N81">
+        <v>-207.4801227999999</v>
+      </c>
+      <c r="O81">
+        <v>-51.87003069999999</v>
+      </c>
+      <c r="P81">
+        <v>-155.6100921</v>
+      </c>
+      <c r="Q81">
+        <v>-127.6100921</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.3058699600990653</v>
+      </c>
+      <c r="T81">
+        <v>3.079286623180635</v>
+      </c>
+      <c r="U81">
+        <v>0.2138</v>
+      </c>
+      <c r="V81">
+        <v>0.1578161310517152</v>
+      </c>
+      <c r="W81">
+        <v>0.1800589111811433</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>0.6312645242068609</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.2082292314539069</v>
+      </c>
+      <c r="C82">
+        <v>-947.9014508773066</v>
+      </c>
+      <c r="D82">
+        <v>1360.918549122694</v>
+      </c>
+      <c r="E82">
+        <v>2019.52</v>
+      </c>
+      <c r="F82">
+        <v>2665.12</v>
+      </c>
+      <c r="G82">
+        <v>356.3</v>
+      </c>
+      <c r="H82">
+        <v>2685.8</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>383.2</v>
+      </c>
+      <c r="K82">
+        <v>28</v>
+      </c>
+      <c r="L82">
+        <v>355.2</v>
+      </c>
+      <c r="M82">
+        <v>569.8026560000001</v>
+      </c>
+      <c r="N82">
+        <v>-214.6026560000001</v>
+      </c>
+      <c r="O82">
+        <v>-53.65066400000002</v>
+      </c>
+      <c r="P82">
+        <v>-160.9519920000001</v>
+      </c>
+      <c r="Q82">
+        <v>-132.9519920000001</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.3192234581040185</v>
+      </c>
+      <c r="T82">
+        <v>3.233250954339666</v>
+      </c>
+      <c r="U82">
+        <v>0.2138</v>
+      </c>
+      <c r="V82">
+        <v>0.1558434294135687</v>
+      </c>
+      <c r="W82">
+        <v>0.180480674791379</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>0.6233737176542749</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.2099792314539069</v>
+      </c>
+      <c r="C83">
+        <v>-993.2679960537043</v>
+      </c>
+      <c r="D83">
+        <v>1348.866003946296</v>
+      </c>
+      <c r="E83">
+        <v>2052.834</v>
+      </c>
+      <c r="F83">
+        <v>2698.434</v>
+      </c>
+      <c r="G83">
+        <v>356.3</v>
+      </c>
+      <c r="H83">
+        <v>2685.8</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>383.2</v>
+      </c>
+      <c r="K83">
+        <v>28</v>
+      </c>
+      <c r="L83">
+        <v>355.2</v>
+      </c>
+      <c r="M83">
+        <v>576.9251892</v>
+      </c>
+      <c r="N83">
+        <v>-221.7251892</v>
+      </c>
+      <c r="O83">
+        <v>-55.4312973</v>
+      </c>
+      <c r="P83">
+        <v>-166.2938919</v>
+      </c>
+      <c r="Q83">
+        <v>-138.2938919</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.3339825874779143</v>
+      </c>
+      <c r="T83">
+        <v>3.403422057199649</v>
+      </c>
+      <c r="U83">
+        <v>0.2138</v>
+      </c>
+      <c r="V83">
+        <v>0.1539194364578457</v>
+      </c>
+      <c r="W83">
+        <v>0.1808920244853126</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>0.6156777458313827</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.2117292314539069</v>
+      </c>
+      <c r="C84">
+        <v>-1038.422936126641</v>
+      </c>
+      <c r="D84">
+        <v>1337.02506387336</v>
+      </c>
+      <c r="E84">
+        <v>2086.148000000001</v>
+      </c>
+      <c r="F84">
+        <v>2731.748000000001</v>
+      </c>
+      <c r="G84">
+        <v>356.3</v>
+      </c>
+      <c r="H84">
+        <v>2685.8</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>383.2</v>
+      </c>
+      <c r="K84">
+        <v>28</v>
+      </c>
+      <c r="L84">
+        <v>355.2</v>
+      </c>
+      <c r="M84">
+        <v>584.0477224000001</v>
+      </c>
+      <c r="N84">
+        <v>-228.8477224000001</v>
+      </c>
+      <c r="O84">
+        <v>-57.21193060000003</v>
+      </c>
+      <c r="P84">
+        <v>-171.6357918000001</v>
+      </c>
+      <c r="Q84">
+        <v>-143.6357918000001</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.3503816201155761</v>
+      </c>
+      <c r="T84">
+        <v>3.592501060377407</v>
+      </c>
+      <c r="U84">
+        <v>0.2138</v>
+      </c>
+      <c r="V84">
+        <v>0.1520423701595792</v>
+      </c>
+      <c r="W84">
+        <v>0.1812933412598819</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>0.6081694806383169</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.2134792314539069</v>
+      </c>
+      <c r="C85">
+        <v>-1083.371795290786</v>
+      </c>
+      <c r="D85">
+        <v>1325.390204709214</v>
+      </c>
+      <c r="E85">
+        <v>2119.462</v>
+      </c>
+      <c r="F85">
+        <v>2765.062</v>
+      </c>
+      <c r="G85">
+        <v>356.3</v>
+      </c>
+      <c r="H85">
+        <v>2685.8</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>383.2</v>
+      </c>
+      <c r="K85">
+        <v>28</v>
+      </c>
+      <c r="L85">
+        <v>355.2</v>
+      </c>
+      <c r="M85">
+        <v>591.1702556</v>
+      </c>
+      <c r="N85">
+        <v>-235.9702556</v>
+      </c>
+      <c r="O85">
+        <v>-58.99256390000001</v>
+      </c>
+      <c r="P85">
+        <v>-176.9776917</v>
+      </c>
+      <c r="Q85">
+        <v>-148.9776917</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.3687099507106101</v>
+      </c>
+      <c r="T85">
+        <v>3.803824652164314</v>
+      </c>
+      <c r="U85">
+        <v>0.2138</v>
+      </c>
+      <c r="V85">
+        <v>0.1502105343745241</v>
+      </c>
+      <c r="W85">
+        <v>0.1816849877507267</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>0.6008421374980963</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.2152292314539069</v>
+      </c>
+      <c r="C86">
+        <v>-1128.119907112392</v>
+      </c>
+      <c r="D86">
+        <v>1313.956092887608</v>
+      </c>
+      <c r="E86">
+        <v>2152.776</v>
+      </c>
+      <c r="F86">
+        <v>2798.376</v>
+      </c>
+      <c r="G86">
+        <v>356.3</v>
+      </c>
+      <c r="H86">
+        <v>2685.8</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>383.2</v>
+      </c>
+      <c r="K86">
+        <v>28</v>
+      </c>
+      <c r="L86">
+        <v>355.2</v>
+      </c>
+      <c r="M86">
+        <v>598.2927887999999</v>
+      </c>
+      <c r="N86">
+        <v>-243.0927887999999</v>
+      </c>
+      <c r="O86">
+        <v>-60.77319719999998</v>
+      </c>
+      <c r="P86">
+        <v>-182.3195916</v>
+      </c>
+      <c r="Q86">
+        <v>-154.3195916</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.389329322630023</v>
+      </c>
+      <c r="T86">
+        <v>4.041563692924581</v>
+      </c>
+      <c r="U86">
+        <v>0.2138</v>
+      </c>
+      <c r="V86">
+        <v>0.1484223137272083</v>
+      </c>
+      <c r="W86">
+        <v>0.1820673093251228</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>0.5936892549088334</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.2169792314539069</v>
+      </c>
+      <c r="C87">
+        <v>-1172.672422681698</v>
+      </c>
+      <c r="D87">
+        <v>1302.717577318303</v>
+      </c>
+      <c r="E87">
+        <v>2186.09</v>
+      </c>
+      <c r="F87">
+        <v>2831.69</v>
+      </c>
+      <c r="G87">
+        <v>356.3</v>
+      </c>
+      <c r="H87">
+        <v>2685.8</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>383.2</v>
+      </c>
+      <c r="K87">
+        <v>28</v>
+      </c>
+      <c r="L87">
+        <v>355.2</v>
+      </c>
+      <c r="M87">
+        <v>605.4153219999999</v>
+      </c>
+      <c r="N87">
+        <v>-250.215322</v>
+      </c>
+      <c r="O87">
+        <v>-62.55383049999999</v>
+      </c>
+      <c r="P87">
+        <v>-187.6614915</v>
+      </c>
+      <c r="Q87">
+        <v>-159.6614915</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.4126979441386912</v>
+      </c>
+      <c r="T87">
+        <v>4.311001272452887</v>
+      </c>
+      <c r="U87">
+        <v>0.2138</v>
+      </c>
+      <c r="V87">
+        <v>0.1466761688598294</v>
+      </c>
+      <c r="W87">
+        <v>0.1824406350977684</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>0.5867046754393177</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.2187292314539069</v>
+      </c>
+      <c r="C88">
+        <v>-1217.034318350506</v>
+      </c>
+      <c r="D88">
+        <v>1291.669681649494</v>
+      </c>
+      <c r="E88">
+        <v>2219.404</v>
+      </c>
+      <c r="F88">
+        <v>2865.004</v>
+      </c>
+      <c r="G88">
+        <v>356.3</v>
+      </c>
+      <c r="H88">
+        <v>2685.8</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>383.2</v>
+      </c>
+      <c r="K88">
+        <v>28</v>
+      </c>
+      <c r="L88">
+        <v>355.2</v>
+      </c>
+      <c r="M88">
+        <v>612.5378552</v>
+      </c>
+      <c r="N88">
+        <v>-257.3378552</v>
+      </c>
+      <c r="O88">
+        <v>-64.33446379999999</v>
+      </c>
+      <c r="P88">
+        <v>-193.0033914</v>
+      </c>
+      <c r="Q88">
+        <v>-165.0033914</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.4394049401485978</v>
+      </c>
+      <c r="T88">
+        <v>4.618929934770951</v>
+      </c>
+      <c r="U88">
+        <v>0.2138</v>
+      </c>
+      <c r="V88">
+        <v>0.1449706320126221</v>
+      </c>
+      <c r="W88">
+        <v>0.1828052788757014</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>0.5798825280504885</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.2204792314539069</v>
+      </c>
+      <c r="C89">
+        <v>-1261.210403079359</v>
+      </c>
+      <c r="D89">
+        <v>1280.807596920642</v>
+      </c>
+      <c r="E89">
+        <v>2252.718</v>
+      </c>
+      <c r="F89">
+        <v>2898.318</v>
+      </c>
+      <c r="G89">
+        <v>356.3</v>
+      </c>
+      <c r="H89">
+        <v>2685.8</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>383.2</v>
+      </c>
+      <c r="K89">
+        <v>28</v>
+      </c>
+      <c r="L89">
+        <v>355.2</v>
+      </c>
+      <c r="M89">
+        <v>619.6603884</v>
+      </c>
+      <c r="N89">
+        <v>-264.4603884</v>
+      </c>
+      <c r="O89">
+        <v>-66.1150971</v>
+      </c>
+      <c r="P89">
+        <v>-198.3452913</v>
+      </c>
+      <c r="Q89">
+        <v>-170.3452913</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.4702207047754129</v>
+      </c>
+      <c r="T89">
+        <v>4.974232237445639</v>
+      </c>
+      <c r="U89">
+        <v>0.2138</v>
+      </c>
+      <c r="V89">
+        <v>0.1433043029090287</v>
+      </c>
+      <c r="W89">
+        <v>0.1831615400380497</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>0.5732172116361149</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.2222292314539069</v>
+      </c>
+      <c r="C90">
+        <v>-1305.205325417086</v>
+      </c>
+      <c r="D90">
+        <v>1270.126674582915</v>
+      </c>
+      <c r="E90">
+        <v>2286.032</v>
+      </c>
+      <c r="F90">
+        <v>2931.632</v>
+      </c>
+      <c r="G90">
+        <v>356.3</v>
+      </c>
+      <c r="H90">
+        <v>2685.8</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>383.2</v>
+      </c>
+      <c r="K90">
+        <v>28</v>
+      </c>
+      <c r="L90">
+        <v>355.2</v>
+      </c>
+      <c r="M90">
+        <v>626.7829216</v>
+      </c>
+      <c r="N90">
+        <v>-271.5829216</v>
+      </c>
+      <c r="O90">
+        <v>-67.89573040000001</v>
+      </c>
+      <c r="P90">
+        <v>-203.6871912</v>
+      </c>
+      <c r="Q90">
+        <v>-175.6871912</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>0.5061724301733641</v>
+      </c>
+      <c r="T90">
+        <v>5.38875159056611</v>
+      </c>
+      <c r="U90">
+        <v>0.2138</v>
+      </c>
+      <c r="V90">
+        <v>0.1416758449214261</v>
+      </c>
+      <c r="W90">
+        <v>0.1835097043557991</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>0.5667033796857046</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.2239792314539069</v>
+      </c>
+      <c r="C91">
+        <v>-1349.023580134027</v>
+      </c>
+      <c r="D91">
+        <v>1259.622419865973</v>
+      </c>
+      <c r="E91">
+        <v>2319.346</v>
+      </c>
+      <c r="F91">
+        <v>2964.946</v>
+      </c>
+      <c r="G91">
+        <v>356.3</v>
+      </c>
+      <c r="H91">
+        <v>2685.8</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>383.2</v>
+      </c>
+      <c r="K91">
+        <v>28</v>
+      </c>
+      <c r="L91">
+        <v>355.2</v>
+      </c>
+      <c r="M91">
+        <v>633.9054547999999</v>
+      </c>
+      <c r="N91">
+        <v>-278.7054547999999</v>
+      </c>
+      <c r="O91">
+        <v>-69.67636369999998</v>
+      </c>
+      <c r="P91">
+        <v>-209.0290911</v>
+      </c>
+      <c r="Q91">
+        <v>-181.0290911</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>0.5486608329163973</v>
+      </c>
+      <c r="T91">
+        <v>5.878638098799393</v>
+      </c>
+      <c r="U91">
+        <v>0.2138</v>
+      </c>
+      <c r="V91">
+        <v>0.1400839814953427</v>
+      </c>
+      <c r="W91">
+        <v>0.1838500447562957</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>0.5603359259813709</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.2257292314539069</v>
+      </c>
+      <c r="C92">
+        <v>-1392.6695145288</v>
+      </c>
+      <c r="D92">
+        <v>1249.2904854712</v>
+      </c>
+      <c r="E92">
+        <v>2352.66</v>
+      </c>
+      <c r="F92">
+        <v>2998.26</v>
+      </c>
+      <c r="G92">
+        <v>356.3</v>
+      </c>
+      <c r="H92">
+        <v>2685.8</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>383.2</v>
+      </c>
+      <c r="K92">
+        <v>28</v>
+      </c>
+      <c r="L92">
+        <v>355.2</v>
+      </c>
+      <c r="M92">
+        <v>641.0279880000001</v>
+      </c>
+      <c r="N92">
+        <v>-285.8279880000001</v>
+      </c>
+      <c r="O92">
+        <v>-71.45699700000002</v>
+      </c>
+      <c r="P92">
+        <v>-214.3709910000001</v>
+      </c>
+      <c r="Q92">
+        <v>-186.3709910000001</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>0.5996469162080369</v>
+      </c>
+      <c r="T92">
+        <v>6.466501908679332</v>
+      </c>
+      <c r="U92">
+        <v>0.2138</v>
+      </c>
+      <c r="V92">
+        <v>0.1385274928120611</v>
+      </c>
+      <c r="W92">
+        <v>0.1841828220367813</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>0.5541099712482445</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.2274792314539069</v>
+      </c>
+      <c r="C93">
+        <v>-1436.147334427205</v>
+      </c>
+      <c r="D93">
+        <v>1239.126665572795</v>
+      </c>
+      <c r="E93">
+        <v>2385.974</v>
+      </c>
+      <c r="F93">
+        <v>3031.574</v>
+      </c>
+      <c r="G93">
+        <v>356.3</v>
+      </c>
+      <c r="H93">
+        <v>2685.8</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>383.2</v>
+      </c>
+      <c r="K93">
+        <v>28</v>
+      </c>
+      <c r="L93">
+        <v>355.2</v>
+      </c>
+      <c r="M93">
+        <v>648.1505212</v>
+      </c>
+      <c r="N93">
+        <v>-292.9505212</v>
+      </c>
+      <c r="O93">
+        <v>-73.23763029999999</v>
+      </c>
+      <c r="P93">
+        <v>-219.7128909</v>
+      </c>
+      <c r="Q93">
+        <v>-191.7128909</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>0.6619632402311522</v>
+      </c>
+      <c r="T93">
+        <v>7.185002120754814</v>
+      </c>
+      <c r="U93">
+        <v>0.2138</v>
+      </c>
+      <c r="V93">
+        <v>0.1370052126712692</v>
+      </c>
+      <c r="W93">
+        <v>0.1845082855308826</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>0.548020850685077</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.2292292314539069</v>
+      </c>
+      <c r="C94">
+        <v>-1479.461109890673</v>
+      </c>
+      <c r="D94">
+        <v>1229.126890109327</v>
+      </c>
+      <c r="E94">
+        <v>2419.288</v>
+      </c>
+      <c r="F94">
+        <v>3064.888</v>
+      </c>
+      <c r="G94">
+        <v>356.3</v>
+      </c>
+      <c r="H94">
+        <v>2685.8</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>383.2</v>
+      </c>
+      <c r="K94">
+        <v>28</v>
+      </c>
+      <c r="L94">
+        <v>355.2</v>
+      </c>
+      <c r="M94">
+        <v>655.2730544000001</v>
+      </c>
+      <c r="N94">
+        <v>-300.0730544000001</v>
+      </c>
+      <c r="O94">
+        <v>-75.01826360000003</v>
+      </c>
+      <c r="P94">
+        <v>-225.0547908000001</v>
+      </c>
+      <c r="Q94">
+        <v>-197.0547908000001</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>0.7398586452600466</v>
+      </c>
+      <c r="T94">
+        <v>8.083127385849169</v>
+      </c>
+      <c r="U94">
+        <v>0.2138</v>
+      </c>
+      <c r="V94">
+        <v>0.1355160255770163</v>
+      </c>
+      <c r="W94">
+        <v>0.1848266737316339</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>0.5420641023080651</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.2309792314539069</v>
+      </c>
+      <c r="C95">
+        <v>-1522.61478065051</v>
+      </c>
+      <c r="D95">
+        <v>1219.28721934949</v>
+      </c>
+      <c r="E95">
+        <v>2452.602</v>
+      </c>
+      <c r="F95">
+        <v>3098.202</v>
+      </c>
+      <c r="G95">
+        <v>356.3</v>
+      </c>
+      <c r="H95">
+        <v>2685.8</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>383.2</v>
+      </c>
+      <c r="K95">
+        <v>28</v>
+      </c>
+      <c r="L95">
+        <v>355.2</v>
+      </c>
+      <c r="M95">
+        <v>662.3955876</v>
+      </c>
+      <c r="N95">
+        <v>-307.1955876</v>
+      </c>
+      <c r="O95">
+        <v>-76.7988969</v>
+      </c>
+      <c r="P95">
+        <v>-230.3966907</v>
+      </c>
+      <c r="Q95">
+        <v>-202.3966907</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>0.8400098802971963</v>
+      </c>
+      <c r="T95">
+        <v>9.237859869541909</v>
+      </c>
+      <c r="U95">
+        <v>0.2138</v>
+      </c>
+      <c r="V95">
+        <v>0.1340588640116721</v>
+      </c>
+      <c r="W95">
+        <v>0.1851382148743045</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>0.5362354560466882</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.2327292314539069</v>
+      </c>
+      <c r="C96">
+        <v>-1565.612161283203</v>
+      </c>
+      <c r="D96">
+        <v>1209.603838716797</v>
+      </c>
+      <c r="E96">
+        <v>2485.916</v>
+      </c>
+      <c r="F96">
+        <v>3131.516</v>
+      </c>
+      <c r="G96">
+        <v>356.3</v>
+      </c>
+      <c r="H96">
+        <v>2685.8</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>383.2</v>
+      </c>
+      <c r="K96">
+        <v>28</v>
+      </c>
+      <c r="L96">
+        <v>355.2</v>
+      </c>
+      <c r="M96">
+        <v>669.5181208</v>
+      </c>
+      <c r="N96">
+        <v>-314.3181208</v>
+      </c>
+      <c r="O96">
+        <v>-78.57953020000001</v>
+      </c>
+      <c r="P96">
+        <v>-235.7385906</v>
+      </c>
+      <c r="Q96">
+        <v>-207.7385906</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>0.9735448603467289</v>
+      </c>
+      <c r="T96">
+        <v>10.77750318113223</v>
+      </c>
+      <c r="U96">
+        <v>0.2138</v>
+      </c>
+      <c r="V96">
+        <v>0.1326327058838883</v>
+      </c>
+      <c r="W96">
+        <v>0.1854431274820247</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>0.5305308235355533</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.2344792314539069</v>
+      </c>
+      <c r="C97">
+        <v>-1608.456946141062</v>
+      </c>
+      <c r="D97">
+        <v>1200.073053858939</v>
+      </c>
+      <c r="E97">
+        <v>2519.23</v>
+      </c>
+      <c r="F97">
+        <v>3164.83</v>
+      </c>
+      <c r="G97">
+        <v>356.3</v>
+      </c>
+      <c r="H97">
+        <v>2685.8</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>383.2</v>
+      </c>
+      <c r="K97">
+        <v>28</v>
+      </c>
+      <c r="L97">
+        <v>355.2</v>
+      </c>
+      <c r="M97">
+        <v>676.640654</v>
+      </c>
+      <c r="N97">
+        <v>-321.4406540000001</v>
+      </c>
+      <c r="O97">
+        <v>-80.36016350000001</v>
+      </c>
+      <c r="P97">
+        <v>-241.0804905000001</v>
+      </c>
+      <c r="Q97">
+        <v>-213.0804905000001</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>1.160493832416076</v>
+      </c>
+      <c r="T97">
+        <v>12.93300381735868</v>
+      </c>
+      <c r="U97">
+        <v>0.2138</v>
+      </c>
+      <c r="V97">
+        <v>0.1312365721377421</v>
+      </c>
+      <c r="W97">
+        <v>0.1857416208769507</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>0.5249462885509684</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.2362292314539069</v>
+      </c>
+      <c r="C98">
+        <v>-1651.152714051568</v>
+      </c>
+      <c r="D98">
+        <v>1190.691285948432</v>
+      </c>
+      <c r="E98">
+        <v>2552.544</v>
+      </c>
+      <c r="F98">
+        <v>3198.144</v>
+      </c>
+      <c r="G98">
+        <v>356.3</v>
+      </c>
+      <c r="H98">
+        <v>2685.8</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>383.2</v>
+      </c>
+      <c r="K98">
+        <v>28</v>
+      </c>
+      <c r="L98">
+        <v>355.2</v>
+      </c>
+      <c r="M98">
+        <v>683.7631871999999</v>
+      </c>
+      <c r="N98">
+        <v>-328.5631872</v>
+      </c>
+      <c r="O98">
+        <v>-82.14079679999999</v>
+      </c>
+      <c r="P98">
+        <v>-246.4223904</v>
+      </c>
+      <c r="Q98">
+        <v>-218.4223904</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>1.440917290520091</v>
+      </c>
+      <c r="T98">
+        <v>16.16625477169831</v>
+      </c>
+      <c r="U98">
+        <v>0.2138</v>
+      </c>
+      <c r="V98">
+        <v>0.1298695245113073</v>
+      </c>
+      <c r="W98">
+        <v>0.1860338956594825</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>0.5194780980452292</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.2379792314539069</v>
+      </c>
+      <c r="C99">
+        <v>-1693.702932798036</v>
+      </c>
+      <c r="D99">
+        <v>1181.455067201964</v>
+      </c>
+      <c r="E99">
+        <v>2585.858</v>
+      </c>
+      <c r="F99">
+        <v>3231.458</v>
+      </c>
+      <c r="G99">
+        <v>356.3</v>
+      </c>
+      <c r="H99">
+        <v>2685.8</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>383.2</v>
+      </c>
+      <c r="K99">
+        <v>28</v>
+      </c>
+      <c r="L99">
+        <v>355.2</v>
+      </c>
+      <c r="M99">
+        <v>690.8857204</v>
+      </c>
+      <c r="N99">
+        <v>-335.6857204</v>
+      </c>
+      <c r="O99">
+        <v>-83.92143009999999</v>
+      </c>
+      <c r="P99">
+        <v>-251.7642903</v>
+      </c>
+      <c r="Q99">
+        <v>-223.7642903</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>1.908289720693455</v>
+      </c>
+      <c r="T99">
+        <v>21.55500636226442</v>
+      </c>
+      <c r="U99">
+        <v>0.2138</v>
+      </c>
+      <c r="V99">
+        <v>0.1285306634338712</v>
+      </c>
+      <c r="W99">
+        <v>0.1863201441578383</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>0.5141226537354846</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.2397292314539069</v>
+      </c>
+      <c r="C100">
+        <v>-1736.110963393304</v>
+      </c>
+      <c r="D100">
+        <v>1172.361036606696</v>
+      </c>
+      <c r="E100">
+        <v>2619.172</v>
+      </c>
+      <c r="F100">
+        <v>3264.772</v>
+      </c>
+      <c r="G100">
+        <v>356.3</v>
+      </c>
+      <c r="H100">
+        <v>2685.8</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>383.2</v>
+      </c>
+      <c r="K100">
+        <v>28</v>
+      </c>
+      <c r="L100">
+        <v>355.2</v>
+      </c>
+      <c r="M100">
+        <v>698.0082536</v>
+      </c>
+      <c r="N100">
+        <v>-342.8082536</v>
+      </c>
+      <c r="O100">
+        <v>-85.7020634</v>
+      </c>
+      <c r="P100">
+        <v>-257.1061902</v>
+      </c>
+      <c r="Q100">
+        <v>-229.1061902</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>2.843034581040182</v>
+      </c>
+      <c r="T100">
+        <v>32.33250954339663</v>
+      </c>
+      <c r="U100">
+        <v>0.2138</v>
+      </c>
+      <c r="V100">
+        <v>0.1272191260518929</v>
+      </c>
+      <c r="W100">
+        <v>0.1866005508501053</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>0.5088765042075715</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.2414792314539069</v>
+      </c>
+      <c r="C101">
+        <v>-1778.380064157589</v>
+      </c>
+      <c r="D101">
+        <v>1163.405935842411</v>
+      </c>
+      <c r="E101">
+        <v>2652.486</v>
+      </c>
+      <c r="F101">
+        <v>3298.086</v>
+      </c>
+      <c r="G101">
+        <v>356.3</v>
+      </c>
+      <c r="H101">
+        <v>2685.8</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>383.2</v>
+      </c>
+      <c r="K101">
+        <v>28</v>
+      </c>
+      <c r="L101">
+        <v>355.2</v>
+      </c>
+      <c r="M101">
+        <v>705.1307868</v>
+      </c>
+      <c r="N101">
+        <v>-349.9307868</v>
+      </c>
+      <c r="O101">
+        <v>-87.48269670000001</v>
+      </c>
+      <c r="P101">
+        <v>-262.4480901</v>
+      </c>
+      <c r="Q101">
+        <v>-234.4480901</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>5.647269162080364</v>
+      </c>
+      <c r="T101">
+        <v>64.66501908679325</v>
+      </c>
+      <c r="U101">
+        <v>0.2138</v>
+      </c>
+      <c r="V101">
+        <v>0.125934084374601</v>
+      </c>
+      <c r="W101">
+        <v>0.1868752927607103</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>0.5037363374984041</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/spain/spain_diversified.xlsx
+++ b/research/traditional_assets/database/data/spain/spain_diversified.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.09287321867617701</v>
+        <v>0.09267478562948656</v>
       </c>
       <c r="C2">
-        <v>5752.069617271156</v>
+        <v>5717.03790531555</v>
       </c>
       <c r="D2">
-        <v>5376.069617271156</v>
+        <v>5398.82790531555</v>
       </c>
       <c r="E2">
-        <v>-578.2</v>
+        <v>-520.4100000000001</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>57.79</v>
       </c>
       <c r="G2">
         <v>376</v>
@@ -1451,28 +1451,28 @@
         <v>103.443</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>2.906837</v>
       </c>
       <c r="N2">
-        <v>103.443</v>
+        <v>100.536163</v>
       </c>
       <c r="O2">
-        <v>25.86075</v>
+        <v>25.13404075</v>
       </c>
       <c r="P2">
-        <v>77.58225</v>
+        <v>75.40212225000001</v>
       </c>
       <c r="Q2">
-        <v>78.43925</v>
+        <v>76.25912225</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.09287321867617701</v>
+        <v>0.09322983396917835</v>
       </c>
       <c r="T2">
-        <v>0.7282077218429368</v>
+        <v>0.7337244470084135</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>35.58610269512877</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.09267478562948656</v>
+        <v>0.09247635258279613</v>
       </c>
       <c r="C3">
-        <v>5717.03790531555</v>
+        <v>5682.199695901774</v>
       </c>
       <c r="D3">
-        <v>5398.82790531555</v>
+        <v>5421.779695901774</v>
       </c>
       <c r="E3">
-        <v>-520.4100000000001</v>
+        <v>-462.6200000000001</v>
       </c>
       <c r="F3">
-        <v>57.79</v>
+        <v>115.58</v>
       </c>
       <c r="G3">
         <v>376</v>
@@ -1533,28 +1533,28 @@
         <v>103.443</v>
       </c>
       <c r="M3">
-        <v>2.906837</v>
+        <v>5.813674</v>
       </c>
       <c r="N3">
-        <v>100.536163</v>
+        <v>97.62932599999999</v>
       </c>
       <c r="O3">
-        <v>25.13404075</v>
+        <v>24.4073315</v>
       </c>
       <c r="P3">
-        <v>75.40212225000001</v>
+        <v>73.22199449999999</v>
       </c>
       <c r="Q3">
-        <v>76.25912225</v>
+        <v>74.07899449999999</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.09322983396917835</v>
+        <v>0.09359372712530217</v>
       </c>
       <c r="T3">
-        <v>0.7337244470084135</v>
+        <v>0.7393537584017573</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>35.58610269512877</v>
+        <v>17.79305134756438</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.09247635258279613</v>
+        <v>0.09227791953610567</v>
       </c>
       <c r="C4">
-        <v>5682.199695901774</v>
+        <v>5647.557467451799</v>
       </c>
       <c r="D4">
-        <v>5421.779695901774</v>
+        <v>5444.927467451799</v>
       </c>
       <c r="E4">
-        <v>-462.6200000000001</v>
+        <v>-404.83</v>
       </c>
       <c r="F4">
-        <v>115.58</v>
+        <v>173.37</v>
       </c>
       <c r="G4">
         <v>376</v>
@@ -1615,28 +1615,28 @@
         <v>103.443</v>
       </c>
       <c r="M4">
-        <v>5.813674</v>
+        <v>8.720511</v>
       </c>
       <c r="N4">
-        <v>97.62932599999999</v>
+        <v>94.722489</v>
       </c>
       <c r="O4">
-        <v>24.4073315</v>
+        <v>23.68062225</v>
       </c>
       <c r="P4">
-        <v>73.22199449999999</v>
+        <v>71.04186675</v>
       </c>
       <c r="Q4">
-        <v>74.07899449999999</v>
+        <v>71.89886675</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.09359372712530217</v>
+        <v>0.09396512323309864</v>
       </c>
       <c r="T4">
-        <v>0.7393537584017573</v>
+        <v>0.7450991380712523</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>17.79305134756438</v>
+        <v>11.86203423170959</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.09227791953610567</v>
+        <v>0.09207948648941523</v>
       </c>
       <c r="C5">
-        <v>5647.557467451799</v>
+        <v>5613.113740894613</v>
       </c>
       <c r="D5">
-        <v>5444.927467451799</v>
+        <v>5468.273740894613</v>
       </c>
       <c r="E5">
-        <v>-404.83</v>
+        <v>-347.0400000000001</v>
       </c>
       <c r="F5">
-        <v>173.37</v>
+        <v>231.16</v>
       </c>
       <c r="G5">
         <v>376</v>
@@ -1697,28 +1697,28 @@
         <v>103.443</v>
       </c>
       <c r="M5">
-        <v>8.720511</v>
+        <v>11.627348</v>
       </c>
       <c r="N5">
-        <v>94.722489</v>
+        <v>91.815652</v>
       </c>
       <c r="O5">
-        <v>23.68062225</v>
+        <v>22.953913</v>
       </c>
       <c r="P5">
-        <v>71.04186675</v>
+        <v>68.861739</v>
       </c>
       <c r="Q5">
-        <v>71.89886675</v>
+        <v>69.718739</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.09396512323309864</v>
+        <v>0.09434425675980754</v>
       </c>
       <c r="T5">
-        <v>0.7450991380712523</v>
+        <v>0.7509642131505285</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>11.86203423170959</v>
+        <v>8.89652567378219</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.09207948648941523</v>
+        <v>0.0919373034427248</v>
       </c>
       <c r="C6">
-        <v>5613.113740894613</v>
+        <v>5572.175523781815</v>
       </c>
       <c r="D6">
-        <v>5468.273740894613</v>
+        <v>5485.125523781815</v>
       </c>
       <c r="E6">
-        <v>-347.0400000000001</v>
+        <v>-289.2500000000001</v>
       </c>
       <c r="F6">
-        <v>231.16</v>
+        <v>288.95</v>
       </c>
       <c r="G6">
         <v>376</v>
@@ -1779,45 +1779,45 @@
         <v>103.443</v>
       </c>
       <c r="M6">
-        <v>11.627348</v>
+        <v>14.96761</v>
       </c>
       <c r="N6">
-        <v>91.815652</v>
+        <v>88.47539</v>
       </c>
       <c r="O6">
-        <v>22.953913</v>
+        <v>22.1188475</v>
       </c>
       <c r="P6">
-        <v>68.861739</v>
+        <v>66.3565425</v>
       </c>
       <c r="Q6">
-        <v>69.718739</v>
+        <v>67.2135425</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.09434425675980754</v>
+        <v>0.09473137204497348</v>
       </c>
       <c r="T6">
-        <v>0.7509642131505285</v>
+        <v>0.7569527634946317</v>
       </c>
       <c r="U6">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V6">
         <v>0.25</v>
       </c>
       <c r="W6">
-        <v>0.03772499999999999</v>
+        <v>0.03885</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y6">
-        <v>8.89652567378219</v>
+        <v>6.911123419169795</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.0919373034427248</v>
+        <v>0.09186262039603435</v>
       </c>
       <c r="C7">
-        <v>5572.175523781815</v>
+        <v>5523.278762639559</v>
       </c>
       <c r="D7">
-        <v>5485.125523781815</v>
+        <v>5494.018762639559</v>
       </c>
       <c r="E7">
-        <v>-289.2500000000001</v>
+        <v>-231.46</v>
       </c>
       <c r="F7">
-        <v>288.95</v>
+        <v>346.74</v>
       </c>
       <c r="G7">
         <v>376</v>
@@ -1861,45 +1861,45 @@
         <v>103.443</v>
       </c>
       <c r="M7">
-        <v>14.96761</v>
+        <v>18.827982</v>
       </c>
       <c r="N7">
-        <v>88.47539</v>
+        <v>84.61501799999999</v>
       </c>
       <c r="O7">
-        <v>22.1188475</v>
+        <v>21.1537545</v>
       </c>
       <c r="P7">
-        <v>66.3565425</v>
+        <v>63.46126349999999</v>
       </c>
       <c r="Q7">
-        <v>67.2135425</v>
+        <v>64.3182635</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.09473137204497348</v>
+        <v>0.09512672382556846</v>
       </c>
       <c r="T7">
-        <v>0.7569527634946317</v>
+        <v>0.7630687298035029</v>
       </c>
       <c r="U7">
-        <v>0.0518</v>
+        <v>0.0543</v>
       </c>
       <c r="V7">
         <v>0.25</v>
       </c>
       <c r="W7">
-        <v>0.03885</v>
+        <v>0.040725</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y7">
-        <v>6.911123419169795</v>
+        <v>5.494109777670277</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.09186262039603435</v>
+        <v>0.09169418734934391</v>
       </c>
       <c r="C8">
-        <v>5523.278762639559</v>
+        <v>5485.651976593473</v>
       </c>
       <c r="D8">
-        <v>5494.018762639559</v>
+        <v>5514.181976593472</v>
       </c>
       <c r="E8">
-        <v>-231.46</v>
+        <v>-173.6700000000001</v>
       </c>
       <c r="F8">
-        <v>346.74</v>
+        <v>404.53</v>
       </c>
       <c r="G8">
         <v>376</v>
@@ -1943,28 +1943,28 @@
         <v>103.443</v>
       </c>
       <c r="M8">
-        <v>18.827982</v>
+        <v>21.965979</v>
       </c>
       <c r="N8">
-        <v>84.61501799999999</v>
+        <v>81.47702100000001</v>
       </c>
       <c r="O8">
-        <v>21.1537545</v>
+        <v>20.36925525</v>
       </c>
       <c r="P8">
-        <v>63.46126349999999</v>
+        <v>61.10776575000001</v>
       </c>
       <c r="Q8">
-        <v>64.3182635</v>
+        <v>61.96476575000001</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.09512672382556846</v>
+        <v>0.09553057779499345</v>
       </c>
       <c r="T8">
-        <v>0.7630687298035029</v>
+        <v>0.7693162222695542</v>
       </c>
       <c r="U8">
         <v>0.0543</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>5.494109777670277</v>
+        <v>4.70923695228881</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.0916941873493439</v>
+        <v>0.09158575430265348</v>
       </c>
       <c r="C9">
-        <v>5485.651976593475</v>
+        <v>5440.921050552923</v>
       </c>
       <c r="D9">
-        <v>5514.181976593474</v>
+        <v>5527.241050552922</v>
       </c>
       <c r="E9">
-        <v>-173.67</v>
+        <v>-115.8800000000001</v>
       </c>
       <c r="F9">
-        <v>404.53</v>
+        <v>462.32</v>
       </c>
       <c r="G9">
         <v>376</v>
@@ -2025,45 +2025,45 @@
         <v>103.443</v>
       </c>
       <c r="M9">
-        <v>21.965979</v>
+        <v>25.566296</v>
       </c>
       <c r="N9">
-        <v>81.47702099999999</v>
+        <v>77.87670399999999</v>
       </c>
       <c r="O9">
-        <v>20.36925525</v>
+        <v>19.469176</v>
       </c>
       <c r="P9">
-        <v>61.10776575</v>
+        <v>58.40752799999999</v>
       </c>
       <c r="Q9">
-        <v>61.96476575</v>
+        <v>59.26452799999999</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.09553057779499345</v>
+        <v>0.09594321119853638</v>
       </c>
       <c r="T9">
-        <v>0.7693162222695542</v>
+        <v>0.7756995297892153</v>
       </c>
       <c r="U9">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V9">
         <v>0.25</v>
       </c>
       <c r="W9">
-        <v>0.040725</v>
+        <v>0.041475</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y9">
-        <v>4.709236952288809</v>
+        <v>4.046069090336745</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.09158575430265348</v>
+        <v>0.09142482125596302</v>
       </c>
       <c r="C10">
-        <v>5440.921050552923</v>
+        <v>5402.627362375553</v>
       </c>
       <c r="D10">
-        <v>5527.241050552922</v>
+        <v>5546.737362375553</v>
       </c>
       <c r="E10">
-        <v>-115.8800000000001</v>
+        <v>-58.09000000000003</v>
       </c>
       <c r="F10">
-        <v>462.32</v>
+        <v>520.11</v>
       </c>
       <c r="G10">
         <v>376</v>
@@ -2107,28 +2107,28 @@
         <v>103.443</v>
       </c>
       <c r="M10">
-        <v>25.566296</v>
+        <v>28.762083</v>
       </c>
       <c r="N10">
-        <v>77.87670399999999</v>
+        <v>74.68091699999999</v>
       </c>
       <c r="O10">
-        <v>19.469176</v>
+        <v>18.67022925</v>
       </c>
       <c r="P10">
-        <v>58.40752799999999</v>
+        <v>56.01068775</v>
       </c>
       <c r="Q10">
-        <v>59.26452799999999</v>
+        <v>56.86768774999999</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.09594321119853638</v>
+        <v>0.09636491346809123</v>
       </c>
       <c r="T10">
-        <v>0.7756995297892153</v>
+        <v>0.7822231297818359</v>
       </c>
       <c r="U10">
         <v>0.0553</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>4.046069090336745</v>
+        <v>3.596505858077108</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.09142482125596302</v>
+        <v>0.09126388820927257</v>
       </c>
       <c r="C11">
-        <v>5402.627362375553</v>
+        <v>5364.471700266097</v>
       </c>
       <c r="D11">
-        <v>5546.737362375553</v>
+        <v>5566.371700266097</v>
       </c>
       <c r="E11">
-        <v>-58.09000000000003</v>
+        <v>-0.3000000000000682</v>
       </c>
       <c r="F11">
-        <v>520.11</v>
+        <v>577.9</v>
       </c>
       <c r="G11">
         <v>376</v>
@@ -2189,28 +2189,28 @@
         <v>103.443</v>
       </c>
       <c r="M11">
-        <v>28.762083</v>
+        <v>31.95787</v>
       </c>
       <c r="N11">
-        <v>74.68091699999999</v>
+        <v>71.48513</v>
       </c>
       <c r="O11">
-        <v>18.67022925</v>
+        <v>17.8712825</v>
       </c>
       <c r="P11">
-        <v>56.01068775</v>
+        <v>53.6138475</v>
       </c>
       <c r="Q11">
-        <v>56.86768774999999</v>
+        <v>54.4708475</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.09636491346809123</v>
+        <v>0.09679598689919175</v>
       </c>
       <c r="T11">
-        <v>0.7822231297818359</v>
+        <v>0.7888916986631815</v>
       </c>
       <c r="U11">
         <v>0.0553</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>3.596505858077108</v>
+        <v>3.236855272269397</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.09126388820927257</v>
+        <v>0.09130920516258213</v>
       </c>
       <c r="C12">
-        <v>5364.471700266097</v>
+        <v>5301.138843484849</v>
       </c>
       <c r="D12">
-        <v>5566.371700266097</v>
+        <v>5560.828843484849</v>
       </c>
       <c r="E12">
-        <v>-0.3000000000000682</v>
+        <v>57.49000000000001</v>
       </c>
       <c r="F12">
-        <v>577.9</v>
+        <v>635.6900000000001</v>
       </c>
       <c r="G12">
         <v>376</v>
@@ -2271,45 +2271,45 @@
         <v>103.443</v>
       </c>
       <c r="M12">
-        <v>31.95787</v>
+        <v>36.74288200000001</v>
       </c>
       <c r="N12">
-        <v>71.48513</v>
+        <v>66.70011799999999</v>
       </c>
       <c r="O12">
-        <v>17.8712825</v>
+        <v>16.6750295</v>
       </c>
       <c r="P12">
-        <v>53.6138475</v>
+        <v>50.0250885</v>
       </c>
       <c r="Q12">
-        <v>54.4708475</v>
+        <v>50.88208849999999</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.09679598689919175</v>
+        <v>0.0972367473736878</v>
       </c>
       <c r="T12">
-        <v>0.7888916986631815</v>
+        <v>0.7957101230250069</v>
       </c>
       <c r="U12">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V12">
         <v>0.25</v>
       </c>
       <c r="W12">
-        <v>0.041475</v>
+        <v>0.04335</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y12">
-        <v>3.236855272269397</v>
+        <v>2.815320801454822</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.09130920516258213</v>
+        <v>0.0911670221158917</v>
       </c>
       <c r="C13">
-        <v>5301.138843484849</v>
+        <v>5260.776824212149</v>
       </c>
       <c r="D13">
-        <v>5560.828843484849</v>
+        <v>5578.25682421215</v>
       </c>
       <c r="E13">
-        <v>57.49000000000001</v>
+        <v>115.28</v>
       </c>
       <c r="F13">
-        <v>635.6900000000001</v>
+        <v>693.48</v>
       </c>
       <c r="G13">
         <v>376</v>
@@ -2353,28 +2353,28 @@
         <v>103.443</v>
       </c>
       <c r="M13">
-        <v>36.74288200000001</v>
+        <v>40.083144</v>
       </c>
       <c r="N13">
-        <v>66.70011799999999</v>
+        <v>63.35985599999999</v>
       </c>
       <c r="O13">
-        <v>16.6750295</v>
+        <v>15.839964</v>
       </c>
       <c r="P13">
-        <v>50.0250885</v>
+        <v>47.519892</v>
       </c>
       <c r="Q13">
-        <v>50.88208849999999</v>
+        <v>48.376892</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.0972367473736878</v>
+        <v>0.09768752513169511</v>
       </c>
       <c r="T13">
-        <v>0.7957101230250069</v>
+        <v>0.8026835115768736</v>
       </c>
       <c r="U13">
         <v>0.0578</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>2.815320801454822</v>
+        <v>2.580710734666921</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.0911670221158917</v>
+        <v>0.09163908906920125</v>
       </c>
       <c r="C14">
-        <v>5260.776824212149</v>
+        <v>5145.539986649374</v>
       </c>
       <c r="D14">
-        <v>5578.25682421215</v>
+        <v>5520.809986649373</v>
       </c>
       <c r="E14">
-        <v>115.28</v>
+        <v>173.0699999999999</v>
       </c>
       <c r="F14">
-        <v>693.48</v>
+        <v>751.27</v>
       </c>
       <c r="G14">
         <v>376</v>
@@ -2435,45 +2435,45 @@
         <v>103.443</v>
       </c>
       <c r="M14">
-        <v>40.083144</v>
+        <v>48.156407</v>
       </c>
       <c r="N14">
-        <v>63.35985599999999</v>
+        <v>55.286593</v>
       </c>
       <c r="O14">
-        <v>15.839964</v>
+        <v>13.82164825</v>
       </c>
       <c r="P14">
-        <v>47.519892</v>
+        <v>41.46494475</v>
       </c>
       <c r="Q14">
-        <v>48.376892</v>
+        <v>42.32194475</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.09768752513169511</v>
+        <v>0.09814866559678305</v>
       </c>
       <c r="T14">
-        <v>0.8026835115768736</v>
+        <v>0.8098172079115418</v>
       </c>
       <c r="U14">
-        <v>0.0578</v>
+        <v>0.0641</v>
       </c>
       <c r="V14">
         <v>0.25</v>
       </c>
       <c r="W14">
-        <v>0.04335</v>
+        <v>0.04807500000000001</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y14">
-        <v>2.580710734666921</v>
+        <v>2.14806308120122</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.09163908906920125</v>
+        <v>0.0923631560225108</v>
       </c>
       <c r="C15">
-        <v>5145.539986649374</v>
+        <v>5001.90022026108</v>
       </c>
       <c r="D15">
-        <v>5520.809986649373</v>
+        <v>5434.96022026108</v>
       </c>
       <c r="E15">
-        <v>173.0699999999999</v>
+        <v>230.86</v>
       </c>
       <c r="F15">
-        <v>751.27</v>
+        <v>809.0600000000001</v>
       </c>
       <c r="G15">
         <v>376</v>
@@ -2517,45 +2517,45 @@
         <v>103.443</v>
       </c>
       <c r="M15">
-        <v>48.156407</v>
+        <v>58.17141400000001</v>
       </c>
       <c r="N15">
-        <v>55.286593</v>
+        <v>45.27158599999999</v>
       </c>
       <c r="O15">
-        <v>13.82164825</v>
+        <v>11.3178965</v>
       </c>
       <c r="P15">
-        <v>41.46494475</v>
+        <v>33.9536895</v>
       </c>
       <c r="Q15">
-        <v>42.32194475</v>
+        <v>34.8106895</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.09814866559678305</v>
+        <v>0.09862053025873349</v>
       </c>
       <c r="T15">
-        <v>0.8098172079115418</v>
+        <v>0.8171168041609698</v>
       </c>
       <c r="U15">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V15">
         <v>0.25</v>
       </c>
       <c r="W15">
-        <v>0.04807500000000001</v>
+        <v>0.053925</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y15">
-        <v>2.14806308120122</v>
+        <v>1.778244551524912</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.0923631560225108</v>
+        <v>0.09276547297582037</v>
       </c>
       <c r="C16">
-        <v>5001.90022026108</v>
+        <v>4897.553111418593</v>
       </c>
       <c r="D16">
-        <v>5434.96022026108</v>
+        <v>5388.403111418594</v>
       </c>
       <c r="E16">
-        <v>230.86</v>
+        <v>288.6500000000001</v>
       </c>
       <c r="F16">
-        <v>809.0600000000001</v>
+        <v>866.8500000000001</v>
       </c>
       <c r="G16">
         <v>376</v>
@@ -2599,45 +2599,45 @@
         <v>103.443</v>
       </c>
       <c r="M16">
-        <v>58.17141400000001</v>
+        <v>65.70723000000001</v>
       </c>
       <c r="N16">
-        <v>45.27158599999999</v>
+        <v>37.73576999999999</v>
       </c>
       <c r="O16">
-        <v>11.3178965</v>
+        <v>9.433942499999997</v>
       </c>
       <c r="P16">
-        <v>33.9536895</v>
+        <v>28.30182749999999</v>
       </c>
       <c r="Q16">
-        <v>34.8106895</v>
+        <v>29.15882749999999</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.09862053025873349</v>
+        <v>0.0991034976186122</v>
       </c>
       <c r="T16">
-        <v>0.8171168041609698</v>
+        <v>0.8245881556162666</v>
       </c>
       <c r="U16">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V16">
         <v>0.25</v>
       </c>
       <c r="W16">
-        <v>0.053925</v>
+        <v>0.05685</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y16">
-        <v>1.778244551524912</v>
+        <v>1.574301640778343</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.09276547297582036</v>
+        <v>0.09827012449543837</v>
       </c>
       <c r="C17">
-        <v>4897.553111418595</v>
+        <v>4274.464636127889</v>
       </c>
       <c r="D17">
-        <v>5388.403111418595</v>
+        <v>4823.10463612789</v>
       </c>
       <c r="E17">
-        <v>288.65</v>
+        <v>346.4399999999999</v>
       </c>
       <c r="F17">
-        <v>866.85</v>
+        <v>924.64</v>
       </c>
       <c r="G17">
         <v>376</v>
@@ -2681,45 +2681,45 @@
         <v>103.443</v>
       </c>
       <c r="M17">
-        <v>65.70723000000001</v>
+        <v>109.662304</v>
       </c>
       <c r="N17">
-        <v>37.73576999999999</v>
+        <v>-6.219304000000008</v>
       </c>
       <c r="O17">
-        <v>9.433942499999997</v>
+        <v>-1.554826000000002</v>
       </c>
       <c r="P17">
-        <v>28.30182749999999</v>
+        <v>-4.664478000000006</v>
       </c>
       <c r="Q17">
-        <v>29.15882749999999</v>
+        <v>-3.807478000000006</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.0991034976186122</v>
+        <v>0.09972509155875098</v>
       </c>
       <c r="T17">
-        <v>0.8245881556162666</v>
+        <v>0.8342040161796513</v>
       </c>
       <c r="U17">
-        <v>0.07580000000000001</v>
+        <v>0.1186</v>
       </c>
       <c r="V17">
-        <v>0.25</v>
+        <v>0.2358216912896522</v>
       </c>
       <c r="W17">
-        <v>0.05685</v>
+        <v>0.09063154741304726</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y17">
-        <v>1.574301640778343</v>
+        <v>0.943286765158609</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.09827012449543837</v>
+        <v>0.09899812449543836</v>
       </c>
       <c r="C18">
-        <v>4274.464636127889</v>
+        <v>4150.671930047487</v>
       </c>
       <c r="D18">
-        <v>4823.10463612789</v>
+        <v>4757.101930047487</v>
       </c>
       <c r="E18">
-        <v>346.4399999999999</v>
+        <v>404.23</v>
       </c>
       <c r="F18">
-        <v>924.64</v>
+        <v>982.4300000000001</v>
       </c>
       <c r="G18">
         <v>376</v>
@@ -2763,37 +2763,37 @@
         <v>103.443</v>
       </c>
       <c r="M18">
-        <v>109.662304</v>
+        <v>116.516198</v>
       </c>
       <c r="N18">
-        <v>-6.219304000000008</v>
+        <v>-13.07319800000002</v>
       </c>
       <c r="O18">
-        <v>-1.554826000000002</v>
+        <v>-3.268299500000005</v>
       </c>
       <c r="P18">
-        <v>-4.664478000000006</v>
+        <v>-9.804898500000014</v>
       </c>
       <c r="Q18">
-        <v>-3.807478000000006</v>
+        <v>-8.947898500000015</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.09972509155875098</v>
+        <v>0.1003747914570492</v>
       </c>
       <c r="T18">
-        <v>0.8342040161796513</v>
+        <v>0.8442546669769965</v>
       </c>
       <c r="U18">
         <v>0.1186</v>
       </c>
       <c r="V18">
-        <v>0.2358216912896522</v>
+        <v>0.2219498270961433</v>
       </c>
       <c r="W18">
-        <v>0.09063154741304726</v>
+        <v>0.09227675050639741</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>0.943286765158609</v>
+        <v>0.8877993083845731</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.09899812449543836</v>
+        <v>0.09972612449543838</v>
       </c>
       <c r="C19">
-        <v>4150.671930047487</v>
+        <v>4028.661290469213</v>
       </c>
       <c r="D19">
-        <v>4757.101930047487</v>
+        <v>4692.881290469213</v>
       </c>
       <c r="E19">
-        <v>404.23</v>
+        <v>462.02</v>
       </c>
       <c r="F19">
-        <v>982.4300000000001</v>
+        <v>1040.22</v>
       </c>
       <c r="G19">
         <v>376</v>
@@ -2845,37 +2845,37 @@
         <v>103.443</v>
       </c>
       <c r="M19">
-        <v>116.516198</v>
+        <v>123.370092</v>
       </c>
       <c r="N19">
-        <v>-13.07319800000002</v>
+        <v>-19.92709200000002</v>
       </c>
       <c r="O19">
-        <v>-3.268299500000005</v>
+        <v>-4.981773000000004</v>
       </c>
       <c r="P19">
-        <v>-9.804898500000014</v>
+        <v>-14.94531900000001</v>
       </c>
       <c r="Q19">
-        <v>-8.947898500000015</v>
+        <v>-14.08831900000001</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1003747914570492</v>
+        <v>0.1010403376943303</v>
       </c>
       <c r="T19">
-        <v>0.8442546669769965</v>
+        <v>0.8545504555986672</v>
       </c>
       <c r="U19">
         <v>0.1186</v>
       </c>
       <c r="V19">
-        <v>0.2219498270961433</v>
+        <v>0.2096192811463576</v>
       </c>
       <c r="W19">
-        <v>0.09227675050639741</v>
+        <v>0.09373915325604201</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>0.8877993083845731</v>
+        <v>0.8384771245854302</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.09972612449543838</v>
+        <v>0.1167992104179141</v>
       </c>
       <c r="C20">
-        <v>4028.661290469213</v>
+        <v>2842.380353393334</v>
       </c>
       <c r="D20">
-        <v>4692.881290469213</v>
+        <v>3564.390353393334</v>
       </c>
       <c r="E20">
-        <v>462.02</v>
+        <v>519.8099999999999</v>
       </c>
       <c r="F20">
-        <v>1040.22</v>
+        <v>1098.01</v>
       </c>
       <c r="G20">
         <v>376</v>
@@ -2927,45 +2927,45 @@
         <v>103.443</v>
       </c>
       <c r="M20">
-        <v>123.370092</v>
+        <v>220.480408</v>
       </c>
       <c r="N20">
-        <v>-19.92709200000002</v>
+        <v>-117.037408</v>
       </c>
       <c r="O20">
-        <v>-4.981773000000004</v>
+        <v>-29.259352</v>
       </c>
       <c r="P20">
-        <v>-14.94531900000001</v>
+        <v>-87.77805600000001</v>
       </c>
       <c r="Q20">
-        <v>-14.08831900000001</v>
+        <v>-86.92105600000001</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1010403376943303</v>
+        <v>0.102619954113366</v>
       </c>
       <c r="T20">
-        <v>0.854550455598667</v>
+        <v>0.8789866192229291</v>
       </c>
       <c r="U20">
-        <v>0.1186</v>
+        <v>0.2008</v>
       </c>
       <c r="V20">
-        <v>0.2096192811463576</v>
+        <v>0.1172927346905127</v>
       </c>
       <c r="W20">
-        <v>0.09373915325604201</v>
+        <v>0.1772476188741451</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y20">
-        <v>0.8384771245854302</v>
+        <v>0.4691709387620508</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1167992104179141</v>
+        <v>0.118349210417914</v>
       </c>
       <c r="C21">
-        <v>2842.380353393334</v>
+        <v>2708.437835455034</v>
       </c>
       <c r="D21">
-        <v>3564.390353393334</v>
+        <v>3488.237835455035</v>
       </c>
       <c r="E21">
-        <v>519.8099999999999</v>
+        <v>577.5999999999999</v>
       </c>
       <c r="F21">
-        <v>1098.01</v>
+        <v>1155.8</v>
       </c>
       <c r="G21">
         <v>376</v>
@@ -3009,37 +3009,37 @@
         <v>103.443</v>
       </c>
       <c r="M21">
-        <v>220.480408</v>
+        <v>232.08464</v>
       </c>
       <c r="N21">
-        <v>-117.037408</v>
+        <v>-128.64164</v>
       </c>
       <c r="O21">
-        <v>-29.259352</v>
+        <v>-32.16041</v>
       </c>
       <c r="P21">
-        <v>-87.77805600000001</v>
+        <v>-96.48123</v>
       </c>
       <c r="Q21">
-        <v>-86.92105600000001</v>
+        <v>-95.62423</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.102619954113366</v>
+        <v>0.1033302035397831</v>
       </c>
       <c r="T21">
-        <v>0.8789866192229291</v>
+        <v>0.8899739519632157</v>
       </c>
       <c r="U21">
         <v>0.2008</v>
       </c>
       <c r="V21">
-        <v>0.1172927346905127</v>
+        <v>0.1114280979559871</v>
       </c>
       <c r="W21">
-        <v>0.1772476188741451</v>
+        <v>0.1784252379304378</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>0.4691709387620508</v>
+        <v>0.4457123918239484</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.118349210417914</v>
+        <v>0.119899210417914</v>
       </c>
       <c r="C22">
-        <v>2708.437835455034</v>
+        <v>2577.681219286502</v>
       </c>
       <c r="D22">
-        <v>3488.237835455035</v>
+        <v>3415.271219286502</v>
       </c>
       <c r="E22">
-        <v>577.5999999999999</v>
+        <v>635.3900000000001</v>
       </c>
       <c r="F22">
-        <v>1155.8</v>
+        <v>1213.59</v>
       </c>
       <c r="G22">
         <v>376</v>
@@ -3091,37 +3091,37 @@
         <v>103.443</v>
       </c>
       <c r="M22">
-        <v>232.08464</v>
+        <v>243.688872</v>
       </c>
       <c r="N22">
-        <v>-128.64164</v>
+        <v>-140.245872</v>
       </c>
       <c r="O22">
-        <v>-32.16041</v>
+        <v>-35.061468</v>
       </c>
       <c r="P22">
-        <v>-96.48123</v>
+        <v>-105.184404</v>
       </c>
       <c r="Q22">
-        <v>-95.62423</v>
+        <v>-104.327404</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1033302035397831</v>
+        <v>0.1040584339643373</v>
       </c>
       <c r="T22">
-        <v>0.8899739519632157</v>
+        <v>0.9012394450260413</v>
       </c>
       <c r="U22">
         <v>0.2008</v>
       </c>
       <c r="V22">
-        <v>0.1114280979559871</v>
+        <v>0.106121998053321</v>
       </c>
       <c r="W22">
-        <v>0.1784252379304378</v>
+        <v>0.1794907027908932</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>0.4457123918239484</v>
+        <v>0.4244879922132841</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.119899210417914</v>
+        <v>0.121449210417914</v>
       </c>
       <c r="C23">
-        <v>2577.681219286502</v>
+        <v>2449.914674116369</v>
       </c>
       <c r="D23">
-        <v>3415.271219286502</v>
+        <v>3345.294674116369</v>
       </c>
       <c r="E23">
-        <v>635.3899999999999</v>
+        <v>693.1800000000001</v>
       </c>
       <c r="F23">
-        <v>1213.59</v>
+        <v>1271.38</v>
       </c>
       <c r="G23">
         <v>376</v>
@@ -3173,37 +3173,37 @@
         <v>103.443</v>
       </c>
       <c r="M23">
-        <v>243.688872</v>
+        <v>255.293104</v>
       </c>
       <c r="N23">
-        <v>-140.245872</v>
+        <v>-151.850104</v>
       </c>
       <c r="O23">
-        <v>-35.061468</v>
+        <v>-37.96252600000001</v>
       </c>
       <c r="P23">
-        <v>-105.184404</v>
+        <v>-113.887578</v>
       </c>
       <c r="Q23">
-        <v>-104.327404</v>
+        <v>-113.030578</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1040584339643373</v>
+        <v>0.1048053369638801</v>
       </c>
       <c r="T23">
-        <v>0.9012394450260413</v>
+        <v>0.9127937968853496</v>
       </c>
       <c r="U23">
         <v>0.2008</v>
       </c>
       <c r="V23">
-        <v>0.106121998053321</v>
+        <v>0.1012982708690792</v>
       </c>
       <c r="W23">
-        <v>0.1794907027908932</v>
+        <v>0.1804593072094889</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>0.424487992213284</v>
+        <v>0.4051930834763166</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.121449210417914</v>
+        <v>0.122999210417914</v>
       </c>
       <c r="C24">
-        <v>2449.914674116369</v>
+        <v>2324.958096675867</v>
       </c>
       <c r="D24">
-        <v>3345.294674116369</v>
+        <v>3278.128096675867</v>
       </c>
       <c r="E24">
-        <v>693.1800000000001</v>
+        <v>750.97</v>
       </c>
       <c r="F24">
-        <v>1271.38</v>
+        <v>1329.17</v>
       </c>
       <c r="G24">
         <v>376</v>
@@ -3255,37 +3255,37 @@
         <v>103.443</v>
       </c>
       <c r="M24">
-        <v>255.293104</v>
+        <v>266.897336</v>
       </c>
       <c r="N24">
-        <v>-151.850104</v>
+        <v>-163.454336</v>
       </c>
       <c r="O24">
-        <v>-37.96252600000001</v>
+        <v>-40.863584</v>
       </c>
       <c r="P24">
-        <v>-113.887578</v>
+        <v>-122.590752</v>
       </c>
       <c r="Q24">
-        <v>-113.030578</v>
+        <v>-121.733752</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1048053369638801</v>
+        <v>0.1055716400413331</v>
       </c>
       <c r="T24">
-        <v>0.9127937968853496</v>
+        <v>0.9246482617799644</v>
       </c>
       <c r="U24">
         <v>0.2008</v>
       </c>
       <c r="V24">
-        <v>0.1012982708690792</v>
+        <v>0.09689399822259748</v>
       </c>
       <c r="W24">
-        <v>0.1804593072094889</v>
+        <v>0.1813436851569024</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>0.4051930834763166</v>
+        <v>0.3875759928903898</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.122999210417914</v>
+        <v>0.124549210417914</v>
       </c>
       <c r="C25">
-        <v>2324.958096675867</v>
+        <v>2202.645563397341</v>
       </c>
       <c r="D25">
-        <v>3278.128096675867</v>
+        <v>3213.605563397341</v>
       </c>
       <c r="E25">
-        <v>750.97</v>
+        <v>808.76</v>
       </c>
       <c r="F25">
-        <v>1329.17</v>
+        <v>1386.96</v>
       </c>
       <c r="G25">
         <v>376</v>
@@ -3337,37 +3337,37 @@
         <v>103.443</v>
       </c>
       <c r="M25">
-        <v>266.897336</v>
+        <v>278.501568</v>
       </c>
       <c r="N25">
-        <v>-163.454336</v>
+        <v>-175.058568</v>
       </c>
       <c r="O25">
-        <v>-40.863584</v>
+        <v>-43.76464200000001</v>
       </c>
       <c r="P25">
-        <v>-122.590752</v>
+        <v>-131.293926</v>
       </c>
       <c r="Q25">
-        <v>-121.733752</v>
+        <v>-130.436926</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1055716400413331</v>
+        <v>0.1063581089892454</v>
       </c>
       <c r="T25">
-        <v>0.9246482617799644</v>
+        <v>0.9368146862770693</v>
       </c>
       <c r="U25">
         <v>0.2008</v>
       </c>
       <c r="V25">
-        <v>0.09689399822259748</v>
+        <v>0.0928567482966559</v>
       </c>
       <c r="W25">
-        <v>0.1813436851569024</v>
+        <v>0.1821543649420315</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>0.3875759928903898</v>
+        <v>0.3714269931866235</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.124549210417914</v>
+        <v>0.1260992104179141</v>
       </c>
       <c r="C26">
-        <v>2202.645563397341</v>
+        <v>2082.823961874212</v>
       </c>
       <c r="D26">
-        <v>3213.605563397341</v>
+        <v>3151.573961874212</v>
       </c>
       <c r="E26">
-        <v>808.76</v>
+        <v>866.55</v>
       </c>
       <c r="F26">
-        <v>1386.96</v>
+        <v>1444.75</v>
       </c>
       <c r="G26">
         <v>376</v>
@@ -3419,37 +3419,37 @@
         <v>103.443</v>
       </c>
       <c r="M26">
-        <v>278.501568</v>
+        <v>290.1058</v>
       </c>
       <c r="N26">
-        <v>-175.058568</v>
+        <v>-186.6628</v>
       </c>
       <c r="O26">
-        <v>-43.76464200000001</v>
+        <v>-46.6657</v>
       </c>
       <c r="P26">
-        <v>-131.293926</v>
+        <v>-139.9971</v>
       </c>
       <c r="Q26">
-        <v>-130.436926</v>
+        <v>-139.1401</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1063581089892454</v>
+        <v>0.1071655504424353</v>
       </c>
       <c r="T26">
-        <v>0.9368146862770691</v>
+        <v>0.9493055487607636</v>
       </c>
       <c r="U26">
         <v>0.2008</v>
       </c>
       <c r="V26">
-        <v>0.0928567482966559</v>
+        <v>0.08914247836478968</v>
       </c>
       <c r="W26">
-        <v>0.1821543649420315</v>
+        <v>0.1829001903443502</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>0.3714269931866235</v>
+        <v>0.3565699134591587</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1260992104179141</v>
+        <v>0.127649210417914</v>
       </c>
       <c r="C27">
-        <v>2082.823961874212</v>
+        <v>1965.351777819375</v>
       </c>
       <c r="D27">
-        <v>3151.573961874212</v>
+        <v>3091.891777819375</v>
       </c>
       <c r="E27">
-        <v>866.55</v>
+        <v>924.3399999999999</v>
       </c>
       <c r="F27">
-        <v>1444.75</v>
+        <v>1502.54</v>
       </c>
       <c r="G27">
         <v>376</v>
@@ -3501,37 +3501,37 @@
         <v>103.443</v>
       </c>
       <c r="M27">
-        <v>290.1058</v>
+        <v>301.710032</v>
       </c>
       <c r="N27">
-        <v>-186.6628</v>
+        <v>-198.267032</v>
       </c>
       <c r="O27">
-        <v>-46.6657</v>
+        <v>-49.56675800000001</v>
       </c>
       <c r="P27">
-        <v>-139.9971</v>
+        <v>-148.700274</v>
       </c>
       <c r="Q27">
-        <v>-139.1401</v>
+        <v>-147.843274</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1071655504424353</v>
+        <v>0.1079948146376034</v>
       </c>
       <c r="T27">
-        <v>0.9493055487607636</v>
+        <v>0.9621340021223954</v>
       </c>
       <c r="U27">
         <v>0.2008</v>
       </c>
       <c r="V27">
-        <v>0.08914247836478968</v>
+        <v>0.08571392150460545</v>
       </c>
       <c r="W27">
-        <v>0.1829001903443502</v>
+        <v>0.1835886445618752</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>0.3565699134591587</v>
+        <v>0.3428556860184218</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.127649210417914</v>
+        <v>0.129199210417914</v>
       </c>
       <c r="C28">
-        <v>1965.351777819375</v>
+        <v>1850.098017292085</v>
       </c>
       <c r="D28">
-        <v>3091.891777819375</v>
+        <v>3034.428017292085</v>
       </c>
       <c r="E28">
-        <v>924.3399999999999</v>
+        <v>982.1300000000001</v>
       </c>
       <c r="F28">
-        <v>1502.54</v>
+        <v>1560.33</v>
       </c>
       <c r="G28">
         <v>376</v>
@@ -3583,37 +3583,37 @@
         <v>103.443</v>
       </c>
       <c r="M28">
-        <v>301.710032</v>
+        <v>313.314264</v>
       </c>
       <c r="N28">
-        <v>-198.267032</v>
+        <v>-209.8712640000001</v>
       </c>
       <c r="O28">
-        <v>-49.56675800000001</v>
+        <v>-52.46781600000001</v>
       </c>
       <c r="P28">
-        <v>-148.700274</v>
+        <v>-157.403448</v>
       </c>
       <c r="Q28">
-        <v>-147.843274</v>
+        <v>-156.546448</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1079948146376034</v>
+        <v>0.1088467983997623</v>
       </c>
       <c r="T28">
-        <v>0.9621340021223954</v>
+        <v>0.9753139199596885</v>
       </c>
       <c r="U28">
         <v>0.2008</v>
       </c>
       <c r="V28">
-        <v>0.08571392150460545</v>
+        <v>0.08253933181924969</v>
       </c>
       <c r="W28">
-        <v>0.1835886445618752</v>
+        <v>0.1842261021706947</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>0.3428556860184218</v>
+        <v>0.3301573272769986</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.129199210417914</v>
+        <v>0.130749210417914</v>
       </c>
       <c r="C29">
-        <v>1850.098017292085</v>
+        <v>1736.94124691642</v>
       </c>
       <c r="D29">
-        <v>3034.428017292085</v>
+        <v>2979.06124691642</v>
       </c>
       <c r="E29">
-        <v>982.1300000000001</v>
+        <v>1039.92</v>
       </c>
       <c r="F29">
-        <v>1560.33</v>
+        <v>1618.12</v>
       </c>
       <c r="G29">
         <v>376</v>
@@ -3665,37 +3665,37 @@
         <v>103.443</v>
       </c>
       <c r="M29">
-        <v>313.314264</v>
+        <v>324.9184960000001</v>
       </c>
       <c r="N29">
-        <v>-209.8712640000001</v>
+        <v>-221.4754960000001</v>
       </c>
       <c r="O29">
-        <v>-52.46781600000001</v>
+        <v>-55.36887400000002</v>
       </c>
       <c r="P29">
-        <v>-157.403448</v>
+        <v>-166.1066220000001</v>
       </c>
       <c r="Q29">
-        <v>-156.546448</v>
+        <v>-165.2496220000001</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1088467983997623</v>
+        <v>0.1097224483775368</v>
       </c>
       <c r="T29">
-        <v>0.9753139199596885</v>
+        <v>0.9888599466257953</v>
       </c>
       <c r="U29">
         <v>0.2008</v>
       </c>
       <c r="V29">
-        <v>0.08253933181924969</v>
+        <v>0.07959149853999076</v>
       </c>
       <c r="W29">
-        <v>0.1842261021706947</v>
+        <v>0.1848180270931699</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>0.3301573272769986</v>
+        <v>0.318365994159963</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.130749210417914</v>
+        <v>0.132299210417914</v>
       </c>
       <c r="C30">
-        <v>1736.94124691642</v>
+        <v>1625.768737291058</v>
       </c>
       <c r="D30">
-        <v>2979.06124691642</v>
+        <v>2925.678737291058</v>
       </c>
       <c r="E30">
-        <v>1039.92</v>
+        <v>1097.71</v>
       </c>
       <c r="F30">
-        <v>1618.12</v>
+        <v>1675.91</v>
       </c>
       <c r="G30">
         <v>376</v>
@@ -3747,37 +3747,37 @@
         <v>103.443</v>
       </c>
       <c r="M30">
-        <v>324.9184960000001</v>
+        <v>336.5227280000001</v>
       </c>
       <c r="N30">
-        <v>-221.4754960000001</v>
+        <v>-233.0797280000001</v>
       </c>
       <c r="O30">
-        <v>-55.36887400000002</v>
+        <v>-58.26993200000003</v>
       </c>
       <c r="P30">
-        <v>-166.1066220000001</v>
+        <v>-174.8097960000001</v>
       </c>
       <c r="Q30">
-        <v>-165.2496220000001</v>
+        <v>-173.9527960000001</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1097224483775368</v>
+        <v>0.1106227645518683</v>
       </c>
       <c r="T30">
-        <v>0.9888599466257953</v>
+        <v>1.002787551507849</v>
       </c>
       <c r="U30">
         <v>0.2008</v>
       </c>
       <c r="V30">
-        <v>0.07959149853999076</v>
+        <v>0.07684696410757728</v>
       </c>
       <c r="W30">
-        <v>0.1848180270931699</v>
+        <v>0.1853691296071985</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>0.318365994159963</v>
+        <v>0.3073878564303091</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.132299210417914</v>
+        <v>0.133849210417914</v>
       </c>
       <c r="C31">
-        <v>1625.768737291059</v>
+        <v>1516.475696874486</v>
       </c>
       <c r="D31">
-        <v>2925.678737291058</v>
+        <v>2874.175696874486</v>
       </c>
       <c r="E31">
-        <v>1097.71</v>
+        <v>1155.5</v>
       </c>
       <c r="F31">
-        <v>1675.91</v>
+        <v>1733.7</v>
       </c>
       <c r="G31">
         <v>376</v>
@@ -3829,37 +3829,37 @@
         <v>103.443</v>
       </c>
       <c r="M31">
-        <v>336.522728</v>
+        <v>348.12696</v>
       </c>
       <c r="N31">
-        <v>-233.079728</v>
+        <v>-244.68396</v>
       </c>
       <c r="O31">
-        <v>-58.269932</v>
+        <v>-61.17099</v>
       </c>
       <c r="P31">
-        <v>-174.809796</v>
+        <v>-183.51297</v>
       </c>
       <c r="Q31">
-        <v>-173.952796</v>
+        <v>-182.65597</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1106227645518683</v>
+        <v>0.1115488040454664</v>
       </c>
       <c r="T31">
-        <v>1.002787551507849</v>
+        <v>1.017113087957961</v>
       </c>
       <c r="U31">
         <v>0.2008</v>
       </c>
       <c r="V31">
-        <v>0.07684696410757731</v>
+        <v>0.07428539863732472</v>
       </c>
       <c r="W31">
-        <v>0.1853691296071985</v>
+        <v>0.1858834919536252</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>0.3073878564303092</v>
+        <v>0.2971415945492989</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.133849210417914</v>
+        <v>0.135399210417914</v>
       </c>
       <c r="C32">
-        <v>1516.475696874486</v>
+        <v>1408.964585389504</v>
       </c>
       <c r="D32">
-        <v>2874.175696874486</v>
+        <v>2824.454585389504</v>
       </c>
       <c r="E32">
-        <v>1155.5</v>
+        <v>1213.29</v>
       </c>
       <c r="F32">
-        <v>1733.7</v>
+        <v>1791.49</v>
       </c>
       <c r="G32">
         <v>376</v>
@@ -3911,37 +3911,37 @@
         <v>103.443</v>
       </c>
       <c r="M32">
-        <v>348.12696</v>
+        <v>359.731192</v>
       </c>
       <c r="N32">
-        <v>-244.68396</v>
+        <v>-256.288192</v>
       </c>
       <c r="O32">
-        <v>-61.17099</v>
+        <v>-64.07204800000001</v>
       </c>
       <c r="P32">
-        <v>-183.51297</v>
+        <v>-192.216144</v>
       </c>
       <c r="Q32">
-        <v>-182.65597</v>
+        <v>-191.359144</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1115488040454664</v>
+        <v>0.1125016852635166</v>
       </c>
       <c r="T32">
-        <v>1.017113087957961</v>
+        <v>1.031853857348656</v>
       </c>
       <c r="U32">
         <v>0.2008</v>
       </c>
       <c r="V32">
-        <v>0.07428539863732472</v>
+        <v>0.07188909545547553</v>
       </c>
       <c r="W32">
-        <v>0.1858834919536252</v>
+        <v>0.1863646696325405</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>0.2971415945492989</v>
+        <v>0.2875563818219021</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.135399210417914</v>
+        <v>0.136949210417914</v>
       </c>
       <c r="C33">
-        <v>1408.964585389504</v>
+        <v>1303.144497281431</v>
       </c>
       <c r="D33">
-        <v>2824.454585389504</v>
+        <v>2776.424497281431</v>
       </c>
       <c r="E33">
-        <v>1213.29</v>
+        <v>1271.08</v>
       </c>
       <c r="F33">
-        <v>1791.49</v>
+        <v>1849.28</v>
       </c>
       <c r="G33">
         <v>376</v>
@@ -3993,37 +3993,37 @@
         <v>103.443</v>
       </c>
       <c r="M33">
-        <v>359.731192</v>
+        <v>371.335424</v>
       </c>
       <c r="N33">
-        <v>-256.288192</v>
+        <v>-267.892424</v>
       </c>
       <c r="O33">
-        <v>-64.07204800000001</v>
+        <v>-66.973106</v>
       </c>
       <c r="P33">
-        <v>-192.216144</v>
+        <v>-200.919318</v>
       </c>
       <c r="Q33">
-        <v>-191.359144</v>
+        <v>-200.062318</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1125016852635166</v>
+        <v>0.1134825923997448</v>
       </c>
       <c r="T33">
-        <v>1.031853857348656</v>
+        <v>1.047028178780254</v>
       </c>
       <c r="U33">
         <v>0.2008</v>
       </c>
       <c r="V33">
-        <v>0.07188909545547553</v>
+        <v>0.06964256122249193</v>
       </c>
       <c r="W33">
-        <v>0.1863646696325405</v>
+        <v>0.1868157737065236</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>0.2875563818219021</v>
+        <v>0.2785702448899677</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.136949210417914</v>
+        <v>0.138499210417914</v>
       </c>
       <c r="C34">
-        <v>1303.144497281431</v>
+        <v>1198.930607030532</v>
       </c>
       <c r="D34">
-        <v>2776.424497281431</v>
+        <v>2730.000607030533</v>
       </c>
       <c r="E34">
-        <v>1271.08</v>
+        <v>1328.87</v>
       </c>
       <c r="F34">
-        <v>1849.28</v>
+        <v>1907.07</v>
       </c>
       <c r="G34">
         <v>376</v>
@@ -4075,37 +4075,37 @@
         <v>103.443</v>
       </c>
       <c r="M34">
-        <v>371.335424</v>
+        <v>382.9396560000001</v>
       </c>
       <c r="N34">
-        <v>-267.892424</v>
+        <v>-279.4966560000001</v>
       </c>
       <c r="O34">
-        <v>-66.973106</v>
+        <v>-69.87416400000002</v>
       </c>
       <c r="P34">
-        <v>-200.919318</v>
+        <v>-209.6224920000001</v>
       </c>
       <c r="Q34">
-        <v>-200.062318</v>
+        <v>-208.7654920000001</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1134825923997448</v>
+        <v>0.1144927803460097</v>
       </c>
       <c r="T34">
-        <v>1.047028178780254</v>
+        <v>1.062655465030705</v>
       </c>
       <c r="U34">
         <v>0.2008</v>
       </c>
       <c r="V34">
-        <v>0.06964256122249193</v>
+        <v>0.06753218057938611</v>
       </c>
       <c r="W34">
-        <v>0.1868157737065236</v>
+        <v>0.1872395381396593</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>0.2785702448899677</v>
+        <v>0.2701287223175444</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.138499210417914</v>
+        <v>0.140049210417914</v>
       </c>
       <c r="C35">
-        <v>1198.930607030532</v>
+        <v>1096.243669198011</v>
       </c>
       <c r="D35">
-        <v>2730.000607030533</v>
+        <v>2685.103669198011</v>
       </c>
       <c r="E35">
-        <v>1328.87</v>
+        <v>1386.66</v>
       </c>
       <c r="F35">
-        <v>1907.07</v>
+        <v>1964.86</v>
       </c>
       <c r="G35">
         <v>376</v>
@@ -4157,37 +4157,37 @@
         <v>103.443</v>
       </c>
       <c r="M35">
-        <v>382.9396560000001</v>
+        <v>394.543888</v>
       </c>
       <c r="N35">
-        <v>-279.4966560000001</v>
+        <v>-291.1008880000001</v>
       </c>
       <c r="O35">
-        <v>-69.87416400000002</v>
+        <v>-72.77522200000001</v>
       </c>
       <c r="P35">
-        <v>-209.6224920000001</v>
+        <v>-218.325666</v>
       </c>
       <c r="Q35">
-        <v>-208.7654920000001</v>
+        <v>-217.468666</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1144927803460097</v>
+        <v>0.1155335800482219</v>
       </c>
       <c r="T35">
-        <v>1.062655465030705</v>
+        <v>1.078756305409958</v>
       </c>
       <c r="U35">
         <v>0.2008</v>
       </c>
       <c r="V35">
-        <v>0.06753218057938611</v>
+        <v>0.06554593997411004</v>
       </c>
       <c r="W35">
-        <v>0.1872395381396593</v>
+        <v>0.1876383752531987</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>0.2701287223175444</v>
+        <v>0.2621837598964402</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.140049210417914</v>
+        <v>0.141599210417914</v>
       </c>
       <c r="C36">
-        <v>1096.243669198011</v>
+        <v>995.0095670065516</v>
       </c>
       <c r="D36">
-        <v>2685.103669198011</v>
+        <v>2641.659567006552</v>
       </c>
       <c r="E36">
-        <v>1386.66</v>
+        <v>1444.45</v>
       </c>
       <c r="F36">
-        <v>1964.86</v>
+        <v>2022.65</v>
       </c>
       <c r="G36">
         <v>376</v>
@@ -4239,37 +4239,37 @@
         <v>103.443</v>
       </c>
       <c r="M36">
-        <v>394.543888</v>
+        <v>406.14812</v>
       </c>
       <c r="N36">
-        <v>-291.1008880000001</v>
+        <v>-302.70512</v>
       </c>
       <c r="O36">
-        <v>-72.77522200000001</v>
+        <v>-75.67628000000001</v>
       </c>
       <c r="P36">
-        <v>-218.325666</v>
+        <v>-227.02884</v>
       </c>
       <c r="Q36">
-        <v>-217.468666</v>
+        <v>-226.17184</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1155335800482219</v>
+        <v>0.1166064043566561</v>
       </c>
       <c r="T36">
-        <v>1.078756305409958</v>
+        <v>1.09535255626242</v>
       </c>
       <c r="U36">
         <v>0.2008</v>
       </c>
       <c r="V36">
-        <v>0.06554593997411004</v>
+        <v>0.06367319883199263</v>
       </c>
       <c r="W36">
-        <v>0.1876383752531987</v>
+        <v>0.1880144216745359</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>0.2621837598964402</v>
+        <v>0.2546927953279704</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.141599210417914</v>
+        <v>0.143149210417914</v>
       </c>
       <c r="C37">
-        <v>995.0095670065516</v>
+        <v>895.1589040460367</v>
       </c>
       <c r="D37">
-        <v>2641.659567006552</v>
+        <v>2599.598904046037</v>
       </c>
       <c r="E37">
-        <v>1444.45</v>
+        <v>1502.24</v>
       </c>
       <c r="F37">
-        <v>2022.65</v>
+        <v>2080.44</v>
       </c>
       <c r="G37">
         <v>376</v>
@@ -4321,37 +4321,37 @@
         <v>103.443</v>
       </c>
       <c r="M37">
-        <v>406.14812</v>
+        <v>417.752352</v>
       </c>
       <c r="N37">
-        <v>-302.70512</v>
+        <v>-314.309352</v>
       </c>
       <c r="O37">
-        <v>-75.67628000000001</v>
+        <v>-78.57733800000001</v>
       </c>
       <c r="P37">
-        <v>-227.02884</v>
+        <v>-235.732014</v>
       </c>
       <c r="Q37">
-        <v>-226.17184</v>
+        <v>-234.875014</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1166064043566561</v>
+        <v>0.1177127544247289</v>
       </c>
       <c r="T37">
-        <v>1.09535255626242</v>
+        <v>1.11246743995402</v>
       </c>
       <c r="U37">
         <v>0.2008</v>
       </c>
       <c r="V37">
-        <v>0.06367319883199263</v>
+        <v>0.06190449886443727</v>
       </c>
       <c r="W37">
-        <v>0.1880144216745359</v>
+        <v>0.188369576628021</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.2546927953279704</v>
+        <v>0.247617995457749</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.143149210417914</v>
+        <v>0.1446992104179141</v>
       </c>
       <c r="C38">
-        <v>895.1589040460367</v>
+        <v>796.6266343732591</v>
       </c>
       <c r="D38">
-        <v>2599.598904046037</v>
+        <v>2558.856634373259</v>
       </c>
       <c r="E38">
-        <v>1502.24</v>
+        <v>1560.03</v>
       </c>
       <c r="F38">
-        <v>2080.44</v>
+        <v>2138.23</v>
       </c>
       <c r="G38">
         <v>376</v>
@@ -4403,37 +4403,37 @@
         <v>103.443</v>
       </c>
       <c r="M38">
-        <v>417.752352</v>
+        <v>429.356584</v>
       </c>
       <c r="N38">
-        <v>-314.309352</v>
+        <v>-325.913584</v>
       </c>
       <c r="O38">
-        <v>-78.57733800000001</v>
+        <v>-81.478396</v>
       </c>
       <c r="P38">
-        <v>-235.732014</v>
+        <v>-244.435188</v>
       </c>
       <c r="Q38">
-        <v>-234.875014</v>
+        <v>-243.578188</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1177127544247289</v>
+        <v>0.1188542267171849</v>
       </c>
       <c r="T38">
-        <v>1.11246743995402</v>
+        <v>1.130125653286623</v>
       </c>
       <c r="U38">
         <v>0.2008</v>
       </c>
       <c r="V38">
-        <v>0.06190449886443727</v>
+        <v>0.06023140430053356</v>
       </c>
       <c r="W38">
-        <v>0.188369576628021</v>
+        <v>0.1887055340164529</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.247617995457749</v>
+        <v>0.2409256172021342</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1446992104179141</v>
+        <v>0.146249210417914</v>
       </c>
       <c r="C39">
-        <v>796.6266343732591</v>
+        <v>699.3517268585342</v>
       </c>
       <c r="D39">
-        <v>2558.856634373259</v>
+        <v>2519.371726858534</v>
       </c>
       <c r="E39">
-        <v>1560.03</v>
+        <v>1617.82</v>
       </c>
       <c r="F39">
-        <v>2138.23</v>
+        <v>2196.02</v>
       </c>
       <c r="G39">
         <v>376</v>
@@ -4485,37 +4485,37 @@
         <v>103.443</v>
       </c>
       <c r="M39">
-        <v>429.356584</v>
+        <v>440.960816</v>
       </c>
       <c r="N39">
-        <v>-325.913584</v>
+        <v>-337.517816</v>
       </c>
       <c r="O39">
-        <v>-81.478396</v>
+        <v>-84.37945400000001</v>
       </c>
       <c r="P39">
-        <v>-244.435188</v>
+        <v>-253.138362</v>
       </c>
       <c r="Q39">
-        <v>-243.578188</v>
+        <v>-252.281362</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1188542267171849</v>
+        <v>0.1200325206964943</v>
       </c>
       <c r="T39">
-        <v>1.130125653286623</v>
+        <v>1.148353486404149</v>
       </c>
       <c r="U39">
         <v>0.2008</v>
       </c>
       <c r="V39">
-        <v>0.06023140430053356</v>
+        <v>0.05864636734525636</v>
       </c>
       <c r="W39">
-        <v>0.1887055340164529</v>
+        <v>0.1890238094370725</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.2409256172021342</v>
+        <v>0.2345854693810254</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.146249210417914</v>
+        <v>0.147799210417914</v>
       </c>
       <c r="C40">
-        <v>699.3517268585342</v>
+        <v>603.2768601362245</v>
       </c>
       <c r="D40">
-        <v>2519.371726858534</v>
+        <v>2481.086860136224</v>
       </c>
       <c r="E40">
-        <v>1617.82</v>
+        <v>1675.61</v>
       </c>
       <c r="F40">
-        <v>2196.02</v>
+        <v>2253.81</v>
       </c>
       <c r="G40">
         <v>376</v>
@@ -4567,37 +4567,37 @@
         <v>103.443</v>
       </c>
       <c r="M40">
-        <v>440.960816</v>
+        <v>452.565048</v>
       </c>
       <c r="N40">
-        <v>-337.517816</v>
+        <v>-349.122048</v>
       </c>
       <c r="O40">
-        <v>-84.37945400000001</v>
+        <v>-87.280512</v>
       </c>
       <c r="P40">
-        <v>-253.138362</v>
+        <v>-261.841536</v>
       </c>
       <c r="Q40">
-        <v>-252.281362</v>
+        <v>-260.984536</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1200325206964943</v>
+        <v>0.1212494472652893</v>
       </c>
       <c r="T40">
-        <v>1.148353486404149</v>
+        <v>1.167178953394381</v>
       </c>
       <c r="U40">
         <v>0.2008</v>
       </c>
       <c r="V40">
-        <v>0.05864636734525636</v>
+        <v>0.05714261433640364</v>
       </c>
       <c r="W40">
-        <v>0.1890238094370725</v>
+        <v>0.1893257630412502</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.2345854693810254</v>
+        <v>0.2285704573456145</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.147799210417914</v>
+        <v>0.149349210417914</v>
       </c>
       <c r="C41">
-        <v>603.2768601362245</v>
+        <v>508.3481449524929</v>
       </c>
       <c r="D41">
-        <v>2481.086860136224</v>
+        <v>2443.948144952493</v>
       </c>
       <c r="E41">
-        <v>1675.61</v>
+        <v>1733.4</v>
       </c>
       <c r="F41">
-        <v>2253.81</v>
+        <v>2311.6</v>
       </c>
       <c r="G41">
         <v>376</v>
@@ -4649,37 +4649,37 @@
         <v>103.443</v>
       </c>
       <c r="M41">
-        <v>452.565048</v>
+        <v>464.16928</v>
       </c>
       <c r="N41">
-        <v>-349.122048</v>
+        <v>-360.72628</v>
       </c>
       <c r="O41">
-        <v>-87.280512</v>
+        <v>-90.18157000000001</v>
       </c>
       <c r="P41">
-        <v>-261.841536</v>
+        <v>-270.54471</v>
       </c>
       <c r="Q41">
-        <v>-260.984536</v>
+        <v>-269.68771</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1212494472652893</v>
+        <v>0.1225069380530441</v>
       </c>
       <c r="T41">
-        <v>1.167178953394381</v>
+        <v>1.186631935950954</v>
       </c>
       <c r="U41">
         <v>0.2008</v>
       </c>
       <c r="V41">
-        <v>0.05714261433640364</v>
+        <v>0.05571404897799354</v>
       </c>
       <c r="W41">
-        <v>0.1893257630412502</v>
+        <v>0.1896126189652189</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.2285704573456145</v>
+        <v>0.2228561959119741</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.149349210417914</v>
+        <v>0.150899210417914</v>
       </c>
       <c r="C42">
-        <v>508.3481449524929</v>
+        <v>414.5148710818953</v>
       </c>
       <c r="D42">
-        <v>2443.948144952493</v>
+        <v>2407.904871081896</v>
       </c>
       <c r="E42">
-        <v>1733.4</v>
+        <v>1791.19</v>
       </c>
       <c r="F42">
-        <v>2311.6</v>
+        <v>2369.39</v>
       </c>
       <c r="G42">
         <v>376</v>
@@ -4731,37 +4731,37 @@
         <v>103.443</v>
       </c>
       <c r="M42">
-        <v>464.16928</v>
+        <v>475.7735120000001</v>
       </c>
       <c r="N42">
-        <v>-360.72628</v>
+        <v>-372.3305120000001</v>
       </c>
       <c r="O42">
-        <v>-90.18157000000001</v>
+        <v>-93.08262800000003</v>
       </c>
       <c r="P42">
-        <v>-270.54471</v>
+        <v>-279.2478840000001</v>
       </c>
       <c r="Q42">
-        <v>-269.68771</v>
+        <v>-278.3908840000001</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1225069380530441</v>
+        <v>0.1238070556471635</v>
       </c>
       <c r="T42">
-        <v>1.186631935950954</v>
+        <v>1.206744341645038</v>
       </c>
       <c r="U42">
         <v>0.2008</v>
       </c>
       <c r="V42">
-        <v>0.05571404897799354</v>
+        <v>0.05435516973462784</v>
       </c>
       <c r="W42">
-        <v>0.1896126189652189</v>
+        <v>0.1898854819172867</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.2228561959119741</v>
+        <v>0.2174206789385114</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.150899210417914</v>
+        <v>0.152449210417914</v>
       </c>
       <c r="C43">
-        <v>414.5148710818953</v>
+        <v>321.7292763132914</v>
       </c>
       <c r="D43">
-        <v>2407.904871081896</v>
+        <v>2372.909276313292</v>
       </c>
       <c r="E43">
-        <v>1791.19</v>
+        <v>1848.98</v>
       </c>
       <c r="F43">
-        <v>2369.39</v>
+        <v>2427.18</v>
       </c>
       <c r="G43">
         <v>376</v>
@@ -4813,37 +4813,37 @@
         <v>103.443</v>
       </c>
       <c r="M43">
-        <v>475.7735120000001</v>
+        <v>487.3777440000001</v>
       </c>
       <c r="N43">
-        <v>-372.3305120000001</v>
+        <v>-383.9347440000001</v>
       </c>
       <c r="O43">
-        <v>-93.08262800000003</v>
+        <v>-95.98368600000002</v>
       </c>
       <c r="P43">
-        <v>-279.2478840000001</v>
+        <v>-287.951058</v>
       </c>
       <c r="Q43">
-        <v>-278.3908840000001</v>
+        <v>-287.094058</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1238070556471635</v>
+        <v>0.1251520048824594</v>
       </c>
       <c r="T43">
-        <v>1.206744341645038</v>
+        <v>1.227550278569953</v>
       </c>
       <c r="U43">
         <v>0.2008</v>
       </c>
       <c r="V43">
-        <v>0.05435516973462784</v>
+        <v>0.05306099902666051</v>
       </c>
       <c r="W43">
-        <v>0.1898854819172867</v>
+        <v>0.1901453513954466</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.2174206789385114</v>
+        <v>0.212243996106642</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.152449210417914</v>
+        <v>0.153999210417914</v>
       </c>
       <c r="C44">
-        <v>321.7292763132918</v>
+        <v>229.9463352920079</v>
       </c>
       <c r="D44">
-        <v>2372.909276313292</v>
+        <v>2338.916335292008</v>
       </c>
       <c r="E44">
-        <v>1848.98</v>
+        <v>1906.77</v>
       </c>
       <c r="F44">
-        <v>2427.18</v>
+        <v>2484.97</v>
       </c>
       <c r="G44">
         <v>376</v>
@@ -4895,37 +4895,37 @@
         <v>103.443</v>
       </c>
       <c r="M44">
-        <v>487.377744</v>
+        <v>498.981976</v>
       </c>
       <c r="N44">
-        <v>-383.934744</v>
+        <v>-395.538976</v>
       </c>
       <c r="O44">
-        <v>-95.98368600000001</v>
+        <v>-98.884744</v>
       </c>
       <c r="P44">
-        <v>-287.951058</v>
+        <v>-296.654232</v>
       </c>
       <c r="Q44">
-        <v>-287.094058</v>
+        <v>-295.797232</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1251520048824594</v>
+        <v>0.1265441453189938</v>
       </c>
       <c r="T44">
-        <v>1.227550278569953</v>
+        <v>1.249086248369425</v>
       </c>
       <c r="U44">
         <v>0.2008</v>
       </c>
       <c r="V44">
-        <v>0.05306099902666052</v>
+        <v>0.05182702230511028</v>
       </c>
       <c r="W44">
-        <v>0.1901453513954466</v>
+        <v>0.1903931339211339</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.212243996106642</v>
+        <v>0.2073080892204411</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.153999210417914</v>
+        <v>0.155549210417914</v>
       </c>
       <c r="C45">
-        <v>229.9463352920079</v>
+        <v>139.1235662552399</v>
       </c>
       <c r="D45">
-        <v>2338.916335292008</v>
+        <v>2305.88356625524</v>
       </c>
       <c r="E45">
-        <v>1906.77</v>
+        <v>1964.56</v>
       </c>
       <c r="F45">
-        <v>2484.97</v>
+        <v>2542.76</v>
       </c>
       <c r="G45">
         <v>376</v>
@@ -4977,37 +4977,37 @@
         <v>103.443</v>
       </c>
       <c r="M45">
-        <v>498.981976</v>
+        <v>510.5862080000001</v>
       </c>
       <c r="N45">
-        <v>-395.538976</v>
+        <v>-407.1432080000001</v>
       </c>
       <c r="O45">
-        <v>-98.884744</v>
+        <v>-101.785802</v>
       </c>
       <c r="P45">
-        <v>-296.654232</v>
+        <v>-305.3574060000001</v>
       </c>
       <c r="Q45">
-        <v>-295.797232</v>
+        <v>-304.5004060000001</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1265441453189938</v>
+        <v>0.127986005056833</v>
       </c>
       <c r="T45">
-        <v>1.249086248369425</v>
+        <v>1.271391359947451</v>
       </c>
       <c r="U45">
         <v>0.2008</v>
       </c>
       <c r="V45">
-        <v>0.05182702230511028</v>
+        <v>0.05064913543453958</v>
       </c>
       <c r="W45">
-        <v>0.1903931339211339</v>
+        <v>0.1906296536047445</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.2073080892204411</v>
+        <v>0.2025965417381583</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.155549210417914</v>
+        <v>0.173004922693369</v>
       </c>
       <c r="C46">
-        <v>139.1235662552399</v>
+        <v>-235.0916099172041</v>
       </c>
       <c r="D46">
-        <v>2305.88356625524</v>
+        <v>1989.458390082796</v>
       </c>
       <c r="E46">
-        <v>1964.56</v>
+        <v>2022.35</v>
       </c>
       <c r="F46">
-        <v>2542.76</v>
+        <v>2600.55</v>
       </c>
       <c r="G46">
         <v>376</v>
@@ -5059,45 +5059,45 @@
         <v>103.443</v>
       </c>
       <c r="M46">
-        <v>510.5862080000001</v>
+        <v>613.20969</v>
       </c>
       <c r="N46">
-        <v>-407.1432080000001</v>
+        <v>-509.76669</v>
       </c>
       <c r="O46">
-        <v>-101.785802</v>
+        <v>-127.4416725</v>
       </c>
       <c r="P46">
-        <v>-305.3574060000001</v>
+        <v>-382.3250175000001</v>
       </c>
       <c r="Q46">
-        <v>-304.5004060000001</v>
+        <v>-381.4680175</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.127986005056833</v>
+        <v>0.1297634092859662</v>
       </c>
       <c r="T46">
-        <v>1.271391359947451</v>
+        <v>1.298887238089859</v>
       </c>
       <c r="U46">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V46">
-        <v>0.05064913543453958</v>
+        <v>0.04217276801349959</v>
       </c>
       <c r="W46">
-        <v>0.1906296536047445</v>
+        <v>0.2258556613024168</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y46">
-        <v>0.2025965417381583</v>
+        <v>0.1686910720539984</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.173004922693369</v>
+        <v>0.174904922693369</v>
       </c>
       <c r="C47">
-        <v>-235.0916099172041</v>
+        <v>-322.1598966184401</v>
       </c>
       <c r="D47">
-        <v>1989.458390082796</v>
+        <v>1960.18010338156</v>
       </c>
       <c r="E47">
-        <v>2022.35</v>
+        <v>2080.14</v>
       </c>
       <c r="F47">
-        <v>2600.55</v>
+        <v>2658.34</v>
       </c>
       <c r="G47">
         <v>376</v>
@@ -5141,37 +5141,37 @@
         <v>103.443</v>
       </c>
       <c r="M47">
-        <v>613.20969</v>
+        <v>626.836572</v>
       </c>
       <c r="N47">
-        <v>-509.76669</v>
+        <v>-523.3935720000001</v>
       </c>
       <c r="O47">
-        <v>-127.4416725</v>
+        <v>-130.848393</v>
       </c>
       <c r="P47">
-        <v>-382.3250175000001</v>
+        <v>-392.5451790000001</v>
       </c>
       <c r="Q47">
-        <v>-381.4680175</v>
+        <v>-391.688179</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1297634092859662</v>
+        <v>0.1313182872357063</v>
       </c>
       <c r="T47">
-        <v>1.298887238089859</v>
+        <v>1.322940705461893</v>
       </c>
       <c r="U47">
         <v>0.2358</v>
       </c>
       <c r="V47">
-        <v>0.04217276801349959</v>
+        <v>0.04125596870885829</v>
       </c>
       <c r="W47">
-        <v>0.2258556613024168</v>
+        <v>0.2260718425784512</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.1686910720539984</v>
+        <v>0.1650238748354331</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.174904922693369</v>
+        <v>0.176804922693369</v>
       </c>
       <c r="C48">
-        <v>-322.1598966184401</v>
+        <v>-408.3789214203721</v>
       </c>
       <c r="D48">
-        <v>1960.18010338156</v>
+        <v>1931.751078579628</v>
       </c>
       <c r="E48">
-        <v>2080.14</v>
+        <v>2137.93</v>
       </c>
       <c r="F48">
-        <v>2658.34</v>
+        <v>2716.13</v>
       </c>
       <c r="G48">
         <v>376</v>
@@ -5223,37 +5223,37 @@
         <v>103.443</v>
       </c>
       <c r="M48">
-        <v>626.836572</v>
+        <v>640.4634540000001</v>
       </c>
       <c r="N48">
-        <v>-523.3935720000001</v>
+        <v>-537.0204540000001</v>
       </c>
       <c r="O48">
-        <v>-130.848393</v>
+        <v>-134.2551135</v>
       </c>
       <c r="P48">
-        <v>-392.5451790000001</v>
+        <v>-402.7653405000001</v>
       </c>
       <c r="Q48">
-        <v>-391.688179</v>
+        <v>-401.9083405000001</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1313182872357063</v>
+        <v>0.1329318398250592</v>
       </c>
       <c r="T48">
-        <v>1.322940705461893</v>
+        <v>1.347901850847967</v>
       </c>
       <c r="U48">
         <v>0.2358</v>
       </c>
       <c r="V48">
-        <v>0.04125596870885829</v>
+        <v>0.04037818214058471</v>
       </c>
       <c r="W48">
-        <v>0.2260718425784512</v>
+        <v>0.2262788246512501</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.1650238748354331</v>
+        <v>0.1615127285623388</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.176804922693369</v>
+        <v>0.178704922693369</v>
       </c>
       <c r="C49">
-        <v>-408.3789214203721</v>
+        <v>-493.7851072991234</v>
       </c>
       <c r="D49">
-        <v>1931.751078579628</v>
+        <v>1904.134892700876</v>
       </c>
       <c r="E49">
-        <v>2137.93</v>
+        <v>2195.72</v>
       </c>
       <c r="F49">
-        <v>2716.13</v>
+        <v>2773.92</v>
       </c>
       <c r="G49">
         <v>376</v>
@@ -5305,37 +5305,37 @@
         <v>103.443</v>
       </c>
       <c r="M49">
-        <v>640.4634540000001</v>
+        <v>654.0903360000001</v>
       </c>
       <c r="N49">
-        <v>-537.0204540000001</v>
+        <v>-550.6473360000001</v>
       </c>
       <c r="O49">
-        <v>-134.2551135</v>
+        <v>-137.661834</v>
       </c>
       <c r="P49">
-        <v>-402.7653405000001</v>
+        <v>-412.9855020000001</v>
       </c>
       <c r="Q49">
-        <v>-401.9083405000001</v>
+        <v>-412.1285020000001</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1329318398250592</v>
+        <v>0.1346074521293873</v>
       </c>
       <c r="T49">
-        <v>1.347901850847967</v>
+        <v>1.373823040287351</v>
       </c>
       <c r="U49">
         <v>0.2358</v>
       </c>
       <c r="V49">
-        <v>0.04037818214058471</v>
+        <v>0.03953697001265586</v>
       </c>
       <c r="W49">
-        <v>0.2262788246512501</v>
+        <v>0.2264771824710158</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.1615127285623388</v>
+        <v>0.1581478800506234</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1787049226933689</v>
+        <v>0.180604922693369</v>
       </c>
       <c r="C50">
-        <v>-493.7851072991234</v>
+        <v>-578.4128237849009</v>
       </c>
       <c r="D50">
-        <v>1904.134892700876</v>
+        <v>1877.297176215099</v>
       </c>
       <c r="E50">
-        <v>2195.72</v>
+        <v>2253.51</v>
       </c>
       <c r="F50">
-        <v>2773.92</v>
+        <v>2831.71</v>
       </c>
       <c r="G50">
         <v>376</v>
@@ -5387,37 +5387,37 @@
         <v>103.443</v>
       </c>
       <c r="M50">
-        <v>654.0903360000001</v>
+        <v>667.717218</v>
       </c>
       <c r="N50">
-        <v>-550.6473360000001</v>
+        <v>-564.274218</v>
       </c>
       <c r="O50">
-        <v>-137.661834</v>
+        <v>-141.0685545</v>
       </c>
       <c r="P50">
-        <v>-412.9855020000001</v>
+        <v>-423.2056635</v>
       </c>
       <c r="Q50">
-        <v>-412.1285020000001</v>
+        <v>-422.3486635</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1346074521293873</v>
+        <v>0.1363487747201596</v>
       </c>
       <c r="T50">
-        <v>1.37382304028735</v>
+        <v>1.400760746959651</v>
       </c>
       <c r="U50">
         <v>0.2358</v>
       </c>
       <c r="V50">
-        <v>0.03953697001265586</v>
+        <v>0.03873009307362207</v>
       </c>
       <c r="W50">
-        <v>0.2264771824710158</v>
+        <v>0.2266674440532399</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.1581478800506234</v>
+        <v>0.1549203722944883</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.180604922693369</v>
+        <v>0.182504922693369</v>
       </c>
       <c r="C51">
-        <v>-578.4128237849009</v>
+        <v>-662.2945296615735</v>
       </c>
       <c r="D51">
-        <v>1877.297176215099</v>
+        <v>1851.205470338427</v>
       </c>
       <c r="E51">
-        <v>2253.51</v>
+        <v>2311.3</v>
       </c>
       <c r="F51">
-        <v>2831.71</v>
+        <v>2889.5</v>
       </c>
       <c r="G51">
         <v>376</v>
@@ -5469,37 +5469,37 @@
         <v>103.443</v>
       </c>
       <c r="M51">
-        <v>667.717218</v>
+        <v>681.3441</v>
       </c>
       <c r="N51">
-        <v>-564.274218</v>
+        <v>-577.9011</v>
       </c>
       <c r="O51">
-        <v>-141.0685545</v>
+        <v>-144.475275</v>
       </c>
       <c r="P51">
-        <v>-423.2056635</v>
+        <v>-433.425825</v>
       </c>
       <c r="Q51">
-        <v>-422.3486635</v>
+        <v>-432.568825</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1363487747201596</v>
+        <v>0.1381597502145628</v>
       </c>
       <c r="T51">
-        <v>1.400760746959651</v>
+        <v>1.428775961898844</v>
       </c>
       <c r="U51">
         <v>0.2358</v>
       </c>
       <c r="V51">
-        <v>0.03873009307362207</v>
+        <v>0.03795549121214963</v>
       </c>
       <c r="W51">
-        <v>0.2266674440532399</v>
+        <v>0.2268500951721751</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.1549203722944883</v>
+        <v>0.1518219648485984</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.182504922693369</v>
+        <v>0.1844049226933689</v>
       </c>
       <c r="C52">
-        <v>-662.2945296615735</v>
+        <v>-745.4609039294928</v>
       </c>
       <c r="D52">
-        <v>1851.205470338427</v>
+        <v>1825.829096070507</v>
       </c>
       <c r="E52">
-        <v>2311.3</v>
+        <v>2369.09</v>
       </c>
       <c r="F52">
-        <v>2889.5</v>
+        <v>2947.29</v>
       </c>
       <c r="G52">
         <v>376</v>
@@ -5551,37 +5551,37 @@
         <v>103.443</v>
       </c>
       <c r="M52">
-        <v>681.3441</v>
+        <v>694.970982</v>
       </c>
       <c r="N52">
-        <v>-577.9011</v>
+        <v>-591.5279820000001</v>
       </c>
       <c r="O52">
-        <v>-144.475275</v>
+        <v>-147.8819955</v>
       </c>
       <c r="P52">
-        <v>-433.425825</v>
+        <v>-443.6459865</v>
       </c>
       <c r="Q52">
-        <v>-432.568825</v>
+        <v>-442.7889865</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1381597502145628</v>
+        <v>0.1400446430760845</v>
       </c>
       <c r="T52">
-        <v>1.428775961898844</v>
+        <v>1.457934654998821</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>0.03795549121214963</v>
+        <v>0.03721126589426434</v>
       </c>
       <c r="W52">
-        <v>0.2268500951721751</v>
+        <v>0.2270255835021325</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.1518219648485984</v>
+        <v>0.1488450635770573</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1844049226933689</v>
+        <v>0.186304922693369</v>
       </c>
       <c r="C53">
-        <v>-745.4609039294928</v>
+        <v>-827.940966142507</v>
       </c>
       <c r="D53">
-        <v>1825.829096070507</v>
+        <v>1801.139033857493</v>
       </c>
       <c r="E53">
-        <v>2369.09</v>
+        <v>2426.88</v>
       </c>
       <c r="F53">
-        <v>2947.29</v>
+        <v>3005.08</v>
       </c>
       <c r="G53">
         <v>376</v>
@@ -5633,37 +5633,37 @@
         <v>103.443</v>
       </c>
       <c r="M53">
-        <v>694.970982</v>
+        <v>708.597864</v>
       </c>
       <c r="N53">
-        <v>-591.5279820000001</v>
+        <v>-605.154864</v>
       </c>
       <c r="O53">
-        <v>-147.8819955</v>
+        <v>-151.288716</v>
       </c>
       <c r="P53">
-        <v>-443.6459865</v>
+        <v>-453.866148</v>
       </c>
       <c r="Q53">
-        <v>-442.7889865</v>
+        <v>-453.0091479999999</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1400446430760845</v>
+        <v>0.1420080731401696</v>
       </c>
       <c r="T53">
-        <v>1.457934654998821</v>
+        <v>1.48830829364463</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>0.03721126589426434</v>
+        <v>0.03649566462706696</v>
       </c>
       <c r="W53">
-        <v>0.2270255835021325</v>
+        <v>0.2271943222809376</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.1488450635770573</v>
+        <v>0.1459826585082677</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.186304922693369</v>
+        <v>0.188204922693369</v>
       </c>
       <c r="C54">
-        <v>-827.940966142507</v>
+        <v>-909.7621871115884</v>
       </c>
       <c r="D54">
-        <v>1801.139033857493</v>
+        <v>1777.107812888412</v>
       </c>
       <c r="E54">
-        <v>2426.88</v>
+        <v>2484.67</v>
       </c>
       <c r="F54">
-        <v>3005.08</v>
+        <v>3062.87</v>
       </c>
       <c r="G54">
         <v>376</v>
@@ -5715,37 +5715,37 @@
         <v>103.443</v>
       </c>
       <c r="M54">
-        <v>708.597864</v>
+        <v>722.2247460000001</v>
       </c>
       <c r="N54">
-        <v>-605.154864</v>
+        <v>-618.7817460000001</v>
       </c>
       <c r="O54">
-        <v>-151.288716</v>
+        <v>-154.6954365</v>
       </c>
       <c r="P54">
-        <v>-453.866148</v>
+        <v>-464.0863095000001</v>
       </c>
       <c r="Q54">
-        <v>-453.0091479999999</v>
+        <v>-463.2293095000001</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1420080731401696</v>
+        <v>0.1440550534197476</v>
       </c>
       <c r="T54">
-        <v>1.48830829364463</v>
+        <v>1.519974427551962</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>0.03649566462706696</v>
+        <v>0.03580706718127323</v>
       </c>
       <c r="W54">
-        <v>0.2271943222809376</v>
+        <v>0.2273566935586558</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.1459826585082677</v>
+        <v>0.1432282687250929</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.188204922693369</v>
+        <v>0.190104922693369</v>
       </c>
       <c r="C55">
-        <v>-909.7621871115884</v>
+        <v>-990.9505908629462</v>
       </c>
       <c r="D55">
-        <v>1777.107812888412</v>
+        <v>1753.709409137054</v>
       </c>
       <c r="E55">
-        <v>2484.67</v>
+        <v>2542.46</v>
       </c>
       <c r="F55">
-        <v>3062.87</v>
+        <v>3120.66</v>
       </c>
       <c r="G55">
         <v>376</v>
@@ -5797,37 +5797,37 @@
         <v>103.443</v>
       </c>
       <c r="M55">
-        <v>722.2247460000001</v>
+        <v>735.8516280000001</v>
       </c>
       <c r="N55">
-        <v>-618.7817460000001</v>
+        <v>-632.4086280000001</v>
       </c>
       <c r="O55">
-        <v>-154.6954365</v>
+        <v>-158.102157</v>
       </c>
       <c r="P55">
-        <v>-464.0863095000001</v>
+        <v>-474.3064710000001</v>
       </c>
       <c r="Q55">
-        <v>-463.2293095000001</v>
+        <v>-473.4494710000001</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1440550534197476</v>
+        <v>0.1461910328419161</v>
       </c>
       <c r="T55">
-        <v>1.519974427551962</v>
+        <v>1.553017349890049</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.03580706718127323</v>
+        <v>0.03514397334458299</v>
       </c>
       <c r="W55">
-        <v>0.2273566935586558</v>
+        <v>0.2275130510853473</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.1432282687250929</v>
+        <v>0.1405758933783319</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.190104922693369</v>
+        <v>0.192004922693369</v>
       </c>
       <c r="C56">
-        <v>-990.9505908629462</v>
+        <v>-1071.530848646185</v>
       </c>
       <c r="D56">
-        <v>1753.709409137054</v>
+        <v>1730.919151353815</v>
       </c>
       <c r="E56">
-        <v>2542.46</v>
+        <v>2600.25</v>
       </c>
       <c r="F56">
-        <v>3120.66</v>
+        <v>3178.45</v>
       </c>
       <c r="G56">
         <v>376</v>
@@ -5879,37 +5879,37 @@
         <v>103.443</v>
       </c>
       <c r="M56">
-        <v>735.8516280000001</v>
+        <v>749.4785100000001</v>
       </c>
       <c r="N56">
-        <v>-632.4086280000001</v>
+        <v>-646.0355100000002</v>
       </c>
       <c r="O56">
-        <v>-158.102157</v>
+        <v>-161.5088775</v>
       </c>
       <c r="P56">
-        <v>-474.3064710000001</v>
+        <v>-484.5266325000001</v>
       </c>
       <c r="Q56">
-        <v>-473.4494710000001</v>
+        <v>-483.6696325000001</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1461910328419161</v>
+        <v>0.1484219446828476</v>
       </c>
       <c r="T56">
-        <v>1.553017349890049</v>
+        <v>1.587528846554272</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.03514397334458299</v>
+        <v>0.03450499201104511</v>
       </c>
       <c r="W56">
-        <v>0.2275130510853473</v>
+        <v>0.2276637228837956</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.1405758933783319</v>
+        <v>0.1380199680441805</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.192004922693369</v>
+        <v>0.193904922693369</v>
       </c>
       <c r="C57">
-        <v>-1071.530848646185</v>
+        <v>-1151.526365706419</v>
       </c>
       <c r="D57">
-        <v>1730.919151353815</v>
+        <v>1708.713634293581</v>
       </c>
       <c r="E57">
-        <v>2600.25</v>
+        <v>2658.04</v>
       </c>
       <c r="F57">
-        <v>3178.45</v>
+        <v>3236.24</v>
       </c>
       <c r="G57">
         <v>376</v>
@@ -5961,37 +5961,37 @@
         <v>103.443</v>
       </c>
       <c r="M57">
-        <v>749.4785100000001</v>
+        <v>763.1053920000001</v>
       </c>
       <c r="N57">
-        <v>-646.0355100000002</v>
+        <v>-659.6623920000001</v>
       </c>
       <c r="O57">
-        <v>-161.5088775</v>
+        <v>-164.915598</v>
       </c>
       <c r="P57">
-        <v>-484.5266325000001</v>
+        <v>-494.746794</v>
       </c>
       <c r="Q57">
-        <v>-483.6696325000001</v>
+        <v>-493.889794</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1484219446828476</v>
+        <v>0.1507542616074577</v>
       </c>
       <c r="T57">
-        <v>1.587528846554272</v>
+        <v>1.623609047612323</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.03450499201104511</v>
+        <v>0.03388883143941931</v>
       </c>
       <c r="W57">
-        <v>0.2276637228837956</v>
+        <v>0.2278090135465849</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.1380199680441805</v>
+        <v>0.1355553257576773</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.193904922693369</v>
+        <v>0.195804922693369</v>
       </c>
       <c r="C58">
-        <v>-1151.526365706419</v>
+        <v>-1230.959361461927</v>
       </c>
       <c r="D58">
-        <v>1708.713634293581</v>
+        <v>1687.070638538073</v>
       </c>
       <c r="E58">
-        <v>2658.04</v>
+        <v>2715.83</v>
       </c>
       <c r="F58">
-        <v>3236.24</v>
+        <v>3294.03</v>
       </c>
       <c r="G58">
         <v>376</v>
@@ -6043,37 +6043,37 @@
         <v>103.443</v>
       </c>
       <c r="M58">
-        <v>763.1053920000001</v>
+        <v>776.7322740000001</v>
       </c>
       <c r="N58">
-        <v>-659.6623920000001</v>
+        <v>-673.2892740000001</v>
       </c>
       <c r="O58">
-        <v>-164.915598</v>
+        <v>-168.3223185</v>
       </c>
       <c r="P58">
-        <v>-494.746794</v>
+        <v>-504.9669555</v>
       </c>
       <c r="Q58">
-        <v>-493.889794</v>
+        <v>-504.1099555</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1507542616074577</v>
+        <v>0.1531950583890265</v>
       </c>
       <c r="T58">
-        <v>1.623609047612323</v>
+        <v>1.661367397556796</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.03388883143941931</v>
+        <v>0.03329429053697336</v>
       </c>
       <c r="W58">
-        <v>0.2278090135465849</v>
+        <v>0.2279492062913817</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.1355553257576773</v>
+        <v>0.1331771621478934</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.195804922693369</v>
+        <v>0.197704922693369</v>
       </c>
       <c r="C59">
-        <v>-1230.959361461927</v>
+        <v>-1309.850943664716</v>
       </c>
       <c r="D59">
-        <v>1687.070638538073</v>
+        <v>1665.969056335285</v>
       </c>
       <c r="E59">
-        <v>2715.83</v>
+        <v>2773.620000000001</v>
       </c>
       <c r="F59">
-        <v>3294.03</v>
+        <v>3351.820000000001</v>
       </c>
       <c r="G59">
         <v>376</v>
@@ -6125,37 +6125,37 @@
         <v>103.443</v>
       </c>
       <c r="M59">
-        <v>776.7322740000001</v>
+        <v>790.3591560000002</v>
       </c>
       <c r="N59">
-        <v>-673.2892740000001</v>
+        <v>-686.9161560000002</v>
       </c>
       <c r="O59">
-        <v>-168.3223185</v>
+        <v>-171.7290390000001</v>
       </c>
       <c r="P59">
-        <v>-504.9669555</v>
+        <v>-515.1871170000002</v>
       </c>
       <c r="Q59">
-        <v>-504.1099555</v>
+        <v>-514.3301170000002</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1531950583890265</v>
+        <v>0.1557520835887652</v>
       </c>
       <c r="T59">
-        <v>1.661367397556796</v>
+        <v>1.700923764165291</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.03329429053697336</v>
+        <v>0.03272025104495657</v>
       </c>
       <c r="W59">
-        <v>0.2279492062913817</v>
+        <v>0.2280845648035993</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.1331771621478934</v>
+        <v>0.1308810041798263</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.197704922693369</v>
+        <v>0.1996049226933689</v>
       </c>
       <c r="C60">
-        <v>-1309.850943664714</v>
+        <v>-1388.221177064315</v>
       </c>
       <c r="D60">
-        <v>1665.969056335285</v>
+        <v>1645.388822935685</v>
       </c>
       <c r="E60">
-        <v>2773.62</v>
+        <v>2831.41</v>
       </c>
       <c r="F60">
-        <v>3351.82</v>
+        <v>3409.61</v>
       </c>
       <c r="G60">
         <v>376</v>
@@ -6207,37 +6207,37 @@
         <v>103.443</v>
       </c>
       <c r="M60">
-        <v>790.359156</v>
+        <v>803.986038</v>
       </c>
       <c r="N60">
-        <v>-686.916156</v>
+        <v>-700.543038</v>
       </c>
       <c r="O60">
-        <v>-171.729039</v>
+        <v>-175.1357595</v>
       </c>
       <c r="P60">
-        <v>-515.1871169999999</v>
+        <v>-525.4072785000001</v>
       </c>
       <c r="Q60">
-        <v>-514.330117</v>
+        <v>-524.5502785000001</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1557520835887652</v>
+        <v>0.1584338417250765</v>
       </c>
       <c r="T60">
-        <v>1.700923764165291</v>
+        <v>1.742409709632737</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.03272025104495658</v>
+        <v>0.03216567051877087</v>
       </c>
       <c r="W60">
-        <v>0.2280845648035993</v>
+        <v>0.2282153348916738</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.1308810041798263</v>
+        <v>0.1286626820750835</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1996049226933689</v>
+        <v>0.2015049226933689</v>
       </c>
       <c r="C61">
-        <v>-1388.221177064315</v>
+        <v>-1466.089147044329</v>
       </c>
       <c r="D61">
-        <v>1645.388822935685</v>
+        <v>1625.310852955671</v>
       </c>
       <c r="E61">
-        <v>2831.41</v>
+        <v>2889.2</v>
       </c>
       <c r="F61">
-        <v>3409.61</v>
+        <v>3467.4</v>
       </c>
       <c r="G61">
         <v>376</v>
@@ -6289,37 +6289,37 @@
         <v>103.443</v>
       </c>
       <c r="M61">
-        <v>803.986038</v>
+        <v>817.61292</v>
       </c>
       <c r="N61">
-        <v>-700.543038</v>
+        <v>-714.16992</v>
       </c>
       <c r="O61">
-        <v>-175.1357595</v>
+        <v>-178.54248</v>
       </c>
       <c r="P61">
-        <v>-525.4072785000001</v>
+        <v>-535.62744</v>
       </c>
       <c r="Q61">
-        <v>-524.5502785000001</v>
+        <v>-534.77044</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1584338417250765</v>
+        <v>0.1612496877682035</v>
       </c>
       <c r="T61">
-        <v>1.742409709632737</v>
+        <v>1.785969952373555</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.03216567051877087</v>
+        <v>0.03162957601012469</v>
       </c>
       <c r="W61">
-        <v>0.2282153348916738</v>
+        <v>0.2283417459768126</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.1286626820750835</v>
+        <v>0.1265183040404988</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.2015049226933689</v>
+        <v>0.203404922693369</v>
       </c>
       <c r="C62">
-        <v>-1466.089147044329</v>
+        <v>-1543.473018655966</v>
       </c>
       <c r="D62">
-        <v>1625.310852955671</v>
+        <v>1605.716981344034</v>
       </c>
       <c r="E62">
-        <v>2889.2</v>
+        <v>2946.99</v>
       </c>
       <c r="F62">
-        <v>3467.4</v>
+        <v>3525.19</v>
       </c>
       <c r="G62">
         <v>376</v>
@@ -6371,37 +6371,37 @@
         <v>103.443</v>
       </c>
       <c r="M62">
-        <v>817.61292</v>
+        <v>831.2398020000001</v>
       </c>
       <c r="N62">
-        <v>-714.16992</v>
+        <v>-727.7968020000001</v>
       </c>
       <c r="O62">
-        <v>-178.54248</v>
+        <v>-181.9492005</v>
       </c>
       <c r="P62">
-        <v>-535.62744</v>
+        <v>-545.8476015000001</v>
       </c>
       <c r="Q62">
-        <v>-534.77044</v>
+        <v>-544.9906015000001</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1612496877682035</v>
+        <v>0.1642099361725164</v>
       </c>
       <c r="T62">
-        <v>1.785969952373555</v>
+        <v>1.831764053716467</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.03162957601012469</v>
+        <v>0.03111105837061445</v>
       </c>
       <c r="W62">
-        <v>0.2283417459768126</v>
+        <v>0.2284640124362091</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.1265183040404988</v>
+        <v>0.1244442334824578</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.203404922693369</v>
+        <v>0.2053049226933689</v>
       </c>
       <c r="C63">
-        <v>-1543.473018655966</v>
+        <v>-1620.390091432388</v>
       </c>
       <c r="D63">
-        <v>1605.716981344034</v>
+        <v>1586.589908567612</v>
       </c>
       <c r="E63">
-        <v>2946.99</v>
+        <v>3004.78</v>
       </c>
       <c r="F63">
-        <v>3525.19</v>
+        <v>3582.98</v>
       </c>
       <c r="G63">
         <v>376</v>
@@ -6453,37 +6453,37 @@
         <v>103.443</v>
       </c>
       <c r="M63">
-        <v>831.2398020000001</v>
+        <v>844.8666840000001</v>
       </c>
       <c r="N63">
-        <v>-727.7968020000001</v>
+        <v>-741.4236840000001</v>
       </c>
       <c r="O63">
-        <v>-181.9492005</v>
+        <v>-185.355921</v>
       </c>
       <c r="P63">
-        <v>-545.8476015000001</v>
+        <v>-556.067763</v>
       </c>
       <c r="Q63">
-        <v>-544.9906015000001</v>
+        <v>-555.210763</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1642099361725164</v>
+        <v>0.1673259871244247</v>
       </c>
       <c r="T63">
-        <v>1.831764053716467</v>
+        <v>1.879968370919532</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.03111105837061445</v>
+        <v>0.03060926710657228</v>
       </c>
       <c r="W63">
-        <v>0.2284640124362091</v>
+        <v>0.2285823348162703</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.1244442334824578</v>
+        <v>0.1224370684262891</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.2053049226933689</v>
+        <v>0.207204922693369</v>
       </c>
       <c r="C64">
-        <v>-1620.390091432388</v>
+        <v>-1696.856850331528</v>
       </c>
       <c r="D64">
-        <v>1586.589908567612</v>
+        <v>1567.913149668472</v>
       </c>
       <c r="E64">
-        <v>3004.78</v>
+        <v>3062.57</v>
       </c>
       <c r="F64">
-        <v>3582.98</v>
+        <v>3640.77</v>
       </c>
       <c r="G64">
         <v>376</v>
@@ -6535,37 +6535,37 @@
         <v>103.443</v>
       </c>
       <c r="M64">
-        <v>844.8666840000001</v>
+        <v>858.493566</v>
       </c>
       <c r="N64">
-        <v>-741.4236840000001</v>
+        <v>-755.050566</v>
       </c>
       <c r="O64">
-        <v>-185.355921</v>
+        <v>-188.7626415</v>
       </c>
       <c r="P64">
-        <v>-556.067763</v>
+        <v>-566.2879245</v>
       </c>
       <c r="Q64">
-        <v>-555.210763</v>
+        <v>-565.4309245000001</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1673259871244247</v>
+        <v>0.1706104732629227</v>
       </c>
       <c r="T64">
-        <v>1.879968370919532</v>
+        <v>1.93077832689033</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.03060926710657228</v>
+        <v>0.03012340572392828</v>
       </c>
       <c r="W64">
-        <v>0.2285823348162703</v>
+        <v>0.2286969009302977</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.1224370684262891</v>
+        <v>0.1204936228957131</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.207204922693369</v>
+        <v>0.2091049226933689</v>
       </c>
       <c r="C65">
-        <v>-1696.856850331528</v>
+        <v>-1772.889013122687</v>
       </c>
       <c r="D65">
-        <v>1567.913149668472</v>
+        <v>1549.670986877313</v>
       </c>
       <c r="E65">
-        <v>3062.57</v>
+        <v>3120.36</v>
       </c>
       <c r="F65">
-        <v>3640.77</v>
+        <v>3698.56</v>
       </c>
       <c r="G65">
         <v>376</v>
@@ -6617,37 +6617,37 @@
         <v>103.443</v>
       </c>
       <c r="M65">
-        <v>858.493566</v>
+        <v>872.120448</v>
       </c>
       <c r="N65">
-        <v>-755.050566</v>
+        <v>-768.677448</v>
       </c>
       <c r="O65">
-        <v>-188.7626415</v>
+        <v>-192.169362</v>
       </c>
       <c r="P65">
-        <v>-566.2879245</v>
+        <v>-576.508086</v>
       </c>
       <c r="Q65">
-        <v>-565.4309245000001</v>
+        <v>-575.6510860000001</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1706104732629227</v>
+        <v>0.1740774308535594</v>
       </c>
       <c r="T65">
-        <v>1.93077832689033</v>
+        <v>1.98441105819284</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.03012340572392828</v>
+        <v>0.0296527275094919</v>
       </c>
       <c r="W65">
-        <v>0.2286969009302977</v>
+        <v>0.2288078868532618</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.1204936228957131</v>
+        <v>0.1186109100379675</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.2091049226933689</v>
+        <v>0.211004922693369</v>
       </c>
       <c r="C66">
-        <v>-1772.889013122687</v>
+        <v>-1848.501574503209</v>
       </c>
       <c r="D66">
-        <v>1549.670986877313</v>
+        <v>1531.848425496791</v>
       </c>
       <c r="E66">
-        <v>3120.36</v>
+        <v>3178.15</v>
       </c>
       <c r="F66">
-        <v>3698.56</v>
+        <v>3756.35</v>
       </c>
       <c r="G66">
         <v>376</v>
@@ -6699,37 +6699,37 @@
         <v>103.443</v>
       </c>
       <c r="M66">
-        <v>872.120448</v>
+        <v>885.74733</v>
       </c>
       <c r="N66">
-        <v>-768.677448</v>
+        <v>-782.30433</v>
       </c>
       <c r="O66">
-        <v>-192.169362</v>
+        <v>-195.5760825</v>
       </c>
       <c r="P66">
-        <v>-576.508086</v>
+        <v>-586.7282475000001</v>
       </c>
       <c r="Q66">
-        <v>-575.6510860000001</v>
+        <v>-585.8712475000001</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1740774308535594</v>
+        <v>0.1777425003065183</v>
       </c>
       <c r="T66">
-        <v>1.98441105819284</v>
+        <v>2.041108516998349</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.0296527275094919</v>
+        <v>0.02919653170165356</v>
       </c>
       <c r="W66">
-        <v>0.2288078868532618</v>
+        <v>0.2289154578247501</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.1186109100379675</v>
+        <v>0.1167861268066143</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.211004922693369</v>
+        <v>0.212904922693369</v>
       </c>
       <c r="C67">
-        <v>-1848.501574503209</v>
+        <v>-1923.70884720549</v>
       </c>
       <c r="D67">
-        <v>1531.848425496791</v>
+        <v>1514.431152794511</v>
       </c>
       <c r="E67">
-        <v>3178.15</v>
+        <v>3235.940000000001</v>
       </c>
       <c r="F67">
-        <v>3756.35</v>
+        <v>3814.14</v>
       </c>
       <c r="G67">
         <v>376</v>
@@ -6781,37 +6781,37 @@
         <v>103.443</v>
       </c>
       <c r="M67">
-        <v>885.74733</v>
+        <v>899.3742120000002</v>
       </c>
       <c r="N67">
-        <v>-782.30433</v>
+        <v>-795.9312120000002</v>
       </c>
       <c r="O67">
-        <v>-195.5760825</v>
+        <v>-198.982803</v>
       </c>
       <c r="P67">
-        <v>-586.7282475000001</v>
+        <v>-596.9484090000001</v>
       </c>
       <c r="Q67">
-        <v>-585.8712475000001</v>
+        <v>-596.0914090000001</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1777425003065183</v>
+        <v>0.1816231620802394</v>
       </c>
       <c r="T67">
-        <v>2.041108516998349</v>
+        <v>2.101141120439477</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.02919653170165356</v>
+        <v>0.02875416000920426</v>
       </c>
       <c r="W67">
-        <v>0.2289154578247501</v>
+        <v>0.2290197690698297</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.1167861268066143</v>
+        <v>0.115016640036817</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.212904922693369</v>
+        <v>0.214804922693369</v>
       </c>
       <c r="C68">
-        <v>-1923.70884720549</v>
+        <v>-1998.524500331169</v>
       </c>
       <c r="D68">
-        <v>1514.431152794511</v>
+        <v>1497.405499668831</v>
       </c>
       <c r="E68">
-        <v>3235.940000000001</v>
+        <v>3293.73</v>
       </c>
       <c r="F68">
-        <v>3814.14</v>
+        <v>3871.93</v>
       </c>
       <c r="G68">
         <v>376</v>
@@ -6863,37 +6863,37 @@
         <v>103.443</v>
       </c>
       <c r="M68">
-        <v>899.3742120000002</v>
+        <v>913.0010940000001</v>
       </c>
       <c r="N68">
-        <v>-795.9312120000002</v>
+        <v>-809.5580940000001</v>
       </c>
       <c r="O68">
-        <v>-198.982803</v>
+        <v>-202.3895235</v>
       </c>
       <c r="P68">
-        <v>-596.9484090000001</v>
+        <v>-607.1685705000001</v>
       </c>
       <c r="Q68">
-        <v>-596.0914090000001</v>
+        <v>-606.3115705000001</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1816231620802394</v>
+        <v>0.1857390154766103</v>
       </c>
       <c r="T68">
-        <v>2.101141120439477</v>
+        <v>2.164812063483098</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.02875416000920426</v>
+        <v>0.02832499344190271</v>
       </c>
       <c r="W68">
-        <v>0.2290197690698297</v>
+        <v>0.2291209665463994</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.115016640036817</v>
+        <v>0.1132999737676108</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.214804922693369</v>
+        <v>0.216704922693369</v>
       </c>
       <c r="C69">
-        <v>-1998.524500331169</v>
+        <v>-2072.961595128288</v>
       </c>
       <c r="D69">
-        <v>1497.405499668831</v>
+        <v>1480.758404871712</v>
       </c>
       <c r="E69">
-        <v>3293.73</v>
+        <v>3351.52</v>
       </c>
       <c r="F69">
-        <v>3871.93</v>
+        <v>3929.72</v>
       </c>
       <c r="G69">
         <v>376</v>
@@ -6945,37 +6945,37 @@
         <v>103.443</v>
       </c>
       <c r="M69">
-        <v>913.0010940000001</v>
+        <v>926.6279760000001</v>
       </c>
       <c r="N69">
-        <v>-809.5580940000001</v>
+        <v>-823.1849760000001</v>
       </c>
       <c r="O69">
-        <v>-202.3895235</v>
+        <v>-205.796244</v>
       </c>
       <c r="P69">
-        <v>-607.1685705000001</v>
+        <v>-617.3887320000001</v>
       </c>
       <c r="Q69">
-        <v>-606.3115705000001</v>
+        <v>-616.5317320000001</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1857390154766103</v>
+        <v>0.1901121097102544</v>
       </c>
       <c r="T69">
-        <v>2.164812063483098</v>
+        <v>2.232462440466945</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.02832499344190271</v>
+        <v>0.02790844942069826</v>
       </c>
       <c r="W69">
-        <v>0.2291209665463994</v>
+        <v>0.2292191876265994</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.1132999737676108</v>
+        <v>0.111633797682793</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.216704922693369</v>
+        <v>0.218604922693369</v>
       </c>
       <c r="C70">
-        <v>-2072.961595128288</v>
+        <v>-2147.032618408212</v>
       </c>
       <c r="D70">
-        <v>1480.758404871712</v>
+        <v>1464.477381591788</v>
       </c>
       <c r="E70">
-        <v>3351.52</v>
+        <v>3409.31</v>
       </c>
       <c r="F70">
-        <v>3929.72</v>
+        <v>3987.51</v>
       </c>
       <c r="G70">
         <v>376</v>
@@ -7027,37 +7027,37 @@
         <v>103.443</v>
       </c>
       <c r="M70">
-        <v>926.6279760000001</v>
+        <v>940.2548580000001</v>
       </c>
       <c r="N70">
-        <v>-823.1849760000001</v>
+        <v>-836.8118580000001</v>
       </c>
       <c r="O70">
-        <v>-205.796244</v>
+        <v>-209.2029645</v>
       </c>
       <c r="P70">
-        <v>-617.3887320000001</v>
+        <v>-627.6088935000001</v>
       </c>
       <c r="Q70">
-        <v>-616.5317320000001</v>
+        <v>-626.7518935000002</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1901121097102544</v>
+        <v>0.1947673390557464</v>
       </c>
       <c r="T70">
-        <v>2.232462440466945</v>
+        <v>2.304477357901363</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.02790844942069826</v>
+        <v>0.02750397913923886</v>
       </c>
       <c r="W70">
-        <v>0.2292191876265994</v>
+        <v>0.2293145617189675</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.111633797682793</v>
+        <v>0.1100159165569554</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.218604922693369</v>
+        <v>0.220504922693369</v>
       </c>
       <c r="C71">
-        <v>-2147.032618408212</v>
+        <v>-2220.749513782008</v>
       </c>
       <c r="D71">
-        <v>1464.477381591788</v>
+        <v>1448.550486217992</v>
       </c>
       <c r="E71">
-        <v>3409.31</v>
+        <v>3467.1</v>
       </c>
       <c r="F71">
-        <v>3987.51</v>
+        <v>4045.3</v>
       </c>
       <c r="G71">
         <v>376</v>
@@ -7109,37 +7109,37 @@
         <v>103.443</v>
       </c>
       <c r="M71">
-        <v>940.2548580000001</v>
+        <v>953.88174</v>
       </c>
       <c r="N71">
-        <v>-836.8118580000001</v>
+        <v>-850.4387400000001</v>
       </c>
       <c r="O71">
-        <v>-209.2029645</v>
+        <v>-212.609685</v>
       </c>
       <c r="P71">
-        <v>-627.6088935000001</v>
+        <v>-637.829055</v>
       </c>
       <c r="Q71">
-        <v>-626.7518935000002</v>
+        <v>-636.9720550000001</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1947673390557464</v>
+        <v>0.1997329170242713</v>
       </c>
       <c r="T71">
-        <v>2.304477357901363</v>
+        <v>2.381293269831408</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.02750397913923886</v>
+        <v>0.02711106515153545</v>
       </c>
       <c r="W71">
-        <v>0.2293145617189675</v>
+        <v>0.2294072108372679</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.1100159165569554</v>
+        <v>0.1084442606061418</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.220504922693369</v>
+        <v>0.222404922693369</v>
       </c>
       <c r="C72">
-        <v>-2220.749513782008</v>
+        <v>-2294.123710880482</v>
       </c>
       <c r="D72">
-        <v>1448.550486217992</v>
+        <v>1432.966289119518</v>
       </c>
       <c r="E72">
-        <v>3467.1</v>
+        <v>3524.89</v>
       </c>
       <c r="F72">
-        <v>4045.3</v>
+        <v>4103.09</v>
       </c>
       <c r="G72">
         <v>376</v>
@@ -7191,37 +7191,37 @@
         <v>103.443</v>
       </c>
       <c r="M72">
-        <v>953.88174</v>
+        <v>967.5086220000001</v>
       </c>
       <c r="N72">
-        <v>-850.4387400000001</v>
+        <v>-864.0656220000001</v>
       </c>
       <c r="O72">
-        <v>-212.609685</v>
+        <v>-216.0164055</v>
       </c>
       <c r="P72">
-        <v>-637.829055</v>
+        <v>-648.0492165000001</v>
       </c>
       <c r="Q72">
-        <v>-636.9720550000001</v>
+        <v>-647.1922165000001</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1997329170242713</v>
+        <v>0.205040948645798</v>
       </c>
       <c r="T72">
-        <v>2.381293269831408</v>
+        <v>2.463406830860078</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.02711106515153545</v>
+        <v>0.02672921916348565</v>
       </c>
       <c r="W72">
-        <v>0.2294072108372679</v>
+        <v>0.2294972501212501</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.1084442606061418</v>
+        <v>0.1069168766539426</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2224049226933689</v>
+        <v>0.2243049226933689</v>
       </c>
       <c r="C73">
-        <v>-2294.123710880482</v>
+        <v>-2367.166152708116</v>
       </c>
       <c r="D73">
-        <v>1432.966289119518</v>
+        <v>1417.713847291884</v>
       </c>
       <c r="E73">
-        <v>3524.89</v>
+        <v>3582.68</v>
       </c>
       <c r="F73">
-        <v>4103.09</v>
+        <v>4160.88</v>
       </c>
       <c r="G73">
         <v>376</v>
@@ -7273,37 +7273,37 @@
         <v>103.443</v>
       </c>
       <c r="M73">
-        <v>967.5086220000001</v>
+        <v>981.1355040000001</v>
       </c>
       <c r="N73">
-        <v>-864.0656220000001</v>
+        <v>-877.6925040000001</v>
       </c>
       <c r="O73">
-        <v>-216.0164055</v>
+        <v>-219.423126</v>
       </c>
       <c r="P73">
-        <v>-648.0492165000001</v>
+        <v>-658.2693780000001</v>
       </c>
       <c r="Q73">
-        <v>-647.1922165000001</v>
+        <v>-657.4123780000001</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2050409486457979</v>
+        <v>0.2107281253831478</v>
       </c>
       <c r="T73">
-        <v>2.463406830860076</v>
+        <v>2.551385646247937</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.02672921916348565</v>
+        <v>0.02635798000843724</v>
       </c>
       <c r="W73">
-        <v>0.2294972501212501</v>
+        <v>0.2295847883140105</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.1069168766539426</v>
+        <v>0.1054319200337489</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2243049226933689</v>
+        <v>0.226204922693369</v>
       </c>
       <c r="C74">
-        <v>-2367.166152708116</v>
+        <v>-2439.887321268483</v>
       </c>
       <c r="D74">
-        <v>1417.713847291884</v>
+        <v>1402.782678731517</v>
       </c>
       <c r="E74">
-        <v>3582.68</v>
+        <v>3640.47</v>
       </c>
       <c r="F74">
-        <v>4160.88</v>
+        <v>4218.67</v>
       </c>
       <c r="G74">
         <v>376</v>
@@ -7355,37 +7355,37 @@
         <v>103.443</v>
       </c>
       <c r="M74">
-        <v>981.1355040000001</v>
+        <v>994.7623860000001</v>
       </c>
       <c r="N74">
-        <v>-877.6925040000001</v>
+        <v>-891.3193860000001</v>
       </c>
       <c r="O74">
-        <v>-219.423126</v>
+        <v>-222.8298465</v>
       </c>
       <c r="P74">
-        <v>-658.2693780000001</v>
+        <v>-668.4895395000001</v>
       </c>
       <c r="Q74">
-        <v>-657.4123780000001</v>
+        <v>-667.6325395000001</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2107281253831478</v>
+        <v>0.2168365744714126</v>
       </c>
       <c r="T74">
-        <v>2.551385646247937</v>
+        <v>2.645881410923786</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.02635798000843724</v>
+        <v>0.02599691178914358</v>
       </c>
       <c r="W74">
-        <v>0.2295847883140105</v>
+        <v>0.22966992820012</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.1054319200337489</v>
+        <v>0.1039876471565743</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.226204922693369</v>
+        <v>0.228104922693369</v>
       </c>
       <c r="C75">
-        <v>-2439.887321268483</v>
+        <v>-2512.297261587225</v>
       </c>
       <c r="D75">
-        <v>1402.782678731517</v>
+        <v>1388.162738412775</v>
       </c>
       <c r="E75">
-        <v>3640.47</v>
+        <v>3698.26</v>
       </c>
       <c r="F75">
-        <v>4218.67</v>
+        <v>4276.46</v>
       </c>
       <c r="G75">
         <v>376</v>
@@ -7437,37 +7437,37 @@
         <v>103.443</v>
       </c>
       <c r="M75">
-        <v>994.7623860000001</v>
+        <v>1008.389268</v>
       </c>
       <c r="N75">
-        <v>-891.3193860000001</v>
+        <v>-904.946268</v>
       </c>
       <c r="O75">
-        <v>-222.8298465</v>
+        <v>-226.236567</v>
       </c>
       <c r="P75">
-        <v>-668.4895395000001</v>
+        <v>-678.709701</v>
       </c>
       <c r="Q75">
-        <v>-667.6325395000001</v>
+        <v>-677.852701</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2168365744714126</v>
+        <v>0.2234149042587746</v>
       </c>
       <c r="T75">
-        <v>2.645881410923786</v>
+        <v>2.747646080574701</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.02599691178914358</v>
+        <v>0.02564560217037137</v>
       </c>
       <c r="W75">
-        <v>0.22966992820012</v>
+        <v>0.2297527670082264</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.1039876471565743</v>
+        <v>0.1025824086814855</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.228104922693369</v>
+        <v>0.230004922693369</v>
       </c>
       <c r="C76">
-        <v>-2512.297261587225</v>
+        <v>-2584.40560424832</v>
       </c>
       <c r="D76">
-        <v>1388.162738412775</v>
+        <v>1373.84439575168</v>
       </c>
       <c r="E76">
-        <v>3698.26</v>
+        <v>3756.05</v>
       </c>
       <c r="F76">
-        <v>4276.46</v>
+        <v>4334.25</v>
       </c>
       <c r="G76">
         <v>376</v>
@@ -7519,37 +7519,37 @@
         <v>103.443</v>
       </c>
       <c r="M76">
-        <v>1008.389268</v>
+        <v>1022.01615</v>
       </c>
       <c r="N76">
-        <v>-904.946268</v>
+        <v>-918.5731500000001</v>
       </c>
       <c r="O76">
-        <v>-226.236567</v>
+        <v>-229.6432875</v>
       </c>
       <c r="P76">
-        <v>-678.709701</v>
+        <v>-688.9298625</v>
       </c>
       <c r="Q76">
-        <v>-677.852701</v>
+        <v>-688.0728625</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2234149042587746</v>
+        <v>0.2305195004291256</v>
       </c>
       <c r="T76">
-        <v>2.747646080574701</v>
+        <v>2.857551923797689</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.02564560217037137</v>
+        <v>0.02530366080809975</v>
       </c>
       <c r="W76">
-        <v>0.2297527670082264</v>
+        <v>0.2298333967814501</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.1025824086814855</v>
+        <v>0.101214643232399</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.230004922693369</v>
+        <v>0.231904922693369</v>
       </c>
       <c r="C77">
-        <v>-2584.40560424832</v>
+        <v>-2656.221586549869</v>
       </c>
       <c r="D77">
-        <v>1373.84439575168</v>
+        <v>1359.818413450131</v>
       </c>
       <c r="E77">
-        <v>3756.05</v>
+        <v>3813.84</v>
       </c>
       <c r="F77">
-        <v>4334.25</v>
+        <v>4392.04</v>
       </c>
       <c r="G77">
         <v>376</v>
@@ -7601,37 +7601,37 @@
         <v>103.443</v>
       </c>
       <c r="M77">
-        <v>1022.01615</v>
+        <v>1035.643032</v>
       </c>
       <c r="N77">
-        <v>-918.5731500000001</v>
+        <v>-932.200032</v>
       </c>
       <c r="O77">
-        <v>-229.6432875</v>
+        <v>-233.050008</v>
       </c>
       <c r="P77">
-        <v>-688.9298625</v>
+        <v>-699.150024</v>
       </c>
       <c r="Q77">
-        <v>-688.0728625</v>
+        <v>-698.2930240000001</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2305195004291256</v>
+        <v>0.2382161462803392</v>
       </c>
       <c r="T77">
-        <v>2.857551923797689</v>
+        <v>2.97661658728926</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.02530366080809975</v>
+        <v>0.02497071790273002</v>
       </c>
       <c r="W77">
-        <v>0.2298333967814501</v>
+        <v>0.2299119047185363</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.101214643232399</v>
+        <v>0.09988287161092002</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.231904922693369</v>
+        <v>0.233804922693369</v>
       </c>
       <c r="C78">
-        <v>-2656.221586549869</v>
+        <v>-2727.754072377057</v>
       </c>
       <c r="D78">
-        <v>1359.818413450131</v>
+        <v>1346.075927622943</v>
       </c>
       <c r="E78">
-        <v>3813.84</v>
+        <v>3871.63</v>
       </c>
       <c r="F78">
-        <v>4392.04</v>
+        <v>4449.83</v>
       </c>
       <c r="G78">
         <v>376</v>
@@ -7683,37 +7683,37 @@
         <v>103.443</v>
       </c>
       <c r="M78">
-        <v>1035.643032</v>
+        <v>1049.269914</v>
       </c>
       <c r="N78">
-        <v>-932.200032</v>
+        <v>-945.826914</v>
       </c>
       <c r="O78">
-        <v>-233.050008</v>
+        <v>-236.4567285</v>
       </c>
       <c r="P78">
-        <v>-699.150024</v>
+        <v>-709.3701854999999</v>
       </c>
       <c r="Q78">
-        <v>-698.2930240000001</v>
+        <v>-708.5131855</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2382161462803392</v>
+        <v>0.2465820656838322</v>
       </c>
       <c r="T78">
-        <v>2.97661658728926</v>
+        <v>3.106034699780097</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.02497071790273002</v>
+        <v>0.02464642286503223</v>
       </c>
       <c r="W78">
-        <v>0.2299119047185363</v>
+        <v>0.2299883734884254</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.09988287161092002</v>
+        <v>0.09858569146012885</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.233804922693369</v>
+        <v>0.235704922693369</v>
       </c>
       <c r="C79">
-        <v>-2727.754072377057</v>
+        <v>-2799.011570882154</v>
       </c>
       <c r="D79">
-        <v>1346.075927622943</v>
+        <v>1332.608429117846</v>
       </c>
       <c r="E79">
-        <v>3871.63</v>
+        <v>3929.42</v>
       </c>
       <c r="F79">
-        <v>4449.83</v>
+        <v>4507.62</v>
       </c>
       <c r="G79">
         <v>376</v>
@@ -7765,37 +7765,37 @@
         <v>103.443</v>
       </c>
       <c r="M79">
-        <v>1049.269914</v>
+        <v>1062.896796</v>
       </c>
       <c r="N79">
-        <v>-945.826914</v>
+        <v>-959.453796</v>
       </c>
       <c r="O79">
-        <v>-236.4567285</v>
+        <v>-239.863449</v>
       </c>
       <c r="P79">
-        <v>-709.3701854999999</v>
+        <v>-719.5903470000001</v>
       </c>
       <c r="Q79">
-        <v>-708.5131855</v>
+        <v>-718.7333470000001</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2465820656838322</v>
+        <v>0.2557085232149154</v>
       </c>
       <c r="T79">
-        <v>3.106034699780097</v>
+        <v>3.247218095224647</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.02464642286503223</v>
+        <v>0.0243304430847113</v>
       </c>
       <c r="W79">
-        <v>0.2299883734884254</v>
+        <v>0.2300628815206251</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.09858569146012885</v>
+        <v>0.0973217723388452</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.235704922693369</v>
+        <v>0.237604922693369</v>
       </c>
       <c r="C80">
-        <v>-2799.011570882154</v>
+        <v>-2870.002254054252</v>
       </c>
       <c r="D80">
-        <v>1332.608429117846</v>
+        <v>1319.407745945748</v>
       </c>
       <c r="E80">
-        <v>3929.42</v>
+        <v>3987.21</v>
       </c>
       <c r="F80">
-        <v>4507.62</v>
+        <v>4565.41</v>
       </c>
       <c r="G80">
         <v>376</v>
@@ -7847,37 +7847,37 @@
         <v>103.443</v>
       </c>
       <c r="M80">
-        <v>1062.896796</v>
+        <v>1076.523678</v>
       </c>
       <c r="N80">
-        <v>-959.453796</v>
+        <v>-973.080678</v>
       </c>
       <c r="O80">
-        <v>-239.863449</v>
+        <v>-243.2701695</v>
       </c>
       <c r="P80">
-        <v>-719.5903470000001</v>
+        <v>-729.8105085</v>
       </c>
       <c r="Q80">
-        <v>-718.7333470000001</v>
+        <v>-728.9535085</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2557085232149154</v>
+        <v>0.2657041671775305</v>
       </c>
       <c r="T80">
-        <v>3.247218095224647</v>
+        <v>3.401847528330583</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.0243304430847113</v>
+        <v>0.02402246279249977</v>
       </c>
       <c r="W80">
-        <v>0.2300628815206251</v>
+        <v>0.2301355032735286</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.0973217723388452</v>
+        <v>0.09608985116999902</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.237604922693369</v>
+        <v>0.239504922693369</v>
       </c>
       <c r="C81">
-        <v>-2870.002254054252</v>
+        <v>-2940.733973254984</v>
       </c>
       <c r="D81">
-        <v>1319.407745945748</v>
+        <v>1306.466026745016</v>
       </c>
       <c r="E81">
-        <v>3987.21</v>
+        <v>4045</v>
       </c>
       <c r="F81">
-        <v>4565.41</v>
+        <v>4623.2</v>
       </c>
       <c r="G81">
         <v>376</v>
@@ -7929,37 +7929,37 @@
         <v>103.443</v>
       </c>
       <c r="M81">
-        <v>1076.523678</v>
+        <v>1090.15056</v>
       </c>
       <c r="N81">
-        <v>-973.080678</v>
+        <v>-986.7075600000001</v>
       </c>
       <c r="O81">
-        <v>-243.2701695</v>
+        <v>-246.67689</v>
       </c>
       <c r="P81">
-        <v>-729.8105085</v>
+        <v>-740.0306700000001</v>
       </c>
       <c r="Q81">
-        <v>-728.9535085</v>
+        <v>-739.1736700000001</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2657041671775305</v>
+        <v>0.276699375536407</v>
       </c>
       <c r="T81">
-        <v>3.401847528330583</v>
+        <v>3.571939904747112</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.02402246279249977</v>
+        <v>0.02372218200759352</v>
       </c>
       <c r="W81">
-        <v>0.2301355032735286</v>
+        <v>0.2302063094826095</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.09608985116999902</v>
+        <v>0.09488872803037407</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.239504922693369</v>
+        <v>0.241404922693369</v>
       </c>
       <c r="C82">
-        <v>-2940.733973254984</v>
+        <v>-3011.214274790528</v>
       </c>
       <c r="D82">
-        <v>1306.466026745016</v>
+        <v>1293.775725209473</v>
       </c>
       <c r="E82">
-        <v>4045</v>
+        <v>4102.790000000001</v>
       </c>
       <c r="F82">
-        <v>4623.2</v>
+        <v>4680.990000000001</v>
       </c>
       <c r="G82">
         <v>376</v>
@@ -8011,37 +8011,37 @@
         <v>103.443</v>
       </c>
       <c r="M82">
-        <v>1090.15056</v>
+        <v>1103.777442</v>
       </c>
       <c r="N82">
-        <v>-986.7075600000001</v>
+        <v>-1000.334442</v>
       </c>
       <c r="O82">
-        <v>-246.67689</v>
+        <v>-250.0836105000001</v>
       </c>
       <c r="P82">
-        <v>-740.0306700000001</v>
+        <v>-750.2508315000002</v>
       </c>
       <c r="Q82">
-        <v>-739.1736700000001</v>
+        <v>-749.3938315000003</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.276699375536407</v>
+        <v>0.2888519742488495</v>
       </c>
       <c r="T82">
-        <v>3.571939904747112</v>
+        <v>3.759936741839066</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.02372218200759352</v>
+        <v>0.02342931556305532</v>
       </c>
       <c r="W82">
-        <v>0.2302063094826095</v>
+        <v>0.2302753673902316</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.09488872803037407</v>
+        <v>0.09371726225222132</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.241404922693369</v>
+        <v>0.243304922693369</v>
       </c>
       <c r="C83">
-        <v>-3011.214274790528</v>
+        <v>-3081.450414584797</v>
       </c>
       <c r="D83">
-        <v>1293.775725209473</v>
+        <v>1281.329585415204</v>
       </c>
       <c r="E83">
-        <v>4102.790000000001</v>
+        <v>4160.580000000001</v>
       </c>
       <c r="F83">
-        <v>4680.990000000001</v>
+        <v>4738.780000000001</v>
       </c>
       <c r="G83">
         <v>376</v>
@@ -8093,37 +8093,37 @@
         <v>103.443</v>
       </c>
       <c r="M83">
-        <v>1103.777442</v>
+        <v>1117.404324</v>
       </c>
       <c r="N83">
-        <v>-1000.334442</v>
+        <v>-1013.961324</v>
       </c>
       <c r="O83">
-        <v>-250.0836105000001</v>
+        <v>-253.490331</v>
       </c>
       <c r="P83">
-        <v>-750.2508315000002</v>
+        <v>-760.4709930000001</v>
       </c>
       <c r="Q83">
-        <v>-749.3938315000003</v>
+        <v>-759.6139930000002</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2888519742488495</v>
+        <v>0.3023548617071189</v>
       </c>
       <c r="T83">
-        <v>3.759936741839066</v>
+        <v>3.96882211638568</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.02342931556305532</v>
+        <v>0.02314359220253026</v>
       </c>
       <c r="W83">
-        <v>0.2302753673902316</v>
+        <v>0.2303427409586434</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.09371726225222132</v>
+        <v>0.09257436881012104</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.243304922693369</v>
+        <v>0.245204922693369</v>
       </c>
       <c r="C84">
-        <v>-3081.450414584797</v>
+        <v>-3151.44937201376</v>
       </c>
       <c r="D84">
-        <v>1281.329585415204</v>
+        <v>1269.120627986241</v>
       </c>
       <c r="E84">
-        <v>4160.580000000001</v>
+        <v>4218.370000000001</v>
       </c>
       <c r="F84">
-        <v>4738.780000000001</v>
+        <v>4796.570000000001</v>
       </c>
       <c r="G84">
         <v>376</v>
@@ -8175,37 +8175,37 @@
         <v>103.443</v>
       </c>
       <c r="M84">
-        <v>1117.404324</v>
+        <v>1131.031206</v>
       </c>
       <c r="N84">
-        <v>-1013.961324</v>
+        <v>-1027.588206</v>
       </c>
       <c r="O84">
-        <v>-253.490331</v>
+        <v>-256.8970515</v>
       </c>
       <c r="P84">
-        <v>-760.4709930000001</v>
+        <v>-770.6911545</v>
       </c>
       <c r="Q84">
-        <v>-759.6139930000002</v>
+        <v>-769.8341545000001</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3023548617071189</v>
+        <v>0.3174463241604789</v>
       </c>
       <c r="T84">
-        <v>3.96882211638568</v>
+        <v>4.202282240878956</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.02314359220253026</v>
+        <v>0.02286475374225881</v>
       </c>
       <c r="W84">
-        <v>0.2303427409586434</v>
+        <v>0.2304084910675754</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.09257436881012104</v>
+        <v>0.09145901496903519</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.245204922693369</v>
+        <v>0.247104922693369</v>
       </c>
       <c r="C85">
-        <v>-3151.44937201376</v>
+        <v>-3221.217862956312</v>
       </c>
       <c r="D85">
-        <v>1269.120627986241</v>
+        <v>1257.142137043688</v>
       </c>
       <c r="E85">
-        <v>4218.370000000001</v>
+        <v>4276.160000000001</v>
       </c>
       <c r="F85">
-        <v>4796.570000000001</v>
+        <v>4854.360000000001</v>
       </c>
       <c r="G85">
         <v>376</v>
@@ -8257,37 +8257,37 @@
         <v>103.443</v>
       </c>
       <c r="M85">
-        <v>1131.031206</v>
+        <v>1144.658088</v>
       </c>
       <c r="N85">
-        <v>-1027.588206</v>
+        <v>-1041.215088</v>
       </c>
       <c r="O85">
-        <v>-256.8970515</v>
+        <v>-260.303772</v>
       </c>
       <c r="P85">
-        <v>-770.6911545</v>
+        <v>-780.9113160000002</v>
       </c>
       <c r="Q85">
-        <v>-769.8341545000001</v>
+        <v>-780.0543160000002</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3174463241604789</v>
+        <v>0.3344242194205089</v>
       </c>
       <c r="T85">
-        <v>4.202282240878956</v>
+        <v>4.464924880933892</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.02286475374225881</v>
+        <v>0.02259255429294621</v>
       </c>
       <c r="W85">
-        <v>0.2304084910675754</v>
+        <v>0.2304726756977233</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.09145901496903519</v>
+        <v>0.09037021717178484</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.247104922693369</v>
+        <v>0.249004922693369</v>
       </c>
       <c r="C86">
-        <v>-3221.217862956311</v>
+        <v>-3290.76235211299</v>
       </c>
       <c r="D86">
-        <v>1257.142137043688</v>
+        <v>1245.387647887009</v>
       </c>
       <c r="E86">
-        <v>4276.16</v>
+        <v>4333.95</v>
       </c>
       <c r="F86">
-        <v>4854.36</v>
+        <v>4912.15</v>
       </c>
       <c r="G86">
         <v>376</v>
@@ -8339,37 +8339,37 @@
         <v>103.443</v>
       </c>
       <c r="M86">
-        <v>1144.658088</v>
+        <v>1158.28497</v>
       </c>
       <c r="N86">
-        <v>-1041.215088</v>
+        <v>-1054.84197</v>
       </c>
       <c r="O86">
-        <v>-260.303772</v>
+        <v>-263.7104925</v>
       </c>
       <c r="P86">
-        <v>-780.9113159999999</v>
+        <v>-791.1314775</v>
       </c>
       <c r="Q86">
-        <v>-780.054316</v>
+        <v>-790.2744775</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3344242194205087</v>
+        <v>0.3536658340485426</v>
       </c>
       <c r="T86">
-        <v>4.464924880933889</v>
+        <v>4.762586539662815</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.02259255429294621</v>
+        <v>0.02232675953655861</v>
       </c>
       <c r="W86">
-        <v>0.2304726756977233</v>
+        <v>0.2305353501012795</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.09037021717178484</v>
+        <v>0.08930703814623442</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.249004922693369</v>
+        <v>0.2509049226933689</v>
       </c>
       <c r="C87">
-        <v>-3290.76235211299</v>
+        <v>-3360.089064639987</v>
       </c>
       <c r="D87">
-        <v>1245.387647887009</v>
+        <v>1233.850935360013</v>
       </c>
       <c r="E87">
-        <v>4333.95</v>
+        <v>4391.74</v>
       </c>
       <c r="F87">
-        <v>4912.15</v>
+        <v>4969.94</v>
       </c>
       <c r="G87">
         <v>376</v>
@@ -8421,37 +8421,37 @@
         <v>103.443</v>
       </c>
       <c r="M87">
-        <v>1158.28497</v>
+        <v>1171.911852</v>
       </c>
       <c r="N87">
-        <v>-1054.84197</v>
+        <v>-1068.468852</v>
       </c>
       <c r="O87">
-        <v>-263.7104925</v>
+        <v>-267.117213</v>
       </c>
       <c r="P87">
-        <v>-791.1314775</v>
+        <v>-801.351639</v>
       </c>
       <c r="Q87">
-        <v>-790.2744775</v>
+        <v>-800.494639</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3536658340485426</v>
+        <v>0.3756562507662956</v>
       </c>
       <c r="T87">
-        <v>4.762586539662815</v>
+        <v>5.102771292495873</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.02232675953655861</v>
+        <v>0.02206714605357537</v>
       </c>
       <c r="W87">
-        <v>0.2305353501012795</v>
+        <v>0.2305965669605669</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.08930703814623442</v>
+        <v>0.0882685842143015</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2509049226933689</v>
+        <v>0.252804922693369</v>
       </c>
       <c r="C88">
-        <v>-3360.089064639987</v>
+        <v>-3429.20399714247</v>
       </c>
       <c r="D88">
-        <v>1233.850935360013</v>
+        <v>1222.52600285753</v>
       </c>
       <c r="E88">
-        <v>4391.74</v>
+        <v>4449.53</v>
       </c>
       <c r="F88">
-        <v>4969.94</v>
+        <v>5027.73</v>
       </c>
       <c r="G88">
         <v>376</v>
@@ -8503,37 +8503,37 @@
         <v>103.443</v>
       </c>
       <c r="M88">
-        <v>1171.911852</v>
+        <v>1185.538734</v>
       </c>
       <c r="N88">
-        <v>-1068.468852</v>
+        <v>-1082.095734</v>
       </c>
       <c r="O88">
-        <v>-267.117213</v>
+        <v>-270.5239335</v>
       </c>
       <c r="P88">
-        <v>-801.351639</v>
+        <v>-811.5718005</v>
       </c>
       <c r="Q88">
-        <v>-800.494639</v>
+        <v>-810.7148005</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3756562507662956</v>
+        <v>0.4010298085175491</v>
       </c>
       <c r="T88">
-        <v>5.102771292495873</v>
+        <v>5.495292161149401</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.02206714605357537</v>
+        <v>0.02181350069663772</v>
       </c>
       <c r="W88">
-        <v>0.2305965669605669</v>
+        <v>0.2306563765357328</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.0882685842143015</v>
+        <v>0.08725400278655082</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.252804922693369</v>
+        <v>0.254704922693369</v>
       </c>
       <c r="C89">
-        <v>-3429.20399714247</v>
+        <v>-3498.112928067993</v>
       </c>
       <c r="D89">
-        <v>1222.52600285753</v>
+        <v>1211.407071932007</v>
       </c>
       <c r="E89">
-        <v>4449.53</v>
+        <v>4507.320000000001</v>
       </c>
       <c r="F89">
-        <v>5027.73</v>
+        <v>5085.52</v>
       </c>
       <c r="G89">
         <v>376</v>
@@ -8585,37 +8585,37 @@
         <v>103.443</v>
       </c>
       <c r="M89">
-        <v>1185.538734</v>
+        <v>1199.165616</v>
       </c>
       <c r="N89">
-        <v>-1082.095734</v>
+        <v>-1095.722616</v>
       </c>
       <c r="O89">
-        <v>-270.5239335</v>
+        <v>-273.9306540000001</v>
       </c>
       <c r="P89">
-        <v>-811.5718005</v>
+        <v>-821.7919620000002</v>
       </c>
       <c r="Q89">
-        <v>-810.7148005</v>
+        <v>-820.9349620000003</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.4010298085175491</v>
+        <v>0.4306322925606783</v>
       </c>
       <c r="T89">
-        <v>5.495292161149401</v>
+        <v>5.953233174578519</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.02181350069663772</v>
+        <v>0.02156562000690319</v>
       </c>
       <c r="W89">
-        <v>0.2306563765357328</v>
+        <v>0.2307148268023722</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.08725400278655082</v>
+        <v>0.08626248002761272</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.254704922693369</v>
+        <v>0.256604922693369</v>
       </c>
       <c r="C90">
-        <v>-3498.112928067993</v>
+        <v>-3566.821427537851</v>
       </c>
       <c r="D90">
-        <v>1211.407071932007</v>
+        <v>1200.488572462149</v>
       </c>
       <c r="E90">
-        <v>4507.320000000001</v>
+        <v>4565.110000000001</v>
       </c>
       <c r="F90">
-        <v>5085.52</v>
+        <v>5143.31</v>
       </c>
       <c r="G90">
         <v>376</v>
@@ -8667,37 +8667,37 @@
         <v>103.443</v>
       </c>
       <c r="M90">
-        <v>1199.165616</v>
+        <v>1212.792498</v>
       </c>
       <c r="N90">
-        <v>-1095.722616</v>
+        <v>-1109.349498</v>
       </c>
       <c r="O90">
-        <v>-273.9306540000001</v>
+        <v>-277.3373745000001</v>
       </c>
       <c r="P90">
-        <v>-821.7919620000002</v>
+        <v>-832.0121235000001</v>
       </c>
       <c r="Q90">
-        <v>-820.9349620000003</v>
+        <v>-831.1551235000002</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4306322925606783</v>
+        <v>0.4656170464298309</v>
       </c>
       <c r="T90">
-        <v>5.953233174578519</v>
+        <v>6.494436190449294</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.02156562000690319</v>
+        <v>0.02132330966974698</v>
       </c>
       <c r="W90">
-        <v>0.2307148268023722</v>
+        <v>0.2307719635798737</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.08626248002761272</v>
+        <v>0.08529323867898786</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.256604922693369</v>
+        <v>0.2585049226933689</v>
       </c>
       <c r="C91">
-        <v>-3566.821427537851</v>
+        <v>-3635.334866651511</v>
       </c>
       <c r="D91">
-        <v>1200.488572462149</v>
+        <v>1189.76513334849</v>
       </c>
       <c r="E91">
-        <v>4565.110000000001</v>
+        <v>4622.900000000001</v>
       </c>
       <c r="F91">
-        <v>5143.31</v>
+        <v>5201.1</v>
       </c>
       <c r="G91">
         <v>376</v>
@@ -8749,37 +8749,37 @@
         <v>103.443</v>
       </c>
       <c r="M91">
-        <v>1212.792498</v>
+        <v>1226.41938</v>
       </c>
       <c r="N91">
-        <v>-1109.349498</v>
+        <v>-1122.97638</v>
       </c>
       <c r="O91">
-        <v>-277.3373745000001</v>
+        <v>-280.744095</v>
       </c>
       <c r="P91">
-        <v>-832.0121235000001</v>
+        <v>-842.232285</v>
       </c>
       <c r="Q91">
-        <v>-831.1551235000002</v>
+        <v>-841.3752850000001</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4656170464298309</v>
+        <v>0.507598751072814</v>
       </c>
       <c r="T91">
-        <v>6.494436190449294</v>
+        <v>7.143879809494225</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.02132330966974698</v>
+        <v>0.02108638400674979</v>
       </c>
       <c r="W91">
-        <v>0.2307719635798737</v>
+        <v>0.2308278306512084</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.08529323867898786</v>
+        <v>0.08434553602699912</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2585049226933689</v>
+        <v>0.260404922693369</v>
       </c>
       <c r="C92">
-        <v>-3635.334866651511</v>
+        <v>-3703.658426296794</v>
       </c>
       <c r="D92">
-        <v>1189.76513334849</v>
+        <v>1179.231573703206</v>
       </c>
       <c r="E92">
-        <v>4622.900000000001</v>
+        <v>4680.690000000001</v>
       </c>
       <c r="F92">
-        <v>5201.1</v>
+        <v>5258.89</v>
       </c>
       <c r="G92">
         <v>376</v>
@@ -8831,37 +8831,37 @@
         <v>103.443</v>
       </c>
       <c r="M92">
-        <v>1226.41938</v>
+        <v>1240.046262</v>
       </c>
       <c r="N92">
-        <v>-1122.97638</v>
+        <v>-1136.603262</v>
       </c>
       <c r="O92">
-        <v>-280.744095</v>
+        <v>-284.1508155</v>
       </c>
       <c r="P92">
-        <v>-842.232285</v>
+        <v>-852.4524465000001</v>
       </c>
       <c r="Q92">
-        <v>-841.3752850000001</v>
+        <v>-851.5954465000001</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.507598751072814</v>
+        <v>0.5589097234142378</v>
       </c>
       <c r="T92">
-        <v>7.143879809494225</v>
+        <v>7.937644232771361</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.02108638400674979</v>
+        <v>0.02085466550118112</v>
       </c>
       <c r="W92">
-        <v>0.2308278306512084</v>
+        <v>0.2308824698748215</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.08434553602699912</v>
+        <v>0.08341866200472448</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.260404922693369</v>
+        <v>0.2623049226933689</v>
       </c>
       <c r="C93">
-        <v>-3703.658426296794</v>
+        <v>-3771.797105496155</v>
       </c>
       <c r="D93">
-        <v>1179.231573703206</v>
+        <v>1168.882894503845</v>
       </c>
       <c r="E93">
-        <v>4680.690000000001</v>
+        <v>4738.48</v>
       </c>
       <c r="F93">
-        <v>5258.89</v>
+        <v>5316.68</v>
       </c>
       <c r="G93">
         <v>376</v>
@@ -8913,37 +8913,37 @@
         <v>103.443</v>
       </c>
       <c r="M93">
-        <v>1240.046262</v>
+        <v>1253.673144</v>
       </c>
       <c r="N93">
-        <v>-1136.603262</v>
+        <v>-1150.230144</v>
       </c>
       <c r="O93">
-        <v>-284.1508155</v>
+        <v>-287.557536</v>
       </c>
       <c r="P93">
-        <v>-852.4524465000001</v>
+        <v>-862.6726080000001</v>
       </c>
       <c r="Q93">
-        <v>-851.5954465000001</v>
+        <v>-861.8156080000001</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.5589097234142378</v>
+        <v>0.6230484388410176</v>
       </c>
       <c r="T93">
-        <v>7.937644232771361</v>
+        <v>8.929849761867782</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.02085466550118112</v>
+        <v>0.02062798435442914</v>
       </c>
       <c r="W93">
-        <v>0.2308824698748215</v>
+        <v>0.2309359212892256</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.08341866200472448</v>
+        <v>0.08251193741771656</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2623049226933689</v>
+        <v>0.264204922693369</v>
       </c>
       <c r="C94">
-        <v>-3771.797105496155</v>
+        <v>-3839.75572931731</v>
       </c>
       <c r="D94">
-        <v>1168.882894503845</v>
+        <v>1158.71427068269</v>
       </c>
       <c r="E94">
-        <v>4738.48</v>
+        <v>4796.27</v>
       </c>
       <c r="F94">
-        <v>5316.68</v>
+        <v>5374.47</v>
       </c>
       <c r="G94">
         <v>376</v>
@@ -8995,37 +8995,37 @@
         <v>103.443</v>
       </c>
       <c r="M94">
-        <v>1253.673144</v>
+        <v>1267.300026</v>
       </c>
       <c r="N94">
-        <v>-1150.230144</v>
+        <v>-1163.857026</v>
       </c>
       <c r="O94">
-        <v>-287.557536</v>
+        <v>-290.9642565</v>
       </c>
       <c r="P94">
-        <v>-862.6726080000001</v>
+        <v>-872.8927695000001</v>
       </c>
       <c r="Q94">
-        <v>-861.8156080000001</v>
+        <v>-872.0357695000001</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.6230484388410176</v>
+        <v>0.7055125015325917</v>
       </c>
       <c r="T94">
-        <v>8.929849761867782</v>
+        <v>10.20554258499175</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.02062798435442914</v>
+        <v>0.02040617807104819</v>
       </c>
       <c r="W94">
-        <v>0.2309359212892256</v>
+        <v>0.2309882232108469</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.08251193741771656</v>
+        <v>0.08162471228419277</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.264204922693369</v>
+        <v>0.2661049226933689</v>
       </c>
       <c r="C95">
-        <v>-3839.75572931731</v>
+        <v>-3907.538956374526</v>
       </c>
       <c r="D95">
-        <v>1158.71427068269</v>
+        <v>1148.721043625475</v>
       </c>
       <c r="E95">
-        <v>4796.27</v>
+        <v>4854.06</v>
       </c>
       <c r="F95">
-        <v>5374.47</v>
+        <v>5432.26</v>
       </c>
       <c r="G95">
         <v>376</v>
@@ -9077,37 +9077,37 @@
         <v>103.443</v>
       </c>
       <c r="M95">
-        <v>1267.300026</v>
+        <v>1280.926908</v>
       </c>
       <c r="N95">
-        <v>-1163.857026</v>
+        <v>-1177.483908</v>
       </c>
       <c r="O95">
-        <v>-290.9642565</v>
+        <v>-294.370977</v>
       </c>
       <c r="P95">
-        <v>-872.8927695000001</v>
+        <v>-883.1129310000001</v>
       </c>
       <c r="Q95">
-        <v>-872.0357695000001</v>
+        <v>-882.2559310000001</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.7055125015325917</v>
+        <v>0.8154645851213572</v>
       </c>
       <c r="T95">
-        <v>10.20554258499175</v>
+        <v>11.90646634915705</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.02040617807104819</v>
+        <v>0.02018909107029235</v>
       </c>
       <c r="W95">
-        <v>0.2309882232108469</v>
+        <v>0.2310394123256251</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.08162471228419277</v>
+        <v>0.08075636428116939</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2661049226933689</v>
+        <v>0.268004922693369</v>
       </c>
       <c r="C96">
-        <v>-3907.538956374526</v>
+        <v>-3975.151285945055</v>
       </c>
       <c r="D96">
-        <v>1148.721043625475</v>
+        <v>1138.898714054945</v>
       </c>
       <c r="E96">
-        <v>4854.06</v>
+        <v>4911.85</v>
       </c>
       <c r="F96">
-        <v>5432.26</v>
+        <v>5490.05</v>
       </c>
       <c r="G96">
         <v>376</v>
@@ -9159,37 +9159,37 @@
         <v>103.443</v>
       </c>
       <c r="M96">
-        <v>1280.926908</v>
+        <v>1294.55379</v>
       </c>
       <c r="N96">
-        <v>-1177.483908</v>
+        <v>-1191.11079</v>
       </c>
       <c r="O96">
-        <v>-294.370977</v>
+        <v>-297.7776975</v>
       </c>
       <c r="P96">
-        <v>-883.1129310000001</v>
+        <v>-893.3330925000001</v>
       </c>
       <c r="Q96">
-        <v>-882.2559310000001</v>
+        <v>-892.4760925000002</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.8154645851213572</v>
+        <v>0.9693975021456291</v>
       </c>
       <c r="T96">
-        <v>11.90646634915705</v>
+        <v>14.28775961898847</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.02018909107029235</v>
+        <v>0.01997657432218401</v>
       </c>
       <c r="W96">
-        <v>0.2310394123256251</v>
+        <v>0.231089523774829</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.08075636428116939</v>
+        <v>0.07990629728873599</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.268004922693369</v>
+        <v>0.269904922693369</v>
       </c>
       <c r="C97">
-        <v>-3975.151285945055</v>
+        <v>-4042.597064723575</v>
       </c>
       <c r="D97">
-        <v>1138.898714054945</v>
+        <v>1129.242935276425</v>
       </c>
       <c r="E97">
-        <v>4911.85</v>
+        <v>4969.64</v>
       </c>
       <c r="F97">
-        <v>5490.05</v>
+        <v>5547.84</v>
       </c>
       <c r="G97">
         <v>376</v>
@@ -9241,37 +9241,37 @@
         <v>103.443</v>
       </c>
       <c r="M97">
-        <v>1294.55379</v>
+        <v>1308.180672</v>
       </c>
       <c r="N97">
-        <v>-1191.11079</v>
+        <v>-1204.737672</v>
       </c>
       <c r="O97">
-        <v>-297.7776975</v>
+        <v>-301.1844180000001</v>
       </c>
       <c r="P97">
-        <v>-893.3330925000001</v>
+        <v>-903.5532540000002</v>
       </c>
       <c r="Q97">
-        <v>-892.4760925000002</v>
+        <v>-902.6962540000002</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.9693975021456291</v>
+        <v>1.200296877682037</v>
       </c>
       <c r="T97">
-        <v>14.28775961898847</v>
+        <v>17.85969952373559</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.01997657432218401</v>
+        <v>0.01976848500632793</v>
       </c>
       <c r="W97">
-        <v>0.231089523774829</v>
+        <v>0.2311385912355079</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.07990629728873599</v>
+        <v>0.07907394002531176</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.269904922693369</v>
+        <v>0.271804922693369</v>
       </c>
       <c r="C98">
-        <v>-4042.597064723575</v>
+        <v>-4109.88049323591</v>
       </c>
       <c r="D98">
-        <v>1129.242935276425</v>
+        <v>1119.74950676409</v>
       </c>
       <c r="E98">
-        <v>4969.64</v>
+        <v>5027.43</v>
       </c>
       <c r="F98">
-        <v>5547.84</v>
+        <v>5605.63</v>
       </c>
       <c r="G98">
         <v>376</v>
@@ -9323,37 +9323,37 @@
         <v>103.443</v>
       </c>
       <c r="M98">
-        <v>1308.180672</v>
+        <v>1321.807554</v>
       </c>
       <c r="N98">
-        <v>-1204.737672</v>
+        <v>-1218.364554</v>
       </c>
       <c r="O98">
-        <v>-301.1844180000001</v>
+        <v>-304.5911385</v>
       </c>
       <c r="P98">
-        <v>-903.5532540000002</v>
+        <v>-913.7734155000001</v>
       </c>
       <c r="Q98">
-        <v>-902.6962540000002</v>
+        <v>-912.9164155000001</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.200296877682034</v>
+        <v>1.585129170242712</v>
       </c>
       <c r="T98">
-        <v>17.85969952373554</v>
+        <v>23.81293269831406</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.01976848500632793</v>
+        <v>0.01956468619182971</v>
       </c>
       <c r="W98">
-        <v>0.2311385912355079</v>
+        <v>0.2311866469959666</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.07907394002531176</v>
+        <v>0.07825874476731887</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.271804922693369</v>
+        <v>0.2737049226933689</v>
       </c>
       <c r="C99">
-        <v>-4109.88049323591</v>
+        <v>-4177.005631931945</v>
       </c>
       <c r="D99">
-        <v>1119.74950676409</v>
+        <v>1110.414368068056</v>
       </c>
       <c r="E99">
-        <v>5027.43</v>
+        <v>5085.22</v>
       </c>
       <c r="F99">
-        <v>5605.63</v>
+        <v>5663.42</v>
       </c>
       <c r="G99">
         <v>376</v>
@@ -9405,37 +9405,37 @@
         <v>103.443</v>
       </c>
       <c r="M99">
-        <v>1321.807554</v>
+        <v>1335.434436</v>
       </c>
       <c r="N99">
-        <v>-1218.364554</v>
+        <v>-1231.991436</v>
       </c>
       <c r="O99">
-        <v>-304.5911385</v>
+        <v>-307.997859</v>
       </c>
       <c r="P99">
-        <v>-913.7734155000001</v>
+        <v>-923.993577</v>
       </c>
       <c r="Q99">
-        <v>-912.9164155000001</v>
+        <v>-923.136577</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.585129170242712</v>
+        <v>2.354793755364068</v>
       </c>
       <c r="T99">
-        <v>23.81293269831406</v>
+        <v>35.71939904747109</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.01956468619182971</v>
+        <v>0.01936504653681104</v>
       </c>
       <c r="W99">
-        <v>0.2311866469959666</v>
+        <v>0.23123372202662</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.07825874476731887</v>
+        <v>0.07746018614724415</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2737049226933689</v>
+        <v>0.2756049226933689</v>
       </c>
       <c r="C100">
-        <v>-4177.005631931945</v>
+        <v>-4243.976406976282</v>
       </c>
       <c r="D100">
-        <v>1110.414368068056</v>
+        <v>1101.233593023718</v>
       </c>
       <c r="E100">
-        <v>5085.22</v>
+        <v>5143.01</v>
       </c>
       <c r="F100">
-        <v>5663.42</v>
+        <v>5721.21</v>
       </c>
       <c r="G100">
         <v>376</v>
@@ -9487,37 +9487,37 @@
         <v>103.443</v>
       </c>
       <c r="M100">
-        <v>1335.434436</v>
+        <v>1349.061318</v>
       </c>
       <c r="N100">
-        <v>-1231.991436</v>
+        <v>-1245.618318</v>
       </c>
       <c r="O100">
-        <v>-307.997859</v>
+        <v>-311.4045795</v>
       </c>
       <c r="P100">
-        <v>-923.993577</v>
+        <v>-934.2137385000001</v>
       </c>
       <c r="Q100">
-        <v>-923.136577</v>
+        <v>-933.3567385000001</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.354793755364068</v>
+        <v>4.663787510728135</v>
       </c>
       <c r="T100">
-        <v>35.71939904747109</v>
+        <v>71.43879809494216</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.01936504653681104</v>
+        <v>0.01916944000613618</v>
       </c>
       <c r="W100">
-        <v>0.23123372202662</v>
+        <v>0.2312798460465531</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.07746018614724415</v>
+        <v>0.07667776002454474</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2756049226933689</v>
-      </c>
-      <c r="C101">
-        <v>-4243.976406976282</v>
-      </c>
-      <c r="D101">
-        <v>1101.233593023718</v>
-      </c>
-      <c r="E101">
-        <v>5143.01</v>
-      </c>
-      <c r="F101">
-        <v>5721.21</v>
-      </c>
-      <c r="G101">
-        <v>376</v>
-      </c>
-      <c r="H101">
-        <v>5200.8</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>104.3</v>
-      </c>
-      <c r="K101">
-        <v>0.857</v>
-      </c>
-      <c r="L101">
-        <v>103.443</v>
-      </c>
-      <c r="M101">
-        <v>1349.061318</v>
-      </c>
-      <c r="N101">
-        <v>-1245.618318</v>
-      </c>
-      <c r="O101">
-        <v>-311.4045795</v>
-      </c>
-      <c r="P101">
-        <v>-934.2137385000001</v>
-      </c>
-      <c r="Q101">
-        <v>-933.3567385000001</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.663787510728135</v>
-      </c>
-      <c r="T101">
-        <v>71.43879809494216</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.01916944000613618</v>
-      </c>
-      <c r="W101">
-        <v>0.2312798460465531</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.07667776002454474</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
